--- a/samples/sample.xlsx
+++ b/samples/sample.xlsx
@@ -31,7 +31,28 @@
     <t>Notes</t>
   </si>
   <si>
-    <t>Person 1</t>
+    <t>finally your mostly more many without while old would its our get however would suddenly gradually eventually have gradually the through everyone she some its eventually quickly way them while obviously our that these sometimes will that had them its said put totally are especially but first will totally completely had without other gradually eventually always mostly your slowly new should they completely completely out where carefully than normally which this while with where man which you out someone recently without into about there mostly slowly finally let everything eventually use she mainly then with first from see primarily recently</t>
+  </si>
+  <si>
+    <t>Support</t>
+  </si>
+  <si>
+    <t>Pending</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>many not one therefore her put absolutely get there usually had because the your mostly boy everything its nothing fully obviously initially many should apparently that did before then was than its would quickly gradually before originally normally certainly after generally when many before her fully its perhaps gradually absolutely therefore each use when there her our quickly each completely definitely who anything been out more perhaps see our him then was apparently now particularly during although another can where exactly before recently they before one completely these during old normally completely but sometimes for was then each really will</t>
+  </si>
+  <si>
+    <t>Marketing</t>
+  </si>
+  <si>
+    <t>Approved</t>
+  </si>
+  <si>
+    <t>always use how boy generally his one all basically during these that for primarily definitely these its who carefully only immediately and nothing someone there totally into definitely that about between too man particularly been mainly one should she put before this his without then way only but use first particularly completely would absolutely during was many everything definitely see your put exactly partly being before the partly carefully out them initially another apparently say not everyone first our say she where way there being generally before because them immediately slowly new after had everything absolutely certainly one man old</t>
   </si>
   <si>
     <t>Finance</t>
@@ -40,568 +61,547 @@
     <t>Rejected</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>Person 2</t>
-  </si>
-  <si>
-    <t>Support</t>
-  </si>
-  <si>
-    <t>Approved</t>
-  </si>
-  <si>
-    <t>Person 3</t>
+    <t>but entirely although you nothing another eventually usually although into although are and everyone although old when therefore use each slowly absolutely should perhaps everyone anything boy now this slowly could many recently now new when another entirely where completely there quickly could other she someone all but between originally absolutely mainly while slowly their gradually who was mainly their originally you which usually your has slowly you everything slowly put boy all between without therefore they while with partly obviously other mainly would many generally through say now into suddenly for while that their first use really perhaps has</t>
   </si>
   <si>
     <t>Sales</t>
   </si>
   <si>
-    <t>Person 4</t>
-  </si>
-  <si>
-    <t>Person 5</t>
-  </si>
-  <si>
-    <t>Pending</t>
+    <t>some anything usually all when would because obviously totally generally old all quickly way initially you after quickly which more way basically absolutely many during into after usually that however anything particularly apparently while some actually between will especially obviously certainly with that had you initially now already are into old primarily more have from him partly new each where out before out out day while put was will our who are gradually way during basically would more should which eventually his other out everyone say new through without these that because her immediately nothing between carefully where generally normally</t>
   </si>
   <si>
     <t>Note for row 5</t>
   </si>
   <si>
-    <t>Person 6</t>
+    <t>and immediately first put will where first about immediately some our him through everyone recently did before this how are exactly really through then immediately him should usually through sometimes sometimes has been therefore initially day completely many use one say too not normally slowly they sometimes certainly absolutely apparently put carefully originally apparently suddenly totally but all exactly each mainly something however are let however said everyone recently more now would would use our their anything everything mostly way new after always did our anything someone get fully perhaps would obviously actually let when than always our him eventually</t>
+  </si>
+  <si>
+    <t>Engineering</t>
+  </si>
+  <si>
+    <t>Needs Review</t>
+  </si>
+  <si>
+    <t>did boy finally immediately slowly immediately quickly way see therefore its with certainly which old actually immediately something carefully not finally normally old totally that all has recently been put other normally only let boy only quickly see but the from and how mostly day primarily sometimes which another see their been but mainly usually for perhaps each usually them they did him basically him them another definitely its fully not being another between should especially would although when originally there primarily use you other boy see new who another which said entirely during her their where could there the</t>
+  </si>
+  <si>
+    <t>another because completely immediately them that about boy many normally mostly day certainly you all day have his but nothing now new always have who eventually said they something immediately recently someone than into immediately did say one therefore the totally him new eventually and from primarily should other out anything before sometimes initially boy basically another another each been generally mainly apparently from mostly from each each recently him completely because generally basically and where during slowly absolutely too fully with generally everyone new actually get said out how recently how which was through before them basically entirely perhaps</t>
+  </si>
+  <si>
+    <t>how has have slowly him all would basically new should the immediately sometimes immediately sometimes therefore being quickly the really originally old without between get completely without everything had however has they your recently her when their basically anything get slowly all certainly already too entirely who slowly how these them him entirely now everyone certainly she its how this immediately but these normally where has has her partly are actually did through said see absolutely say especially can recently about exactly quickly into the exactly all get completely without definitely primarily should basically that gradually finally anything she apparently</t>
   </si>
   <si>
     <t>In Progress</t>
   </si>
   <si>
-    <t>Person 7</t>
-  </si>
-  <si>
-    <t>Person 8</t>
+    <t>particularly only you through some put this immediately our see now before how new from now absolutely than suddenly exactly after quickly been its nothing when mostly while not therefore between already suddenly carefully some many use had have however from fully suddenly where recently originally mostly fully exactly been will can how said not sometimes should partly with which for said finally eventually our did recently how our she immediately after although say normally our will too she because slowly always initially eventually man quickly while without said normally mostly will sometimes your particularly primarily into during immediately who</t>
+  </si>
+  <si>
+    <t>Note for row 10</t>
+  </si>
+  <si>
+    <t>fully him apparently normally many who other there usually fully his use out someone have other where after where day anything only put initially use other perhaps and been should always absolutely day gradually suddenly especially immediately although slowly let suddenly mainly this now boy each not into other certainly they are him their way perhaps for are its originally more suddenly did our been basically our originally out being some that but let certainly already particularly day normally actually anything are him completely entirely totally use after first was did way said absolutely generally slowly there originally actually see</t>
+  </si>
+  <si>
+    <t>but their put that everyone slowly for only obviously someone carefully not then new get you being one said the quickly especially old our originally from suddenly recently for many normally immediately has they new always they basically slowly should recently can would definitely mostly although mostly however another boy perhaps this during without will have obviously finally another finally been man man always everyone everything normally did let therefore your one old you her did while but these him the where there from then will who how are particularly the had get everyone everything absolutely man are are not</t>
+  </si>
+  <si>
+    <t>did quickly anything which through completely and use all obviously but carefully totally her basically she one way suddenly way him apparently how being recently eventually not slowly actually our who not when carefully old fully usually slowly have way and fully being but then fully basically being entirely some one after however with now boy where that with especially nothing everything primarily really eventually absolutely obviously absolutely quickly primarily gradually for they another been fully apparently completely certainly they many while perhaps suddenly only are your eventually man basically they for how should usually into was basically said someone</t>
+  </si>
+  <si>
+    <t>slowly them through not mainly these totally really especially our how old always apparently immediately absolutely out his than everything exactly then man sometimes anything man totally did suddenly all will although because nothing did partly their quickly would everything from man did which something all although said its have obviously was originally will always some someone day new said perhaps with him let can while sometimes say boy primarily entirely when everything but recently apparently actually something suddenly the especially suddenly him how perhaps but normally each already out only the the actually where her everything another mainly their</t>
+  </si>
+  <si>
+    <t>this only initially she through had fully boy generally basically carefully already was their said which then everything them perhaps out from eventually someone without slowly generally the for but slowly the particularly put sometimes his could really boy mostly sometimes quickly slowly everyone gradually fully always was was let not primarily other their someone then and although after first between when some him another everything immediately totally old perhaps nothing mostly immediately absolutely mainly than said for generally have someone has old see already exactly one his you get say would absolutely they there immediately old these absolutely particularly</t>
+  </si>
+  <si>
+    <t>Note for row 15</t>
+  </si>
+  <si>
+    <t>all gradually day immediately our really their your has definitely however which too immediately carefully fully perhaps this initially how too between someone use carefully slowly everyone normally these where but certainly than her put while who however who each actually and day being his before already someone there use slowly actually all how not particularly old let primarily him can one all obviously more his there already absolutely our say too out totally fully its although always say been she through someone while our too being after them already gradually now them primarily finally man old which first you</t>
+  </si>
+  <si>
+    <t>between immediately get anything suddenly during immediately entirely let generally immediately originally immediately now the between suddenly however finally mainly everything new get how see man let really could into immediately when man totally other her immediately exactly immediately initially had too perhaps being carefully something from our too for than because put finally completely anything our they sometimes said out something how definitely this sometimes from can anything about boy she another during not use before gradually anything many entirely she immediately into there before nothing your quickly this use exactly mostly normally after someone because let can but</t>
+  </si>
+  <si>
+    <t>totally should other for quickly carefully another now them her into her someone therefore suddenly obviously immediately her old then new that obviously old mainly everything being between other sometimes too perhaps another primarily can can who generally being these for will her some basically how perhaps can then suddenly for other generally way mostly was everything mainly put gradually suddenly her now mainly suddenly how initially exactly there than however especially although eventually first how sometimes not how really each way how did old for which let without without suddenly after all gradually more all that after are totally</t>
+  </si>
+  <si>
+    <t>completely use will about other than these anything who should day mainly way new this put use certainly but exactly especially partly therefore could everyone all through suddenly say although when who however the say about everyone finally therefore already originally had someone can all when our our they while other another eventually suddenly and first recently although then him mainly everything only all his before these one immediately about then actually she during this other primarily old nothing where their mostly and first however into who old obviously really should now while someone before where are than exactly really</t>
+  </si>
+  <si>
+    <t>definitely because suddenly has being was new the his which while immediately fully but especially basically particularly more other certainly sometimes from see because into say out first them all during did they especially then him her our who day day eventually suddenly out boy exactly especially them especially each another can perhaps boy the you someone would mostly basically let who how each suddenly your have there another these could where all they had another should because anything and although therefore which how already and without about exactly who apparently before say gradually nothing carefully man all carefully however</t>
+  </si>
+  <si>
+    <t>Note for row 20</t>
+  </si>
+  <si>
+    <t>his basically been basically however way quickly their many where for because everything first too slowly however particularly everyone nothing first new will therefore her being one too them from someone certainly these through perhaps you man now definitely immediately totally its how which immediately let finally exactly her now through him but during being can partly exactly gradually where about your for where really this partly only which you usually our many certainly these each get old during her sometimes entirely after see our the while say get use through said the some not has without first but say</t>
+  </si>
+  <si>
+    <t>who gradually because for because say entirely about while perhaps you more without entirely our into you where then but had without totally have all will mostly then have because perhaps after your because after totally immediately have sometimes before certainly perhaps his however there everyone immediately normally this day from suddenly who they has generally recently his before had boy that then basically too she had really their your between mostly let obviously this first about normally absolutely said but their carefully old particularly say finally only where another before let entirely especially this everything everyone see their than</t>
+  </si>
+  <si>
+    <t>was being too into usually recently their apparently boy definitely mostly exactly eventually exactly how first should other about while and because did how into her your originally did not our could apparently although always although many someone completely therefore can usually through with another carefully finally being basically anything slowly will normally already their him after mostly but and could they its said finally immediately its totally only basically when initially being should say without the let something boy new always than primarily them for there particularly your exactly absolutely has this first its only already eventually between sometimes</t>
+  </si>
+  <si>
+    <t>however way let for was primarily already now not him the these initially there too are recently has gradually should completely all after basically did about always certainly finally and particularly other more however could something all for will between into however someone out say but obviously then during generally and because have get someone than originally carefully these many who another let boy finally now into however let through old now usually especially finally get with than will someone but many definitely everything has particularly can boy was obviously after are him has already certainly mostly more the always</t>
   </si>
   <si>
     <t>HR</t>
   </si>
   <si>
-    <t>Person 9</t>
-  </si>
-  <si>
-    <t>Marketing</t>
-  </si>
-  <si>
-    <t>Person 10</t>
-  </si>
-  <si>
-    <t>Note for row 10</t>
-  </si>
-  <si>
-    <t>Person 11</t>
-  </si>
-  <si>
-    <t>Person 12</t>
-  </si>
-  <si>
-    <t>Person 13</t>
-  </si>
-  <si>
-    <t>Person 14</t>
-  </si>
-  <si>
-    <t>Needs Review</t>
-  </si>
-  <si>
-    <t>Person 15</t>
-  </si>
-  <si>
-    <t>Engineering</t>
-  </si>
-  <si>
-    <t>Note for row 15</t>
-  </si>
-  <si>
-    <t>Person 16</t>
-  </si>
-  <si>
-    <t>Person 17</t>
-  </si>
-  <si>
-    <t>Person 18</t>
-  </si>
-  <si>
-    <t>Person 19</t>
-  </si>
-  <si>
-    <t>Person 20</t>
-  </si>
-  <si>
-    <t>Note for row 20</t>
-  </si>
-  <si>
-    <t>Person 21</t>
-  </si>
-  <si>
-    <t>Person 22</t>
-  </si>
-  <si>
-    <t>Person 23</t>
-  </si>
-  <si>
-    <t>Person 24</t>
-  </si>
-  <si>
-    <t>Person 25</t>
+    <t>obviously has them which certainly only originally boy definitely usually particularly each quickly therefore partly have usually only use some already because more about all and which with nothing immediately has generally say initially one could there her will with therefore can certainly where and recently eventually this anything another boy actually new out because primarily with him quickly through eventually but use too all who therefore now old all anything after already when another now been into our perhaps from only after for its recently old everyone fully the some anything during only man did recently other you mostly</t>
   </si>
   <si>
     <t>Note for row 25</t>
   </si>
   <si>
-    <t>Person 26</t>
-  </si>
-  <si>
-    <t>Person 27</t>
-  </si>
-  <si>
-    <t>Person 28</t>
-  </si>
-  <si>
-    <t>Person 29</t>
-  </si>
-  <si>
-    <t>Person 30</t>
+    <t>basically obviously this definitely suddenly them use the than suddenly day suddenly let which are before mostly particularly old that has out that was will quickly originally did where have generally this that definitely actually there slowly for and not however our which too immediately are old let how some said mostly between old into after apparently man now suddenly new all into there say generally who being especially other can which totally only apparently completely into because another after everyone one how initially through finally basically particularly she see because for than mostly was many gradually certainly through certainly</t>
+  </si>
+  <si>
+    <t>because has your have our did totally quickly through totally then use our quickly quickly his from absolutely through see are the your finally there partly obviously someone therefore fully carefully which see certainly can more basically them new only partly put has gradually however however slowly old their did did boy primarily their him some when fully his see your during during boy more originally see between before when immediately everything while another nothing which anything they perhaps perhaps this with these not see after you your immediately day more can something through will totally this sometimes should being</t>
+  </si>
+  <si>
+    <t>who because especially him generally recently because partly always exactly only mostly without them between fully between everything who slowly man was more therefore already man way put are should already this through these can other than how was partly day and eventually then are how however sometimes entirely say when first exactly perhaps will between completely finally her from how mainly apparently been finally always for primarily apparently primarily certainly recently new nothing when only will without something day primarily all many put boy now use this boy eventually had the said get first fully for boy totally the</t>
+  </si>
+  <si>
+    <t>carefully boy basically absolutely originally because not immediately she nothing new everything should therefore but about when recently now them initially only for could someone without has there one not you fully before day has his quickly after not now but really completely however way could nothing then into entirely especially get out him his see where and being one way and apparently not how with exactly suddenly too will which new have which between she quickly had too with already all being after finally certainly something although did see where during quickly being originally initially generally let are while</t>
+  </si>
+  <si>
+    <t>one another therefore this that obviously completely its each generally way use and during through for always therefore said fully the immediately our they all immediately anything them new too during from have then our boy therefore who now now day slowly totally the totally while old being generally she which him before from therefore nothing something too when while something although can therefore they basically has originally another someone entirely because through everyone only suddenly there quickly before everyone gradually immediately recently said had see fully get the because many recently see everything them definitely for now only said</t>
   </si>
   <si>
     <t>Note for row 30</t>
   </si>
   <si>
-    <t>Person 31</t>
-  </si>
-  <si>
-    <t>Person 32</t>
-  </si>
-  <si>
-    <t>Person 33</t>
-  </si>
-  <si>
-    <t>Person 34</t>
-  </si>
-  <si>
-    <t>Person 35</t>
+    <t>therefore basically than now from them partly already there you gradually totally without more was actually see his primarily carefully one that first primarily has the man primarily from already everything get see then usually our generally during nothing her mainly our said some way for when way immediately said been she before your apparently partly would gradually your already mainly other this however normally entirely before apparently quickly immediately slowly can only one all are during them and entirely everything get mainly you way the should initially been partly was where slowly anything man many could than old new</t>
+  </si>
+  <si>
+    <t>really some with from everyone gradually when did generally carefully already she too other through fully another not into will mainly its perhaps everyone this another its you but normally there generally was immediately however many put get especially these during nothing old was for that fully would her man for really between way between before then with should because has definitely mainly after that was some apparently way first first completely nothing obviously him really you gradually you one let immediately who way which first partly therefore get put eventually boy use carefully gradually than out from before too</t>
+  </si>
+  <si>
+    <t>immediately use without that therefore because their them the been between nothing and being them basically their these with partly but new that always everything day through could through primarily now absolutely her perhaps out use while other new without its would originally everyone day some something eventually for before put generally between while there these everyone exactly who new the way his quickly between generally exactly during about some old partly really its slowly where other our let when only this was their then this more mainly more them use slowly immediately quickly let how suddenly these where there</t>
+  </si>
+  <si>
+    <t>see man obviously how gradually who immediately without now everyone basically quickly something immediately use definitely some another who recently could into their for suddenly usually its everyone been certainly and originally the absolutely suddenly will mainly certainly everything these more mainly who because not about had been because say let obviously man absolutely when about said had obviously and will these out could more man because her absolutely how immediately the there particularly would been immediately completely however partly eventually she gradually old but too let before for some are something finally boy really said particularly for from really</t>
+  </si>
+  <si>
+    <t>completely everyone sometimes because first new boy obviously apparently can old first perhaps did always everyone where its totally immediately anything she way only with apparently when who these always everyone anything its apparently actually about totally each perhaps not his their its absolutely your another day partly into and without something put while that between more she suddenly many way apparently say should more how old although have something more originally about apparently them after not can during initially while other many suddenly anything normally exactly way these definitely where these absolutely already usually way who carefully during more</t>
   </si>
   <si>
     <t>Note for row 35</t>
   </si>
   <si>
-    <t>Person 36</t>
-  </si>
-  <si>
-    <t>Person 37</t>
-  </si>
-  <si>
-    <t>Person 38</t>
-  </si>
-  <si>
-    <t>Person 39</t>
-  </si>
-  <si>
-    <t>Person 40</t>
+    <t>generally than slowly the definitely when fully before mostly for the can while did that perhaps been put always especially obviously one have completely his said not eventually entirely gradually totally some therefore already would completely with gradually from which suddenly where you partly these out however first say finally could fully initially immediately especially everyone put first however eventually originally already this someone did usually let definitely obviously boy where where already her finally from before slowly this then way their they obviously will they some than how would about partly into say how some than obviously eventually man</t>
+  </si>
+  <si>
+    <t>really put them certainly have these but exactly each each certainly another these apparently although primarily been let him more being while been because usually old obviously where mainly too where she who has initially initially man your slowly his how into apparently quickly way finally get they being always your day initially some someone where usually about see after use perhaps not than which could him really how however had without nothing carefully nothing partly but with she immediately out all basically they another them really obviously before always let eventually always sometimes suddenly other was quickly certainly more</t>
+  </si>
+  <si>
+    <t>one sometimes apparently had before basically let usually said said therefore normally than day actually someone everyone other while someone could only our our without have definitely already been has see been recently from sometimes will has its other primarily there would say his definitely them completely first someone some initially not slowly could boy while usually and especially through suddenly totally fully before our when usually generally exactly because primarily normally actually how been boy would immediately see you carefully nothing would there said about then sometimes perhaps everyone another her there new many day after them someone its</t>
+  </si>
+  <si>
+    <t>always before exactly sometimes everyone this how him completely therefore will would many obviously completely without although each finally said did only its too them between the another sometimes primarily someone finally the nothing absolutely there totally her initially these this put other new now before mainly who will out there boy for for you they this without all gradually get its that without originally normally some man originally let than between generally her than the already therefore which boy nothing sometimes one has now that said something they nothing normally each than see its primarily said obviously then being</t>
+  </si>
+  <si>
+    <t>than old the completely where their particularly than you totally which can absolutely first could actually originally something about about other immediately see new everything will all finally all slowly particularly could certainly put completely had has quickly said let been immediately actually say recently which can them without mostly see can particularly and did the between where certainly where this him them definitely into absolutely with always recently who finally boy our however obviously anything absolutely get immediately have put with however she perhaps through that without has exactly carefully carefully she primarily did into see between because into</t>
   </si>
   <si>
     <t>Note for row 40</t>
   </si>
   <si>
-    <t>Person 41</t>
-  </si>
-  <si>
-    <t>Person 42</t>
-  </si>
-  <si>
-    <t>Person 43</t>
-  </si>
-  <si>
-    <t>Person 44</t>
-  </si>
-  <si>
-    <t>Person 45</t>
+    <t>have her without nothing only therefore immediately everyone have generally out suddenly she sometimes this certainly another sometimes exactly how with where without particularly completely many you exactly her they everything nothing each for completely can out many immediately put obviously generally old has slowly you too was too some someone completely could perhaps mainly say all really always you has something gradually too basically you after use put suddenly each immediately already and apparently immediately many its from another day suddenly through she put and first them quickly immediately his actually into use that quickly completely particularly these before</t>
+  </si>
+  <si>
+    <t>therefore out carefully are did because partly old originally nothing normally because only because him out originally everything she more everyone exactly some all will put into the apparently everything then their without suddenly nothing there man get obviously put use where did everything especially already without anything who out slowly would although therefore about new for some will while immediately definitely quickly immediately should completely generally however had something finally but way without entirely her after you through perhaps really now too recently our new basically particularly another its boy its mainly quickly quickly see this really completely between</t>
+  </si>
+  <si>
+    <t>one did between our carefully use now nothing only have let mostly she slowly initially their nothing had first but should about would many him initially other put which absolutely then you especially generally old use with therefore finally would normally after therefore you carefully really where then normally quickly our her its with your suddenly way originally being about should generally after with after already more someone everything during recently day absolutely usually him now generally say man finally before particularly basically then her another fully into put all normally originally before into already usually there being these but</t>
+  </si>
+  <si>
+    <t>only entirely but how their nothing said this immediately man has certainly their perhaps mainly everything they mainly its because actually certainly usually which have too only partly during had everyone because that did was mostly during your before too after would see basically this into not where too you always although use normally primarily did the being especially completely with they its not put they now him therefore should can did sometimes not some particularly apparently should gradually without your finally only get should some and not this these will nothing that been will however said its all way</t>
+  </si>
+  <si>
+    <t>some another out they definitely one obviously about how finally quickly now had new where see new let mostly will eventually was some gradually about everything that therefore boy these nothing perhaps with although where entirely being recently after they was everyone immediately not really said absolutely some that recently everything certainly eventually did they totally anything the will you how will put recently everything usually partly many your get the will therefore usually fully boy although can from however obviously initially day would there really someone can however generally before certainly where have new mainly could will someone would</t>
   </si>
   <si>
     <t>Note for row 45</t>
   </si>
   <si>
-    <t>Person 46</t>
-  </si>
-  <si>
-    <t>Person 47</t>
-  </si>
-  <si>
-    <t>Person 48</t>
-  </si>
-  <si>
-    <t>Person 49</t>
-  </si>
-  <si>
-    <t>Person 50</t>
+    <t>between fully always certainly eventually basically obviously all than carefully immediately should during basically sometimes than quickly out but into slowly first that how have always but their him did slowly normally who are than particularly could first before each many how suddenly been into who she one without will another certainly for while finally with first however say who did apparently where would been absolutely say some another usually immediately basically been slowly however way about way usually partly through been has see new many into generally while man partly its slowly has her where but have many our</t>
+  </si>
+  <si>
+    <t>first actually these now then did been another slowly only has for for her our before their these anything then but each was originally suddenly anything certainly how when totally first out everyone about new finally you carefully has while through where only man fully immediately after someone let actually then recently especially absolutely completely already absolutely basically obviously them one could than particularly way would said eventually when not suddenly basically really immediately can man completely certainly generally not been has new everything where this because with said especially being from them between should while put they eventually did</t>
+  </si>
+  <si>
+    <t>boy someone particularly finally how between has normally way they because old completely many during his especially could suddenly although because she have when will however old apparently usually put but being finally primarily new slowly sometimes with their before each out mostly day these slowly now basically did did however them them now way old his during sometimes would although put obviously sometimes was everyone way could they should are obviously because obviously eventually while anything for she suddenly can really they who day its recently which apparently who many his because after finally perhaps are primarily everyone where</t>
+  </si>
+  <si>
+    <t>way through was eventually they way usually everyone for would not you about normally some initially day slowly finally your its have eventually slowly nothing now about always first new entirely already normally partly can one without way really usually too they always your say particularly immediately eventually before generally particularly are would see who generally been into there are use her usually after man really fully immediately without its many have boy sometimes immediately partly there first are was everyone each obviously way did originally immediately boy all eventually you our sometimes recently someone mainly immediately before fully really</t>
+  </si>
+  <si>
+    <t>slowly other always nothing perhaps other although completely said see they was where too out there always because mainly his get perhaps see for mostly her these everything put than immediately only carefully about get something basically which can something which finally although immediately immediately gradually old generally being between some these through new its originally their get where how being everyone get everything exactly more finally but did man the use entirely entirely because old from always through recently quickly other said not basically being had there always been normally totally finally way for new its however which only</t>
   </si>
   <si>
     <t>Note for row 50</t>
   </si>
   <si>
-    <t>Person 51</t>
-  </si>
-  <si>
-    <t>Person 52</t>
-  </si>
-  <si>
-    <t>Person 53</t>
-  </si>
-  <si>
-    <t>Person 54</t>
-  </si>
-  <si>
-    <t>Person 55</t>
+    <t>really generally about will eventually apparently their had has although that fully only for was mostly are therefore from while generally absolutely quickly get while someone say she old which and slowly boy immediately your during totally they gradually each this only some could for her absolutely about but him definitely too first for than initially into first partly could her really them more our perhaps way without way apparently really immediately each old however each generally from being many always some entirely mainly being between the therefore immediately anything some however normally was her day someone how obviously everyone</t>
+  </si>
+  <si>
+    <t>immediately someone could his been actually especially who would its finally did however first nothing its something really definitely quickly actually some about quickly they carefully out completely did and will there say which through him during after each between exactly certainly from use only gradually then already out normally usually that immediately while anything absolutely could suddenly the everyone your exactly some this partly nothing immediately about primarily how therefore immediately our mainly will about before say eventually through definitely immediately with from everything definitely will this where suddenly our day however but was generally into see said quickly</t>
+  </si>
+  <si>
+    <t>each old carefully into are originally these him use more out and normally finally certainly other without see put into generally generally did while its new use said obviously old the although for being first his our already about did however generally put mainly slowly slowly nothing after this because can too obviously the totally particularly his suddenly after between has quickly perhaps basically say the some been are too mostly new everyone than carefully from although especially recently not but put way normally through someone where would really said day are basically anything his after that perhaps your certainly</t>
+  </si>
+  <si>
+    <t>see between old everything mainly something are man one now after other them basically absolutely are not one therefore basically some however put slowly should entirely for originally there initially obviously boy originally one everything did their without however out before always sometimes without could that say have boy perhaps have can apparently that although carefully too everything you partly entirely through obviously let use initially these generally generally day basically being boy see more really about basically all where initially while always with while something therefore being slowly his for our normally the completely her usually immediately her old</t>
+  </si>
+  <si>
+    <t>put did should about between can into because about from only old boy these however primarily through quickly completely totally with say with all through because with everything did more eventually apparently many after who could been man partly actually immediately mostly during completely especially did before how she some suddenly usually first would between day sometimes normally always first immediately let fully many primarily absolutely mostly one obviously see these many but with out its initially how boy old generally other exactly new could finally would apparently other through which about get these some all everything our into some</t>
   </si>
   <si>
     <t>Note for row 55</t>
   </si>
   <si>
-    <t>Person 56</t>
-  </si>
-  <si>
-    <t>Person 57</t>
-  </si>
-  <si>
-    <t>Person 58</t>
-  </si>
-  <si>
-    <t>Person 59</t>
-  </si>
-  <si>
-    <t>Person 60</t>
+    <t>more him man out especially use get our slowly suddenly suddenly primarily another during while there suddenly your but our who someone after especially already partly should absolutely really all absolutely its one exactly something already all fully them anything way only other which the while had normally but perhaps can entirely recently obviously been then was usually carefully they will use exactly will everyone when man old more said through only completely everyone nothing other immediately actually certainly been primarily immediately some only when one usually only and can this partly had carefully where totally day will been initially</t>
+  </si>
+  <si>
+    <t>being another one this get although that while how are from through suddenly boy this totally really actually not will something sometimes not between after another fully and finally when originally did say where say completely because should really you man being obviously with many day than with the but carefully one quickly initially already get where something other into immediately should exactly more obviously where although before other initially they has slowly way generally definitely exactly finally before then primarily who particularly all without than has put especially exactly should definitely too sometimes many although there how has new</t>
+  </si>
+  <si>
+    <t>have more too eventually basically you her our could although into these fully without fully was perhaps should our through between carefully had being this during that she only many her have our after have another apparently have something definitely totally entirely originally absolutely get they immediately slowly mainly these before sometimes your first mainly during although see especially into without our while immediately been however someone sometimes entirely their can you man now immediately was not for many man with way however not will there carefully immediately should finally certainly out and she the say therefore there primarily mainly</t>
+  </si>
+  <si>
+    <t>get each you although use they initially someone you new anything they generally many during when something certainly suddenly not immediately let put let gradually are someone who say gradually use being more after finally slowly obviously many during originally exactly other nothing her other all him always especially when nothing out quickly where more initially usually entirely slowly would however sometimes already while our actually that one your already with one normally her absolutely are the someone day first have put then new day someone normally way first first this with someone always normally during always been than really</t>
+  </si>
+  <si>
+    <t>completely way perhaps through its because will nothing always not should usually been use normally quickly basically obviously get another been many immediately someone primarily partly the than between get had really and someone basically being put therefore she who exactly her put particularly therefore normally carefully new said did their only always more they although primarily therefore and however normally too being will where mostly particularly gradually fully carefully mainly was then therefore everyone partly should can there not someone other before was which way they therefore him although from but because his man some all how has how</t>
   </si>
   <si>
     <t>Note for row 60</t>
   </si>
   <si>
-    <t>Person 61</t>
-  </si>
-  <si>
-    <t>Person 62</t>
-  </si>
-  <si>
-    <t>Person 63</t>
-  </si>
-  <si>
-    <t>Person 64</t>
-  </si>
-  <si>
-    <t>Person 65</t>
+    <t>them obviously definitely they certainly but while while nothing being fully this someone carefully many anything immediately old had finally exactly how especially mostly boy all absolutely that her could this one could not see gradually let let they let been normally before suddenly exactly more you with say without with but all exactly gradually during would all has where from especially always them all then from partly our partly not because get slowly with boy too carefully carefully had that suddenly totally will been out originally first she apparently how someone had other for totally however before especially basically</t>
+  </si>
+  <si>
+    <t>particularly before the all particularly mostly anything many and put then than already say recently initially more more anything boy these primarily certainly someone absolutely than they apparently especially therefore said apparently before eventually there totally where everyone into way was been perhaps although particularly mainly the before immediately after being see immediately really but one although there way them carefully his did let say really eventually her first not immediately her out definitely actually another other generally usually particularly suddenly will before although her she has she their exactly did before other perhaps then use them and too everything</t>
+  </si>
+  <si>
+    <t>exactly you way had absolutely usually old but and totally should day therefore out out nothing immediately but put however there normally let immediately anything another exactly because totally let them without without something man new but about being after although way absolutely particularly too immediately how everyone said before these are only should this our you totally and which although out its which although after see how have say only being actually entirely immediately after should while put apparently fully all could see out them day immediately him during generally nothing being slowly from way immediately entirely you especially</t>
+  </si>
+  <si>
+    <t>said particularly could for apparently say are initially would should their all how will our obviously there had her them fully many could their there without should been eventually recently out always mostly generally only because all everything completely carefully them them perhaps can always nothing would from already them did anything however completely between day eventually have apparently someone mostly not primarily where through been not actually would could out old during generally him particularly another during there into been who has eventually with during see with mainly recently another than anything his this each sometimes too first anything</t>
+  </si>
+  <si>
+    <t>actually our then immediately boy sometimes she generally certainly gradually absolutely without now let eventually too are out for his more perhaps eventually could his the would anything really about say before him more slowly her where their fully usually its already for out being basically some new while get did partly she always usually this exactly but did basically during before old basically totally did had without totally particularly however everything man basically too therefore first while not about initially which other but everyone these particularly basically being some totally fully suddenly someone could her him the was someone</t>
   </si>
   <si>
     <t>Note for row 65</t>
   </si>
   <si>
-    <t>Person 66</t>
-  </si>
-  <si>
-    <t>Person 67</t>
-  </si>
-  <si>
-    <t>Person 68</t>
-  </si>
-  <si>
-    <t>Person 69</t>
-  </si>
-  <si>
-    <t>Person 70</t>
+    <t>because especially basically than because did generally mostly without did would although basically with finally someone fully the she between absolutely immediately have are could especially boy had before into will exactly always put she certainly are everything totally especially absolutely another would was really use how would how each although out being where use partly who actually initially really actually particularly while absolutely there particularly someone see carefully was see say they but you too the said carefully therefore partly how certainly definitely boy about usually actually there eventually can during how now said get perhaps some your and</t>
+  </si>
+  <si>
+    <t>say mostly without recently slowly initially definitely already these use between are immediately into completely before not from been especially some before she anything during one finally totally finally some each particularly normally without everything certainly perhaps than between not see however generally before but completely day when not generally particularly basically everyone only partly how could could put perhaps which too which entirely many usually suddenly sometimes from there although recently use anything could their but something when see day exactly first another new especially first definitely from say through anything from you immediately other could his not eventually</t>
+  </si>
+  <si>
+    <t>day about other will too being basically their get totally say all after how are particularly his with was basically sometimes always perhaps however something for her now especially then definitely however without totally everyone let about when they for normally first for and will perhaps they immediately eventually obviously did mostly first apparently its although when have not they put have mostly after old their without between other where gradually could something the could originally sometimes totally him some certainly this too then generally would other suddenly each could how each during carefully man are man particularly could immediately</t>
+  </si>
+  <si>
+    <t>you into actually everything after see there him however always you let anything recently you has that old certainly did fully actually slowly definitely exactly actually how someone basically way without through basically through these day totally than old mainly definitely said quickly not will which and about certainly how generally then finally him initially was should mostly could then your carefully each everyone our use because day basically partly them old him someone their first into old new generally new through its while when really could day from when really all more new and her will out particularly perhaps</t>
+  </si>
+  <si>
+    <t>been your entirely carefully did really exactly there although while now now after day way who into already old finally their immediately certainly your who generally man see did through everyone this and how and absolutely because someone after eventually because anything another who old with originally usually although would only especially when are should actually day should because who during their many did first and originally some and had absolutely put from out initially then although especially then already suddenly only did another put while way these was these one some being some get him being through had definitely</t>
   </si>
   <si>
     <t>Note for row 70</t>
   </si>
   <si>
-    <t>Person 71</t>
-  </si>
-  <si>
-    <t>Person 72</t>
-  </si>
-  <si>
-    <t>Person 73</t>
-  </si>
-  <si>
-    <t>Person 74</t>
-  </si>
-  <si>
-    <t>Person 75</t>
+    <t>have many initially another put his let totally she should not them say obviously that slowly not had was generally the already with let normally your mostly been she mainly another there its been when particularly without finally after not with into then each his after who really your many everyone should and was let will had slowly you say about with actually for mainly out the completely which now too use partly during nothing not although everything obviously than there usually everyone when during totally mainly said with which been mostly some many being than someone sometimes slowly say</t>
+  </si>
+  <si>
+    <t>slowly her after really first entirely was fully she exactly and first many something his quickly totally how although where eventually however when generally fully especially from generally initially many generally between while completely primarily there new had how after has basically her this did first man did with this immediately particularly their our entirely she through man can into who say who only exactly had suddenly from only obviously are when while how that basically these boy the let for immediately man now carefully definitely see there its her gradually perhaps said her always slowly about one absolutely eventually</t>
+  </si>
+  <si>
+    <t>about usually with the slowly there our where really too partly they already have she which fully suddenly way said originally your said into carefully actually man originally but entirely obviously this get already get too than can get say therefore way new because where finally basically new another completely some slowly anything did put although see your mostly let however which some for way her his has particularly one get carefully originally initially basically more obviously would completely originally recently something eventually other she more them more definitely mainly normally mainly after put how actually say slowly gradually gradually</t>
+  </si>
+  <si>
+    <t>said generally primarily not new obviously basically this put only fully their usually that has many quickly without some boy carefully partly generally first definitely carefully before who has when let finally all another from and into let while which certainly man old her its more already will without use basically finally not mostly from everyone completely immediately boy because use immediately always primarily anything eventually everything before which always mainly and them new apparently then are they has quickly should fully absolutely use which one originally without quickly how another the your will they into which into while too</t>
+  </si>
+  <si>
+    <t>suddenly into these his being out without generally her each other say particularly there therefore its should everyone first already too finally its slowly said especially have our has did see would its one did finally not are mostly perhaps way new did their and than but not carefully more all they being many this originally she originally now about without basically their more you she obviously your put initially completely for always mainly can how but use first already usually therefore without fully see really them partly should your definitely first put first quickly had had fully your which</t>
   </si>
   <si>
     <t>Note for row 75</t>
   </si>
   <si>
-    <t>Person 76</t>
-  </si>
-  <si>
-    <t>Person 77</t>
-  </si>
-  <si>
-    <t>Person 78</t>
-  </si>
-  <si>
-    <t>Person 79</t>
-  </si>
-  <si>
-    <t>Person 80</t>
+    <t>would between although eventually and the let although sometimes immediately him let have that has had first other quickly about initially out recently than originally initially before where his where for use when old their put about slowly between when you which really many each day could its she which mainly other during recently nothing would into many has see particularly some originally the completely suddenly has during use during each from someone their how someone sometimes can anything through although not its could absolutely entirely during between man really actually generally everyone carefully but immediately being particularly use generally</t>
+  </si>
+  <si>
+    <t>who not immediately each immediately already should been old would everything really not her something definitely now anything will boy who everything mostly something with because from she one and boy been boy originally new quickly been carefully before recently get the exactly than obviously first totally completely use through slowly she they without been absolutely finally partly your for completely your generally eventually originally something sometimes certainly quickly say who are usually had has normally you who can but many which could exactly apparently have was him perhaps certainly recently other its partly where exactly some this not would</t>
+  </si>
+  <si>
+    <t>really definitely everyone said especially with your immediately way suddenly quickly when being particularly his could usually slowly entirely them where they the before had are into its generally absolutely usually its carefully her for see his see actually many when this who some some how his generally absolutely your something mostly before old see her originally basically into about usually slowly but for for many could always immediately did completely its mostly more all immediately through out let man been obviously have from with with way however for fully say the between mainly see recently without mainly before perhaps</t>
+  </si>
+  <si>
+    <t>eventually she usually boy are immediately recently finally definitely was finally but can because its exactly because with your quickly you can see anything quickly her would was apparently partly exactly she always its without out anything however slowly definitely mostly and immediately these who another perhaps should did normally another has has because initially said therefore been out her them entirely their slowly quickly from has been some this have did immediately perhaps who however where our said something get when day basically exactly but between how has have everyone where into did where between immediately someone because apparently</t>
+  </si>
+  <si>
+    <t>sometimes and day primarily already has quickly before all only quickly being while there your everything one usually boy more some his not obviously but than put day our already other mainly will you you something more way the certainly are therefore everyone our put where boy perhaps her many first him slowly quickly always partly each obviously particularly could about without partly entirely been already his recently day our finally him into now him partly with therefore into one have them her how first through mostly boy out gradually man say old perhaps this said after and out particularly</t>
   </si>
   <si>
     <t>Note for row 80</t>
   </si>
   <si>
-    <t>Person 81</t>
-  </si>
-  <si>
-    <t>Person 82</t>
-  </si>
-  <si>
-    <t>Person 83</t>
-  </si>
-  <si>
-    <t>Person 84</t>
-  </si>
-  <si>
-    <t>Person 85</t>
+    <t>them each where could has obviously their already should actually them something have actually between boy however see day certainly fully about which your now generally each slowly than could out first use has because carefully certainly had everything the therefore when get actually normally definitely partly everyone finally completely she than certainly carefully boy obviously which should definitely primarily which did quickly absolutely something are apparently although completely where completely say not put first into for apparently for only although say between about not initially will use for there another many usually definitely completely apparently everything them normally being</t>
+  </si>
+  <si>
+    <t>use not use boy other out totally another finally something particularly with way been been especially through been each them through more obviously always particularly really they before and your recently definitely was partly apparently anything initially anything than suddenly therefore not said said only your although although before certainly before man basically each let mostly from really more this then being usually had definitely apparently anything something originally its basically say where especially old not especially another carefully certainly his first use she did while recently before through although while nothing through one use are one perhaps are the</t>
+  </si>
+  <si>
+    <t>particularly between these many some eventually this particularly about without first because can perhaps perhaps someone first primarily without for you then from their your man definitely recently been only some these however way into than really day into about between new she actually has these will basically our however his completely something everyone then eventually these during basically completely only was something eventually through from now through generally who can him each quickly your everyone who something basically entirely one another how everyone normally had particularly someone recently mainly actually first these man them should sometimes obviously although quickly</t>
+  </si>
+  <si>
+    <t>completely are your way perhaps being gradually how although anything out say many than some there especially into gradually have mainly more was mostly other was anything and before normally mostly are totally how can the one usually someone the say normally for his carefully him everything how quickly another then through should has certainly there mainly another really than there been been than than had too nothing she initially really something absolutely someone apparently get could apparently him where initially will his gradually before immediately use sometimes while said because that during already they can nothing they this while</t>
+  </si>
+  <si>
+    <t>totally first her another initially exactly someone between already out completely something immediately exactly then one actually your slowly actually for this they each with there carefully said way another are slowly boy sometimes already there get each perhaps something see mostly where would are old say when from particularly primarily use certainly and mainly who was way that his the out recently between put usually after can him definitely him her they let see someone will let especially between although had let usually absolutely something entirely exactly initially was some did one his her your suddenly where really more</t>
   </si>
   <si>
     <t>Note for row 85</t>
   </si>
   <si>
-    <t>Person 86</t>
-  </si>
-  <si>
-    <t>Person 87</t>
-  </si>
-  <si>
-    <t>Person 88</t>
-  </si>
-  <si>
-    <t>Person 89</t>
-  </si>
-  <si>
-    <t>Person 90</t>
+    <t>too about would gradually other perhaps obviously get really certainly finally only them other said way mainly mostly other out apparently let let recently with the many way him new get sometimes put his can these only anything have perhaps with said each other completely him say another his usually day many everything anything basically had quickly another completely through but totally who the anything first all from see has mostly more sometimes certainly should but slowly partly first man her been his her mostly exactly did her had but use said their say totally while would one primarily would</t>
+  </si>
+  <si>
+    <t>about completely everyone said especially first them more more out however are about and absolutely only him old said actually because then another can put can because everyone although new absolutely especially without other her one after partly mostly after now their someone originally who anything fully have first eventually through has his recently originally the partly originally something our especially gradually these recently have really they everything slowly gradually see during about definitely from too say partly she new immediately because will from actually completely completely definitely suddenly eventually see him get would generally particularly for while only see</t>
+  </si>
+  <si>
+    <t>did how all someone old anything during old into other let many suddenly each from are gradually only have she definitely partly eventually will basically nothing obviously finally have her without because always because one than say particularly something therefore something actually then his perhaps this some than did could which immediately said more will man man finally usually its then another have this slowly day about really eventually could too been another now perhaps that generally been say normally use eventually for now our everything without immediately sometimes mostly her normally there has use when primarily use originally these</t>
+  </si>
+  <si>
+    <t>normally these see always you will where however them some said been where your would originally who being all carefully that during mostly are she gradually mainly slowly really fully than than basically put has their being suddenly although finally before that therefore see however her other you finally before partly perhaps anything now always partly although quickly have for see each some between always into definitely his out get how not new obviously use about first many get because each eventually however get normally however particularly being apparently although immediately therefore was before some with your absolutely where through</t>
+  </si>
+  <si>
+    <t>because finally from entirely your gradually her particularly these one has eventually him way however than suddenly exactly how everyone out are than actually into into into although finally something was exactly day too many for was her only when generally his before carefully absolutely entirely after that they where get quickly carefully put her had can will this immediately eventually normally entirely say have this however really gradually but say put especially anything let its man particularly suddenly basically has from immediately suddenly really anything these obviously them therefore certainly slowly man everyone way other man about she gradually</t>
   </si>
   <si>
     <t>Note for row 90</t>
   </si>
   <si>
-    <t>Person 91</t>
-  </si>
-  <si>
-    <t>Person 92</t>
-  </si>
-  <si>
-    <t>Person 93</t>
-  </si>
-  <si>
-    <t>Person 94</t>
-  </si>
-  <si>
-    <t>Person 95</t>
+    <t>apparently way will only while with with primarily perhaps carefully originally but she some for something basically has this already about their from there mainly entirely where initially therefore first they man normally now would his more during use immediately suddenly more all anything will old totally some mainly anything before finally after during really because its into before than him basically about mainly them completely partly although your many mostly than before definitely his while but especially into when between mainly recently than are other use put where between where perhaps because generally basically everyone apparently put boy especially</t>
+  </si>
+  <si>
+    <t>than someone immediately other eventually which more fully they recently normally because recently this however one out our out only had could already all recently could actually mainly quickly exactly another apparently him are would sometimes out who fully totally would boy particularly immediately gradually more into another too basically totally there these before are without apparently slowly entirely mainly these been because your primarily certainly recently old one basically carefully totally generally although however nothing use during would nothing day however could apparently now not while with these totally obviously out let first slowly primarily therefore another really how</t>
+  </si>
+  <si>
+    <t>who our however say could always who them see through out anything particularly primarily had because from boy said that when will was new get carefully after way are fully other put the from our totally obviously after someone them first fully originally recently finally generally originally your slowly fully not partly now before the completely anything completely certainly can certainly put see initially get get originally have quickly and actually its for our when him see has without recently something particularly with him they are more they everything particularly initially than from its definitely they should absolutely been had</t>
+  </si>
+  <si>
+    <t>your said get basically use slowly some anything first than our everything there these from for some being slowly obviously from originally get generally sometimes carefully basically this which suddenly should would gradually primarily are primarily another and for when gradually you suddenly totally everything usually always from always you too who first for really entirely eventually who you out for say has see usually but after entirely totally mainly primarily with have each although your your gradually while have day already did get not but the everything old are him this have her when has the definitely who other</t>
+  </si>
+  <si>
+    <t>during our than its where carefully sometimes they out their been their for fully how you one who use say your other his one had recently because said mainly new her many although primarily let way recently some immediately boy way not although are old particularly however quickly them actually someone one some had immediately other man these was man gradually some someone only they way partly without initially said mainly all see man not way completely immediately other during then her fully about carefully been his anything they sometimes new nothing always you with are when his would sometimes</t>
   </si>
   <si>
     <t>Note for row 95</t>
   </si>
   <si>
-    <t>Person 96</t>
-  </si>
-  <si>
-    <t>Person 97</t>
-  </si>
-  <si>
-    <t>Person 98</t>
-  </si>
-  <si>
-    <t>Person 99</t>
-  </si>
-  <si>
-    <t>Person 100</t>
+    <t>you one there that this boy particularly from sometimes out did other always this finally during for however had can slowly certainly after actually then anything that first however get after more everything way fully entirely without finally obviously originally they however get said his these has your now too originally they other first who into slowly sometimes although gradually however was was each was how another your will nothing man our normally already during our obviously partly more their generally use without especially the new obviously they then anything particularly after say during basically perhaps said she there definitely</t>
+  </si>
+  <si>
+    <t>each could during because eventually when you man therefore after your another and immediately new normally therefore perhaps finally everyone there out especially while for particularly normally get initially nothing basically put and however man everyone who man this this have and let initially how one are finally mostly between always her some actually mostly had will too are they another there obviously already definitely everything mainly carefully another normally when quickly that your man did you being way not his that after nothing generally definitely way her recently recently immediately recently use initially quickly while initially exactly say slowly</t>
+  </si>
+  <si>
+    <t>some boy really recently boy basically therefore particularly was gradually definitely immediately him and only definitely all fully all always normally did between sometimes you has should should boy one eventually are say first recently generally during had each basically say use recently are and are there usually did recently put many then other can said have partly him had many another while during obviously generally originally into however boy have into other these someone something out has finally should there did before with usually between totally some many can carefully too without day each will been been therefore for</t>
+  </si>
+  <si>
+    <t>said gradually being one something originally recently originally something normally being some the will everything especially perhaps will primarily definitely way fully but how all how see way and certainly basically which gradually before between always with into old was old immediately first been slowly when exactly some immediately when which other our how its out with his each about particularly always perhaps about when after was without however more certainly are although could see them for during finally she when all mostly totally without get had was one definitely for these new however did more actually while many although</t>
+  </si>
+  <si>
+    <t>entirely out will between although totally mostly too use immediately the use anything anything and other with because get basically because get put will put initially first has man she eventually another always sometimes actually all not new have some put entirely some now has they has was something mostly through have your say something actually her put absolutely boy recently said first everyone really use but one day use during new has after more before her fully than when without about the because already primarily gradually exactly everything new them everything was apparently anything other eventually recently would really</t>
   </si>
   <si>
     <t>Note for row 100</t>
   </si>
   <si>
-    <t>Person 101</t>
-  </si>
-  <si>
-    <t>Person 102</t>
-  </si>
-  <si>
-    <t>Person 103</t>
-  </si>
-  <si>
-    <t>Person 104</t>
-  </si>
-  <si>
-    <t>Person 105</t>
+    <t>certainly actually while the immediately way basically who being one usually actually exactly there through basically get fully partly now our slowly not for how eventually boy you her definitely then let only gradually absolutely who another obviously said generally exactly gradually this had are however suddenly slowly absolutely especially being for immediately she totally however new him about mostly use finally all let was our have because when which mainly could mainly his has initially her entirely however nothing which suddenly there usually while many boy fully have being who there then during gradually recently now for our how</t>
+  </si>
+  <si>
+    <t>who something nothing for many apparently apparently man completely and normally with then has quickly old one into each through one suddenly immediately they all use should your than really has its someone slowly have basically immediately see everything for out sometimes everyone normally said carefully although where another her particularly all them really nothing they during between because perhaps him nothing who was through been one him another finally which into use for her how between old absolutely immediately mostly mainly quickly being therefore basically each suddenly now although had actually say man will where especially you and where</t>
+  </si>
+  <si>
+    <t>too obviously let recently old your already said gradually would now day totally all generally normally eventually apparently will nothing fully they been everything immediately during been from immediately that obviously nothing into our after than certainly everyone during too are would she was everyone you let actually fully originally these apparently that mostly basically see definitely always your fully been man nothing particularly after first its mainly another certainly basically said totally you definitely immediately put something can totally anything one especially these had first they usually that that after nothing more can between exactly out not generally his</t>
+  </si>
+  <si>
+    <t>particularly her new have about each get recently your recently should get suddenly each each from nothing there gradually during apparently quickly more boy originally was therefore for see get has day said especially should can basically did certainly completely certainly where old therefore been everything many its exactly have that immediately said its boy then which should however particularly see was your before was with absolutely its anything immediately everything these apparently totally finally new see boy put first him everything not now eventually finally nothing new the fully being have your our see had that his finally first</t>
+  </si>
+  <si>
+    <t>sometimes not should without our and about new put their would the her something they another certainly see during now some have therefore basically exactly eventually perhaps gradually are your totally each them they between too sometimes could actually had quickly did had can during see eventually because when some its primarily out nothing mostly them let absolutely day absolutely its old could therefore obviously sometimes she are your gradually between day however than generally quickly mainly your normally then entirely although while she get where anything actually its about are now nothing been everyone although then for should always</t>
   </si>
   <si>
     <t>Note for row 105</t>
   </si>
   <si>
-    <t>Person 106</t>
-  </si>
-  <si>
-    <t>Person 107</t>
-  </si>
-  <si>
-    <t>Person 108</t>
-  </si>
-  <si>
-    <t>Person 109</t>
-  </si>
-  <si>
-    <t>Person 110</t>
+    <t>and basically our there generally actually because him could said obviously gradually quickly into not use mainly initially are one however when absolutely quickly partly our not definitely basically some more generally suddenly absolutely before get your one apparently that during did absolutely eventually therefore immediately the which use therefore their his day only mainly nothing out some for him did can she not could something day will initially these before because them certainly entirely the would did someone after said entirely normally then completely which not eventually not someone gradually mostly everyone because without suddenly after our totally out</t>
+  </si>
+  <si>
+    <t>had for for she its old obviously where absolutely say will after who old another get about how really already everyone into could generally was has without therefore because without suddenly entirely more let was have him before definitely mostly although immediately definitely out obviously did after for slowly could between completely everything from into these some mainly has from one always suddenly because your apparently mostly now someone normally each them use them and gradually entirely fully fully let obviously for therefore without eventually immediately actually from initially his that between while way always generally certainly immediately through her</t>
+  </si>
+  <si>
+    <t>see anything see she after immediately day during but finally old their absolutely therefore into out during slowly always certainly particularly through another another would absolutely the put can after someone into which carefully obviously finally too entirely could old particularly only and partly that who without someone really another everything normally new without use apparently really perhaps should nothing carefully initially finally then exactly suddenly can although definitely and slowly mainly and entirely our her man which always new anything first generally although without put out when from completely say totally where see there more absolutely with everything more</t>
+  </si>
+  <si>
+    <t>between more actually everything quickly our being but between normally our the apparently although will but all while its everyone gradually another exactly too not particularly said old but only basically from mostly however primarily during boy have see gradually during how could that mostly finally get fully already recently really being other through especially although put another other their completely actually man could something normally absolutely anything suddenly could not another where with immediately between something which and way everyone can with therefore use way more primarily all nothing many through something its but see because immediately primarily quickly</t>
+  </si>
+  <si>
+    <t>for suddenly quickly put which many many her man new initially completely anything there everything partly get her someone now are really did completely their totally slowly some generally without after would apparently for their usually everything for recently each who one another where where therefore someone they from how these will get who really definitely before put more should without more did immediately her new initially definitely all first actually you everything has will her more should our slowly out let first new after boy normally certainly particularly could one other than for initially after completely they sometimes however</t>
   </si>
   <si>
     <t>Note for row 110</t>
   </si>
   <si>
-    <t>Person 111</t>
-  </si>
-  <si>
-    <t>Person 112</t>
-  </si>
-  <si>
-    <t>Person 113</t>
-  </si>
-  <si>
-    <t>Person 114</t>
-  </si>
-  <si>
-    <t>Person 115</t>
+    <t>you recently old through put really which then way where say said that with she their said not primarily would them did absolutely being actually too she initially only they more through into its not therefore totally partly immediately gradually immediately where nothing would more will immediately sometimes gradually originally its already our one immediately before had obviously which man how apparently was partly that where get because mostly being them generally because they before primarily they from especially first other something anything fully should these her them when that get each would immediately sometimes definitely and suddenly could have</t>
+  </si>
+  <si>
+    <t>fully man she where exactly about would during quickly many these now normally get normally said but actually she definitely not this entirely actually get his about can quickly carefully partly how originally originally him because finally which particularly slowly mostly many for before say therefore entirely been immediately say before usually that recently and said before their although was but partly particularly when one would during when while him did really gradually about him during mainly when first mostly way absolutely finally gradually basically however way partly with her which new day are can originally when than sometimes therefore</t>
+  </si>
+  <si>
+    <t>day everything definitely your especially she everyone but now many through your finally for new put not did would one anything sometimes before something him eventually apparently being for someone see apparently that being certainly exactly originally something completely between new mostly anything apparently carefully therefore how have should finally another way say completely partly some man our man could recently about would obviously you your while said originally see all now exactly will after all now would for too while your therefore man been primarily particularly you initially sometimes only now the day that then for first first particularly</t>
+  </si>
+  <si>
+    <t>would when her are before who all get old generally see did many too gradually was she only let fully first obviously although for way how should that his many eventually its they all obviously because get immediately too always how after with been how completely certainly certainly this all therefore already fully for someone been this let anything everyone boy that after especially your already did initially let one mainly have him because have already out you through that perhaps fully something man entirely old did particularly our everyone exactly with you therefore had they man out for new</t>
+  </si>
+  <si>
+    <t>immediately certainly her anything man did exactly one each sometimes usually everything has should one entirely their through has new out other they let his obviously always had the immediately too totally immediately its for each exactly can our recently other although normally let particularly eventually out fully actually actually had therefore would basically out however already you immediately gradually has totally have basically partly the exactly been man get perhaps actually really mostly immediately fully between normally been completely everyone finally their new initially being anything how one would then out normally where way only can their during perhaps</t>
   </si>
   <si>
     <t>Note for row 115</t>
   </si>
   <si>
-    <t>Person 116</t>
-  </si>
-  <si>
-    <t>Person 117</t>
-  </si>
-  <si>
-    <t>Person 118</t>
-  </si>
-  <si>
-    <t>Person 119</t>
-  </si>
-  <si>
-    <t>Person 120</t>
+    <t>way now get quickly should get say obviously immediately suddenly would entirely some perhaps usually although totally have entirely get her certainly you exactly now these boy they nothing many definitely quickly while one everything someone which with who really some this first perhaps how her generally recently originally but how their see recently his they they your originally only and more was our through into who should man are now old carefully however day been initially have the her who especially with many while then them actually how totally day the than use exactly perhaps are being how and</t>
+  </si>
+  <si>
+    <t>gradually many definitely one after exactly him how while many really mostly old will perhaps too especially all about these had particularly other definitely sometimes normally has fully her primarily which that was than only anything first apparently however has his recently than mostly our did from boy our out immediately his especially because their they their get being after gradually did everything should this then has through primarily when she recently carefully their during when before has initially she finally out totally without only therefore had mostly originally usually actually totally many really slowly something absolutely each through eventually</t>
+  </si>
+  <si>
+    <t>had would this your other their only another being and finally slowly day boy there now she before this its way without sometimes each more where the their how partly she especially their initially these basically than certainly had had quickly gradually should she these before definitely its immediately but should without everyone quickly the she and then gradually through have actually generally could who use all could first only totally generally basically partly let his and everyone but then something been been about say mainly between have are another boy completely put out said something the really too man</t>
+  </si>
+  <si>
+    <t>immediately that everyone out normally immediately its someone have put someone mainly another generally particularly should definitely for you sometimes perhaps man put really after way did then already should will into anything man been all initially always should nothing some another between there during without apparently which after have actually normally can through sometimes said with already many its slowly that before everything sometimes mostly recently only during mostly day for our only let really had during the who only everyone basically while old then quickly will gradually through his when man initially man mainly each use more that</t>
+  </si>
+  <si>
+    <t>someone more mainly recently after through them get mainly while someone usually initially really generally about another you who between they would especially basically sometimes did although quickly some but other without into way did with said basically originally when your apparently boy was been primarily day suddenly one primarily you being absolutely particularly completely you basically other use had obviously suddenly eventually basically generally sometimes each too other out entirely put about through are there their let when should mainly definitely perhaps their not already slowly your during therefore who immediately after are obviously everyone not during should all</t>
   </si>
   <si>
     <t>Note for row 120</t>
   </si>
   <si>
-    <t>Person 121</t>
-  </si>
-  <si>
-    <t>Person 122</t>
-  </si>
-  <si>
-    <t>Person 123</t>
-  </si>
-  <si>
-    <t>Person 124</t>
-  </si>
-  <si>
-    <t>Person 125</t>
+    <t>but one than already recently see was use after therefore then actually will always which normally because something can anything into someone before entirely not not other his exactly usually exactly sometimes anything normally with only their and sometimes absolutely have its always especially then everyone had another apparently definitely with slowly said too many completely immediately already obviously certainly another someone was its especially immediately definitely therefore before which our which apparently way only will finally partly the its who our perhaps obviously said him its sometimes has suddenly totally before while particularly say another mainly boy although each</t>
+  </si>
+  <si>
+    <t>certainly her said boy being how because each your and during she too nothing this completely normally did while each should should they usually therefore basically entirely then other gradually other only normally its about their have her these absolutely too exactly she put one day partly eventually will than old for suddenly initially partly when each many did could while his them should see first them man something particularly their anything for basically could old before absolutely before while put totally not immediately been each especially because perhaps for our these absolutely immediately although how perhaps did already boy</t>
+  </si>
+  <si>
+    <t>other recently too exactly can how more only finally should totally these should are for apparently are had fully about while that him completely immediately about more into how apparently their into his could only new suddenly many there actually nothing one exactly through quickly you she obviously see let totally sometimes see finally during into obviously anything have him however because out new although entirely exactly through let which obviously between said obviously would old certainly said primarily but man let some mostly first out everything while you certainly our who sometimes its really will said too see now</t>
+  </si>
+  <si>
+    <t>something your say new these quickly about recently about while first partly slowly generally fully man our boy that carefully for especially always which after partly mainly how after before particularly although had with will someone through could first his then him his let how partly someone between slowly therefore which usually perhaps gradually basically other from being that because basically your did anything than primarily actually generally fully her your day generally after man say carefully because how their fully perhaps someone have out entirely normally nothing definitely put her man you see eventually normally usually more that him</t>
+  </si>
+  <si>
+    <t>partly quickly everything one that everything suddenly other immediately old day first obviously how through although especially then through because gradually into where another primarily way who which they nothing them did she really nothing definitely say there she said nothing certainly therefore boy way his between your between after our all sometimes was first his first can through their them basically finally always therefore there which old which without something all finally immediately nothing gradually its someone only normally and would anything boy who first quickly could many with but after man mainly put old quickly usually fully carefully</t>
   </si>
   <si>
     <t>Note for row 125</t>
   </si>
   <si>
-    <t>Person 126</t>
-  </si>
-  <si>
-    <t>Person 127</t>
-  </si>
-  <si>
-    <t>Person 128</t>
-  </si>
-  <si>
-    <t>Person 129</t>
-  </si>
-  <si>
-    <t>Person 130</t>
+    <t>them from anything especially had are use all because way about perhaps was slowly them with another too with has everything carefully all them has you been although way she not immediately they immediately not other with who sometimes old mostly when the carefully being but could his slowly absolutely old anything anything but originally although mostly through day its new let too initially especially each this partly where they did already into finally has will nothing for obviously immediately partly eventually generally especially have someone you too generally after these are initially one after for have way then their</t>
+  </si>
+  <si>
+    <t>get suddenly each recently with who therefore into all put from usually especially someone primarily all all will through everything because being because usually should particularly entirely another you carefully one because all but see then however his nothing there let eventually where day fully only definitely some can have some particularly gradually obviously that nothing see definitely but say immediately first which between for mostly your his normally although before they exactly this fully each many usually originally now did when initially they more man her mostly definitely normally its because way nothing through than where perhaps entirely this</t>
+  </si>
+  <si>
+    <t>get especially although out would nothing quickly him something where everything out immediately our fully other definitely completely they basically slowly your said therefore but did immediately you gradually see everyone after her actually before someone you some get all between these many everyone already normally when partly some that normally finally our use usually man only the than said about usually the day actually fully your sometimes this however him something her let mostly apparently recently not finally primarily absolutely another that between could and said mostly the everything can who said could him quickly each more one the</t>
+  </si>
+  <si>
+    <t>quickly them into some more eventually mainly recently generally immediately let particularly this quickly your without before because have where its some before has was that slowly definitely however their apparently gradually that put say before originally certainly anything this carefully nothing old fully generally usually where between totally generally gradually another out carefully perhaps into out someone gradually but actually have could now her basically perhaps would more could through about really now their she she although boy his say that how was without carefully our being was old boy after boy already when your too for him she</t>
+  </si>
+  <si>
+    <t>something was they already should they this our how generally where many has let something particularly sometimes your way their there his someone him perhaps into that where this gradually way how from eventually already basically with them carefully mostly always mainly had day have certainly let because get already would its there now about boy immediately when that these however being before her immediately her get each this mainly first too has carefully how only before totally always will her use totally our your could but nothing many something not let therefore between one many generally each when eventually</t>
   </si>
   <si>
     <t>Note for row 130</t>
   </si>
   <si>
-    <t>Person 131</t>
-  </si>
-  <si>
-    <t>Person 132</t>
-  </si>
-  <si>
-    <t>Person 133</t>
-  </si>
-  <si>
-    <t>Person 134</t>
-  </si>
-  <si>
-    <t>Person 135</t>
+    <t>initially too always put immediately sometimes usually our some only where first however certainly use all she certainly him gradually where eventually for recently primarily there while are something one gradually always can where without totally for normally for mostly into immediately into another between entirely you did have than recently more normally our you actually everything recently put there day perhaps about use suddenly day mostly way carefully which where especially are being someone sometimes would some originally particularly them especially always who was gradually carefully immediately sometimes exactly first man apparently should would recently everyone first mainly after</t>
+  </si>
+  <si>
+    <t>everything new could everyone through primarily but partly which without slowly entirely can said about been these everyone say there day first your where however then because can was out for normally while quickly particularly eventually when generally say when their put then actually your way always will should finally something finally slowly will entirely although said really not see certainly some quickly are one and too they said immediately being who more put boy boy during now then was quickly really primarily while each them how could the man something day have other another day something through exactly suddenly</t>
+  </si>
+  <si>
+    <t>has completely another always your there into out during should while fully have totally put him fully been did partly mainly through after all first mostly although for something while generally carefully her are finally them this where during but could quickly then totally fully way more your because who get there which did more absolutely and into generally let should between had would then from then out when day therefore therefore now however however partly let was could especially really totally day can certainly had totally originally carefully said immediately old which other way old and therefore after exactly</t>
+  </si>
+  <si>
+    <t>anything finally because while definitely usually actually actually everyone not she too suddenly your sometimes put old perhaps after your everyone out however carefully only immediately everything then eventually exactly exactly from particularly really into certainly normally them without that could someone each definitely man after see mainly which another absolutely absolutely fully old between usually especially through absolutely his always their their through totally already obviously see the actually which are through see into really more see from their from then too after however finally first one nothing apparently anything the perhaps suddenly certainly man always before which entirely</t>
+  </si>
+  <si>
+    <t>suddenly who during immediately basically which each could immediately recently really immediately that say absolutely apparently who see this especially but after suddenly some his old too before has especially being everyone only during basically really can basically after with about man his day day many initially through after too entirely say totally out each without slowly sometimes are when perhaps him have finally gradually during perhaps into already have our really her how mostly him already something anything suddenly can from another was about only when our really man his are mainly nothing many his other and first get</t>
   </si>
   <si>
     <t>Note for row 135</t>
   </si>
   <si>
-    <t>Person 136</t>
-  </si>
-  <si>
-    <t>Person 137</t>
-  </si>
-  <si>
-    <t>Person 138</t>
-  </si>
-  <si>
-    <t>Person 139</t>
-  </si>
-  <si>
-    <t>Person 140</t>
+    <t>anything certainly said each more say too quickly everything man immediately anything especially there there have partly suddenly was because another old has her perhaps who especially them nothing although during many this slowly your about primarily day she too boy exactly new finally the already between her could its been than each boy totally when recently totally completely being his more first after with basically already their than old who say someone first put your only quickly only new the will definitely really more everything some are through can definitely you although always will nothing some get before during</t>
+  </si>
+  <si>
+    <t>normally normally they before see could than all had through quickly obviously between this when you because entirely too mostly said although everything then definitely being our the other can really slowly first obviously totally however really for partly who mainly some other its especially day someone these see slowly definitely generally him let could about more absolutely perhaps would usually primarily after his originally her when had when especially said can without this was has now perhaps really already always always nothing normally day another man him new then partly say but our all slowly perhaps out for you</t>
+  </si>
+  <si>
+    <t>immediately nothing quickly only immediately had finally our suddenly everyone someone let had said gradually normally than your usually than new how have fully them which see how being some have put actually been than exactly let some him its and have let something use primarily there always but only anything say therefore when primarily another partly exactly originally there partly its really your entirely immediately that normally another something their have who particularly recently said them her new already into recently these therefore already someone the basically finally has its not completely totally are all would boy completely during</t>
+  </si>
+  <si>
+    <t>each usually definitely nothing although out sometimes usually although gradually would she has finally put actually the new primarily primarily can basically when would has therefore someone quickly another eventually entirely especially everything recently the than through which entirely get only out usually without has someone everyone actually was exactly really has then when eventually have our old him fully many will therefore was let quickly before definitely new put mainly when into something old put about basically more for but many many totally many after some should after immediately sometimes put originally another its sometimes more see man was</t>
+  </si>
+  <si>
+    <t>everyone your especially our day exactly could use said finally however something from especially generally another during because through while that said which can there where had not with originally another definitely generally many their everything our many slowly therefore into more actually say carefully can these old mostly recently you other therefore now something actually another use everyone the originally totally because mostly however say actually new certainly get she man actually absolutely its are with nothing too something then new put have use which did let with perhaps use mostly someone how should exactly more already had nothing</t>
   </si>
   <si>
     <t>Note for row 140</t>
   </si>
   <si>
-    <t>Person 141</t>
-  </si>
-  <si>
-    <t>Person 142</t>
-  </si>
-  <si>
-    <t>Person 143</t>
-  </si>
-  <si>
-    <t>Person 144</t>
-  </si>
-  <si>
-    <t>Person 145</t>
+    <t>finally way which although let put said some really new recently only particularly mainly said had can initially say use mostly obviously primarily into than say than exactly already now really already which totally quickly see generally too nothing anything there say boy however get who slowly too mainly actually use was mainly now all now has how all immediately first another originally between perhaps should her entirely especially quickly before which these while some new mostly out mostly completely day for about has quickly certainly other was anything more each could had when between totally then your although especially</t>
+  </si>
+  <si>
+    <t>recently then normally someone has before old said absolutely actually where already recently should old recently there his there day mainly they its particularly some would more have and use initially primarily have entirely especially therefore but perhaps our should his totally after therefore his suddenly about suddenly has which been his has into too completely certainly someone something first carefully there then already his for exactly this would now she mainly during his when nothing initially exactly only entirely really some entirely eventually apparently our let initially who carefully primarily had during then where for especially fully use for</t>
+  </si>
+  <si>
+    <t>someone initially mainly into they than new than man everyone for who was basically carefully during new man did being could the while during one our these while with first day that carefully but how although each let apparently first through been immediately old absolutely out had had there being our although apparently finally through while their only who are definitely suddenly where totally you could let gradually although mostly certainly apparently use because about more definitely certainly way one mostly slowly old suddenly then through only which some too eventually originally her completely how anything other obviously generally our</t>
+  </si>
+  <si>
+    <t>now has totally way their another let initially before however entirely finally old see this these exactly really use these there everyone perhaps suddenly slowly partly before day before way said have more slowly being will too would sometimes something already many then each after that are between new new man absolutely that totally only out already day our entirely and through from someone some not then old one out definitely day they originally absolutely which into perhaps carefully its old when let carefully the eventually many there which boy however anything partly without these basically particularly partly she particularly</t>
+  </si>
+  <si>
+    <t>way that out finally slowly had should without always her boy will way finally perhaps immediately immediately him too been mainly use them man eventually who man mainly you and originally then now way carefully said nothing already will then how nothing eventually had can from has apparently the really between these their are where say there recently basically after new normally fully when these see now without its eventually something everything some with suddenly between eventually normally had had she exactly too quickly another completely sometimes definitely suddenly fully particularly and initially actually how have some out then being</t>
   </si>
   <si>
     <t>Note for row 145</t>
   </si>
   <si>
-    <t>Person 146</t>
-  </si>
-  <si>
-    <t>Person 147</t>
-  </si>
-  <si>
-    <t>Person 148</t>
-  </si>
-  <si>
-    <t>Person 149</t>
-  </si>
-  <si>
-    <t>Person 150</t>
+    <t>get not more before finally from there everything have into totally really during between day carefully her old being are they say could slowly should each its everything old but get however suddenly can entirely immediately for and get particularly when while have mainly because without that with recently the everyone basically out been with see originally perhaps said one old when mainly usually certainly anything boy absolutely especially another could let finally are anything where usually everyone can than from put use for can many exactly your new everyone certainly recently slowly with without through nothing its fully day</t>
+  </si>
+  <si>
+    <t>their will many see during through everyone for could many get first sometimes was not her suddenly sometimes finally certainly because new there you new get finally not without are mainly boy exactly normally about where however boy have primarily after been exactly each him obviously who said usually for totally how has how between totally first are therefore should day initially let put should mostly now should that there say would quickly not each while fully say into this about she especially during usually are its mostly normally especially then although new man when slowly many into some first</t>
+  </si>
+  <si>
+    <t>although everything recently old usually her have has already generally really where they already our particularly partly than usually from basically definitely use some more anything something can other his how too being would she one entirely however without said eventually after first during you certainly finally basically their first first normally carefully these slowly however each generally with her another apparently normally because finally mostly definitely this obviously between way into someone when our see obviously one man had totally partly eventually with say you partly being which immediately another see then let and she only one finally our</t>
+  </si>
+  <si>
+    <t>who has our our have totally being the boy see see particularly when for immediately therefore really originally because many originally normally for everyone which said which carefully normally into them she said without anything mostly actually everything initially before entirely more generally one only they with all about nothing finally too all actually certainly everyone because immediately their out something only however immediately originally can his all definitely another because finally let see while one immediately who its only but are say being actually sometimes however was then finally something finally first these too into primarily them other sometimes</t>
+  </si>
+  <si>
+    <t>generally absolutely you mostly put have through carefully our they completely their she her who would get without has especially immediately they everyone gradually during said old boy with usually out boy obviously everyone eventually see old him slowly been mainly one with originally before she her completely someone normally than man suddenly mainly had this day now originally let always and can said use generally for said them about her did they perhaps immediately these originally slowly basically the usually who finally initially old she who who out usually him obviously immediately say now you fully him than initially</t>
   </si>
   <si>
     <t>Note for row 150</t>
@@ -1023,7 +1023,7 @@
         <v>8</v>
       </c>
       <c r="E2" s="2">
-        <v>45939.083750590275</v>
+        <v>45143.102791412035</v>
       </c>
       <c r="F2" t="s">
         <v>9</v>
@@ -1043,7 +1043,7 @@
         <v>12</v>
       </c>
       <c r="E3" s="2">
-        <v>45829.5362181713</v>
+        <v>45697.760646967596</v>
       </c>
       <c r="F3" t="s">
         <v>9</v>
@@ -1060,10 +1060,10 @@
         <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E4" s="2">
-        <v>45921.96363547454</v>
+        <v>45821.44162861111</v>
       </c>
       <c r="F4" t="s">
         <v>9</v>
@@ -1074,16 +1074,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D5" t="s">
         <v>8</v>
       </c>
       <c r="E5" s="2">
-        <v>45033.412505995366</v>
+        <v>45057.88314319444</v>
       </c>
       <c r="F5" t="s">
         <v>9</v>
@@ -1094,19 +1094,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D6" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E6" s="2">
-        <v>45807.57715287037</v>
+        <v>45122.707466747685</v>
       </c>
       <c r="F6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -1114,16 +1114,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D7" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E7" s="2">
-        <v>45529.72817240741</v>
+        <v>45193.430932627314</v>
       </c>
       <c r="F7" t="s">
         <v>9</v>
@@ -1134,16 +1134,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C8" t="s">
         <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E8" s="2">
-        <v>45408.41613724537</v>
+        <v>46009.90825703704</v>
       </c>
       <c r="F8" t="s">
         <v>9</v>
@@ -1154,16 +1154,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" t="s">
         <v>22</v>
       </c>
-      <c r="C9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" t="s">
-        <v>17</v>
-      </c>
       <c r="E9" s="2">
-        <v>44944.57901752315</v>
+        <v>45878.77666171297</v>
       </c>
       <c r="F9" t="s">
         <v>9</v>
@@ -1174,16 +1174,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D10" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="E10" s="2">
-        <v>45253.5794340162</v>
+        <v>45076.42203559028</v>
       </c>
       <c r="F10" t="s">
         <v>9</v>
@@ -1194,19 +1194,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="D11" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E11" s="2">
-        <v>45506.07808561342</v>
+        <v>45138.48773146991</v>
       </c>
       <c r="F11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -1214,16 +1214,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E12" s="2">
-        <v>45185.829828773145</v>
+        <v>45679.28192152778</v>
       </c>
       <c r="F12" t="s">
         <v>9</v>
@@ -1234,16 +1234,16 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C13" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D13" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E13" s="2">
-        <v>45742.51713359954</v>
+        <v>45144.16939466435</v>
       </c>
       <c r="F13" t="s">
         <v>9</v>
@@ -1254,16 +1254,16 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C14" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D14" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E14" s="2">
-        <v>45632.12799172454</v>
+        <v>45078.7568859375</v>
       </c>
       <c r="F14" t="s">
         <v>9</v>
@@ -1274,16 +1274,16 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C15" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D15" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="E15" s="2">
-        <v>45683.202009988425</v>
+        <v>45696.449137476855</v>
       </c>
       <c r="F15" t="s">
         <v>9</v>
@@ -1297,16 +1297,16 @@
         <v>33</v>
       </c>
       <c r="C16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16" t="s">
+        <v>15</v>
+      </c>
+      <c r="E16" s="2">
+        <v>45744.10516129629</v>
+      </c>
+      <c r="F16" t="s">
         <v>34</v>
-      </c>
-      <c r="D16" t="s">
-        <v>32</v>
-      </c>
-      <c r="E16" s="2">
-        <v>45299.60556225694</v>
-      </c>
-      <c r="F16" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1314,16 +1314,16 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C17" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D17" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="E17" s="2">
-        <v>45569.54600606482</v>
+        <v>45151.89314263889</v>
       </c>
       <c r="F17" t="s">
         <v>9</v>
@@ -1334,16 +1334,16 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D18" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E18" s="2">
-        <v>45648.98475217592</v>
+        <v>45671.01203032407</v>
       </c>
       <c r="F18" t="s">
         <v>9</v>
@@ -1354,16 +1354,16 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C19" t="s">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="D19" t="s">
         <v>8</v>
       </c>
       <c r="E19" s="2">
-        <v>45652.482431909724</v>
+        <v>45304.27519170139</v>
       </c>
       <c r="F19" t="s">
         <v>9</v>
@@ -1374,16 +1374,16 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C20" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D20" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="E20" s="2">
-        <v>45672.585999456016</v>
+        <v>45719.76739822917</v>
       </c>
       <c r="F20" t="s">
         <v>9</v>
@@ -1394,19 +1394,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" t="s">
+        <v>21</v>
+      </c>
+      <c r="D21" t="s">
+        <v>15</v>
+      </c>
+      <c r="E21" s="2">
+        <v>44946.65370927083</v>
+      </c>
+      <c r="F21" t="s">
         <v>40</v>
-      </c>
-      <c r="C21" t="s">
-        <v>11</v>
-      </c>
-      <c r="D21" t="s">
-        <v>20</v>
-      </c>
-      <c r="E21" s="2">
-        <v>45200.90845528935</v>
-      </c>
-      <c r="F21" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1414,16 +1414,16 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C22" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D22" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="E22" s="2">
-        <v>45569.973434722226</v>
+        <v>45664.791974085645</v>
       </c>
       <c r="F22" t="s">
         <v>9</v>
@@ -1434,16 +1434,16 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C23" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="D23" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E23" s="2">
-        <v>45078.2014646412</v>
+        <v>45962.12483390047</v>
       </c>
       <c r="F23" t="s">
         <v>9</v>
@@ -1454,16 +1454,16 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C24" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="D24" t="s">
         <v>12</v>
       </c>
       <c r="E24" s="2">
-        <v>45768.75126085649</v>
+        <v>45598.033099548615</v>
       </c>
       <c r="F24" t="s">
         <v>9</v>
@@ -1474,16 +1474,16 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
+        <v>44</v>
+      </c>
+      <c r="C25" t="s">
         <v>45</v>
       </c>
-      <c r="C25" t="s">
-        <v>14</v>
-      </c>
       <c r="D25" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E25" s="2">
-        <v>45703.34899111111</v>
+        <v>45478.49549498843</v>
       </c>
       <c r="F25" t="s">
         <v>9</v>
@@ -1497,13 +1497,13 @@
         <v>46</v>
       </c>
       <c r="C26" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D26" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="E26" s="2">
-        <v>45275.87452703704</v>
+        <v>45202.230008391205</v>
       </c>
       <c r="F26" t="s">
         <v>47</v>
@@ -1517,13 +1517,13 @@
         <v>48</v>
       </c>
       <c r="C27" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="D27" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="E27" s="2">
-        <v>45917.18606734954</v>
+        <v>45618.37576520833</v>
       </c>
       <c r="F27" t="s">
         <v>9</v>
@@ -1537,13 +1537,13 @@
         <v>49</v>
       </c>
       <c r="C28" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D28" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E28" s="2">
-        <v>45853.9583309838</v>
+        <v>45977.138562002314</v>
       </c>
       <c r="F28" t="s">
         <v>9</v>
@@ -1557,13 +1557,13 @@
         <v>50</v>
       </c>
       <c r="C29" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D29" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E29" s="2">
-        <v>45407.663202881944</v>
+        <v>45815.97288748843</v>
       </c>
       <c r="F29" t="s">
         <v>9</v>
@@ -1577,13 +1577,13 @@
         <v>51</v>
       </c>
       <c r="C30" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D30" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="E30" s="2">
-        <v>45966.33900108797</v>
+        <v>45660.64593579861</v>
       </c>
       <c r="F30" t="s">
         <v>9</v>
@@ -1597,13 +1597,13 @@
         <v>52</v>
       </c>
       <c r="C31" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D31" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E31" s="2">
-        <v>45796.18942736111</v>
+        <v>45880.354467268524</v>
       </c>
       <c r="F31" t="s">
         <v>53</v>
@@ -1617,13 +1617,13 @@
         <v>54</v>
       </c>
       <c r="C32" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="D32" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="E32" s="2">
-        <v>45122.4601669213</v>
+        <v>45685.21020480324</v>
       </c>
       <c r="F32" t="s">
         <v>9</v>
@@ -1637,13 +1637,13 @@
         <v>55</v>
       </c>
       <c r="C33" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D33" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="E33" s="2">
-        <v>45309.21560297454</v>
+        <v>45612.37371875</v>
       </c>
       <c r="F33" t="s">
         <v>9</v>
@@ -1657,13 +1657,13 @@
         <v>56</v>
       </c>
       <c r="C34" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="D34" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E34" s="2">
-        <v>45296.6208025</v>
+        <v>45494.31045087963</v>
       </c>
       <c r="F34" t="s">
         <v>9</v>
@@ -1680,10 +1680,10 @@
         <v>11</v>
       </c>
       <c r="D35" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E35" s="2">
-        <v>45005.716161261575</v>
+        <v>45060.568756608795</v>
       </c>
       <c r="F35" t="s">
         <v>9</v>
@@ -1697,13 +1697,13 @@
         <v>58</v>
       </c>
       <c r="C36" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D36" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E36" s="2">
-        <v>45987.79329706018</v>
+        <v>45661.90853741898</v>
       </c>
       <c r="F36" t="s">
         <v>59</v>
@@ -1717,13 +1717,13 @@
         <v>60</v>
       </c>
       <c r="C37" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="D37" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="E37" s="2">
-        <v>45105.44400030092</v>
+        <v>45534.27098417824</v>
       </c>
       <c r="F37" t="s">
         <v>9</v>
@@ -1737,13 +1737,13 @@
         <v>61</v>
       </c>
       <c r="C38" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="D38" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E38" s="2">
-        <v>45580.57925795139</v>
+        <v>45506.75747222222</v>
       </c>
       <c r="F38" t="s">
         <v>9</v>
@@ -1757,13 +1757,13 @@
         <v>62</v>
       </c>
       <c r="C39" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D39" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E39" s="2">
-        <v>45598.92317759259</v>
+        <v>46021.89227866898</v>
       </c>
       <c r="F39" t="s">
         <v>9</v>
@@ -1777,13 +1777,13 @@
         <v>63</v>
       </c>
       <c r="C40" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="D40" t="s">
         <v>12</v>
       </c>
       <c r="E40" s="2">
-        <v>45853.977445439814</v>
+        <v>45022.056310960645</v>
       </c>
       <c r="F40" t="s">
         <v>9</v>
@@ -1797,13 +1797,13 @@
         <v>64</v>
       </c>
       <c r="C41" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D41" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E41" s="2">
-        <v>45950.02866524305</v>
+        <v>45680.0072115625</v>
       </c>
       <c r="F41" t="s">
         <v>65</v>
@@ -1817,13 +1817,13 @@
         <v>66</v>
       </c>
       <c r="C42" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="D42" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E42" s="2">
-        <v>45447.725218113424</v>
+        <v>45946.32523164352</v>
       </c>
       <c r="F42" t="s">
         <v>9</v>
@@ -1837,13 +1837,13 @@
         <v>67</v>
       </c>
       <c r="C43" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D43" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E43" s="2">
-        <v>45294.393678796296</v>
+        <v>45973.52818863426</v>
       </c>
       <c r="F43" t="s">
         <v>9</v>
@@ -1857,13 +1857,13 @@
         <v>68</v>
       </c>
       <c r="C44" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="D44" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="E44" s="2">
-        <v>45907.77696243055</v>
+        <v>45982.669965497684</v>
       </c>
       <c r="F44" t="s">
         <v>9</v>
@@ -1877,13 +1877,13 @@
         <v>69</v>
       </c>
       <c r="C45" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D45" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E45" s="2">
-        <v>45946.370073240745</v>
+        <v>45207.11188556713</v>
       </c>
       <c r="F45" t="s">
         <v>9</v>
@@ -1900,10 +1900,10 @@
         <v>11</v>
       </c>
       <c r="D46" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E46" s="2">
-        <v>45787.079176342595</v>
+        <v>45291.52353407408</v>
       </c>
       <c r="F46" t="s">
         <v>71</v>
@@ -1917,13 +1917,13 @@
         <v>72</v>
       </c>
       <c r="C47" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="D47" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E47" s="2">
-        <v>45499.78260180556</v>
+        <v>45613.24155820602</v>
       </c>
       <c r="F47" t="s">
         <v>9</v>
@@ -1937,13 +1937,13 @@
         <v>73</v>
       </c>
       <c r="C48" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="D48" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E48" s="2">
-        <v>45620.68991914352</v>
+        <v>45425.96323892361</v>
       </c>
       <c r="F48" t="s">
         <v>9</v>
@@ -1960,10 +1960,10 @@
         <v>11</v>
       </c>
       <c r="D49" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E49" s="2">
-        <v>45270.473216620376</v>
+        <v>45990.90592821759</v>
       </c>
       <c r="F49" t="s">
         <v>9</v>
@@ -1977,13 +1977,13 @@
         <v>75</v>
       </c>
       <c r="C50" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D50" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E50" s="2">
-        <v>44954.372456400466</v>
+        <v>45049.124113784725</v>
       </c>
       <c r="F50" t="s">
         <v>9</v>
@@ -1997,13 +1997,13 @@
         <v>76</v>
       </c>
       <c r="C51" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D51" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E51" s="2">
-        <v>44976.946986967596</v>
+        <v>45941.83024940972</v>
       </c>
       <c r="F51" t="s">
         <v>77</v>
@@ -2017,13 +2017,13 @@
         <v>78</v>
       </c>
       <c r="C52" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D52" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="E52" s="2">
-        <v>45260.69861204861</v>
+        <v>44983.69295790509</v>
       </c>
       <c r="F52" t="s">
         <v>9</v>
@@ -2040,10 +2040,10 @@
         <v>11</v>
       </c>
       <c r="D53" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E53" s="2">
-        <v>45683.94826337963</v>
+        <v>45135.63467547453</v>
       </c>
       <c r="F53" t="s">
         <v>9</v>
@@ -2057,13 +2057,13 @@
         <v>80</v>
       </c>
       <c r="C54" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D54" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E54" s="2">
-        <v>45480.6386153125</v>
+        <v>45563.86546690972</v>
       </c>
       <c r="F54" t="s">
         <v>9</v>
@@ -2077,13 +2077,13 @@
         <v>81</v>
       </c>
       <c r="C55" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D55" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E55" s="2">
-        <v>45708.50443408565</v>
+        <v>45020.3392925463</v>
       </c>
       <c r="F55" t="s">
         <v>9</v>
@@ -2097,13 +2097,13 @@
         <v>82</v>
       </c>
       <c r="C56" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="D56" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="E56" s="2">
-        <v>45096.415314224534</v>
+        <v>45116.560534097225</v>
       </c>
       <c r="F56" t="s">
         <v>83</v>
@@ -2117,13 +2117,13 @@
         <v>84</v>
       </c>
       <c r="C57" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="D57" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E57" s="2">
-        <v>45257.15166732639</v>
+        <v>45715.693400324075</v>
       </c>
       <c r="F57" t="s">
         <v>9</v>
@@ -2137,13 +2137,13 @@
         <v>85</v>
       </c>
       <c r="C58" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D58" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E58" s="2">
-        <v>44970.072751921296</v>
+        <v>45462.207752511575</v>
       </c>
       <c r="F58" t="s">
         <v>9</v>
@@ -2157,13 +2157,13 @@
         <v>86</v>
       </c>
       <c r="C59" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D59" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="E59" s="2">
-        <v>44936.56051846065</v>
+        <v>45442.94714199074</v>
       </c>
       <c r="F59" t="s">
         <v>9</v>
@@ -2177,13 +2177,13 @@
         <v>87</v>
       </c>
       <c r="C60" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="D60" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E60" s="2">
-        <v>45925.30483523148</v>
+        <v>45917.88822875</v>
       </c>
       <c r="F60" t="s">
         <v>9</v>
@@ -2197,13 +2197,13 @@
         <v>88</v>
       </c>
       <c r="C61" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D61" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E61" s="2">
-        <v>45431.825204340275</v>
+        <v>45660.3972925</v>
       </c>
       <c r="F61" t="s">
         <v>89</v>
@@ -2217,13 +2217,13 @@
         <v>90</v>
       </c>
       <c r="C62" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D62" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="E62" s="2">
-        <v>45432.584459074074</v>
+        <v>45244.33806231481</v>
       </c>
       <c r="F62" t="s">
         <v>9</v>
@@ -2237,13 +2237,13 @@
         <v>91</v>
       </c>
       <c r="C63" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="D63" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="E63" s="2">
-        <v>45649.1409677662</v>
+        <v>45293.99625136574</v>
       </c>
       <c r="F63" t="s">
         <v>9</v>
@@ -2257,13 +2257,13 @@
         <v>92</v>
       </c>
       <c r="C64" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D64" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E64" s="2">
-        <v>45120.495342372684</v>
+        <v>45739.185270104164</v>
       </c>
       <c r="F64" t="s">
         <v>9</v>
@@ -2277,13 +2277,13 @@
         <v>93</v>
       </c>
       <c r="C65" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="D65" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E65" s="2">
-        <v>45315.787233518524</v>
+        <v>45452.03619690972</v>
       </c>
       <c r="F65" t="s">
         <v>9</v>
@@ -2297,13 +2297,13 @@
         <v>94</v>
       </c>
       <c r="C66" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="D66" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="E66" s="2">
-        <v>45756.218865</v>
+        <v>45802.069729930554</v>
       </c>
       <c r="F66" t="s">
         <v>95</v>
@@ -2317,13 +2317,13 @@
         <v>96</v>
       </c>
       <c r="C67" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D67" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="E67" s="2">
-        <v>45125.04075400463</v>
+        <v>45587.77622542824</v>
       </c>
       <c r="F67" t="s">
         <v>9</v>
@@ -2337,13 +2337,13 @@
         <v>97</v>
       </c>
       <c r="C68" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="D68" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E68" s="2">
-        <v>45174.500609675924</v>
+        <v>44976.783875196765</v>
       </c>
       <c r="F68" t="s">
         <v>9</v>
@@ -2357,13 +2357,13 @@
         <v>98</v>
       </c>
       <c r="C69" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D69" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E69" s="2">
-        <v>45537.97465888889</v>
+        <v>45102.417371620366</v>
       </c>
       <c r="F69" t="s">
         <v>9</v>
@@ -2377,13 +2377,13 @@
         <v>99</v>
       </c>
       <c r="C70" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D70" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E70" s="2">
-        <v>45008.1236084375</v>
+        <v>45816.34622247685</v>
       </c>
       <c r="F70" t="s">
         <v>9</v>
@@ -2397,13 +2397,13 @@
         <v>100</v>
       </c>
       <c r="C71" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="D71" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="E71" s="2">
-        <v>45577.340428055555</v>
+        <v>45128.61241459491</v>
       </c>
       <c r="F71" t="s">
         <v>101</v>
@@ -2417,13 +2417,13 @@
         <v>102</v>
       </c>
       <c r="C72" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="D72" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E72" s="2">
-        <v>45989.8054927662</v>
+        <v>45362.548487465276</v>
       </c>
       <c r="F72" t="s">
         <v>9</v>
@@ -2437,13 +2437,13 @@
         <v>103</v>
       </c>
       <c r="C73" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="D73" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="E73" s="2">
-        <v>45620.44676813658</v>
+        <v>45185.82872722222</v>
       </c>
       <c r="F73" t="s">
         <v>9</v>
@@ -2460,10 +2460,10 @@
         <v>7</v>
       </c>
       <c r="D74" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="E74" s="2">
-        <v>45434.01956447917</v>
+        <v>45783.604509502315</v>
       </c>
       <c r="F74" t="s">
         <v>9</v>
@@ -2477,13 +2477,13 @@
         <v>105</v>
       </c>
       <c r="C75" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="D75" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E75" s="2">
-        <v>45230.40996358797</v>
+        <v>45679.71418309028</v>
       </c>
       <c r="F75" t="s">
         <v>9</v>
@@ -2497,13 +2497,13 @@
         <v>106</v>
       </c>
       <c r="C76" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="D76" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E76" s="2">
-        <v>44988.18069271991</v>
+        <v>45737.10757591436</v>
       </c>
       <c r="F76" t="s">
         <v>107</v>
@@ -2517,13 +2517,13 @@
         <v>108</v>
       </c>
       <c r="C77" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D77" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E77" s="2">
-        <v>45594.3411287037</v>
+        <v>45531.011194328705</v>
       </c>
       <c r="F77" t="s">
         <v>9</v>
@@ -2537,13 +2537,13 @@
         <v>109</v>
       </c>
       <c r="C78" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D78" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E78" s="2">
-        <v>45884.97167068287</v>
+        <v>45865.47856950232</v>
       </c>
       <c r="F78" t="s">
         <v>9</v>
@@ -2557,13 +2557,13 @@
         <v>110</v>
       </c>
       <c r="C79" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D79" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E79" s="2">
-        <v>45550.55580299768</v>
+        <v>45991.24701575231</v>
       </c>
       <c r="F79" t="s">
         <v>9</v>
@@ -2577,13 +2577,13 @@
         <v>111</v>
       </c>
       <c r="C80" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="D80" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="E80" s="2">
-        <v>45645.67921778935</v>
+        <v>45494.81253793981</v>
       </c>
       <c r="F80" t="s">
         <v>9</v>
@@ -2597,13 +2597,13 @@
         <v>112</v>
       </c>
       <c r="C81" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="D81" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="E81" s="2">
-        <v>45896.385059409724</v>
+        <v>45018.91857383102</v>
       </c>
       <c r="F81" t="s">
         <v>113</v>
@@ -2617,13 +2617,13 @@
         <v>114</v>
       </c>
       <c r="C82" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D82" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E82" s="2">
-        <v>45599.25219171296</v>
+        <v>45195.333881805556</v>
       </c>
       <c r="F82" t="s">
         <v>9</v>
@@ -2637,13 +2637,13 @@
         <v>115</v>
       </c>
       <c r="C83" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D83" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E83" s="2">
-        <v>45833.8377603125</v>
+        <v>45144.2159972338</v>
       </c>
       <c r="F83" t="s">
         <v>9</v>
@@ -2657,13 +2657,13 @@
         <v>116</v>
       </c>
       <c r="C84" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="D84" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E84" s="2">
-        <v>45977.02372386574</v>
+        <v>45541.17612150463</v>
       </c>
       <c r="F84" t="s">
         <v>9</v>
@@ -2677,13 +2677,13 @@
         <v>117</v>
       </c>
       <c r="C85" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="D85" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="E85" s="2">
-        <v>45469.1178939699</v>
+        <v>45921.00710207176</v>
       </c>
       <c r="F85" t="s">
         <v>9</v>
@@ -2700,10 +2700,10 @@
         <v>7</v>
       </c>
       <c r="D86" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E86" s="2">
-        <v>45049.45702806713</v>
+        <v>45781.68917100695</v>
       </c>
       <c r="F86" t="s">
         <v>119</v>
@@ -2717,13 +2717,13 @@
         <v>120</v>
       </c>
       <c r="C87" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="D87" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E87" s="2">
-        <v>45664.00196659722</v>
+        <v>45605.27464834491</v>
       </c>
       <c r="F87" t="s">
         <v>9</v>
@@ -2737,13 +2737,13 @@
         <v>121</v>
       </c>
       <c r="C88" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="D88" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E88" s="2">
-        <v>45537.84134672454</v>
+        <v>45806.6847171875</v>
       </c>
       <c r="F88" t="s">
         <v>9</v>
@@ -2757,13 +2757,13 @@
         <v>122</v>
       </c>
       <c r="C89" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="D89" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E89" s="2">
-        <v>45761.68908195602</v>
+        <v>45038.293456388885</v>
       </c>
       <c r="F89" t="s">
         <v>9</v>
@@ -2777,13 +2777,13 @@
         <v>123</v>
       </c>
       <c r="C90" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="D90" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E90" s="2">
-        <v>45378.36965071759</v>
+        <v>45255.2180877662</v>
       </c>
       <c r="F90" t="s">
         <v>9</v>
@@ -2797,13 +2797,13 @@
         <v>124</v>
       </c>
       <c r="C91" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="D91" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E91" s="2">
-        <v>45453.34148153935</v>
+        <v>45627.365948692124</v>
       </c>
       <c r="F91" t="s">
         <v>125</v>
@@ -2817,13 +2817,13 @@
         <v>126</v>
       </c>
       <c r="C92" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="D92" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="E92" s="2">
-        <v>45801.89120465278</v>
+        <v>45855.4849374537</v>
       </c>
       <c r="F92" t="s">
         <v>9</v>
@@ -2837,13 +2837,13 @@
         <v>127</v>
       </c>
       <c r="C93" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D93" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E93" s="2">
-        <v>44965.167293125</v>
+        <v>45929.957528252315</v>
       </c>
       <c r="F93" t="s">
         <v>9</v>
@@ -2857,13 +2857,13 @@
         <v>128</v>
       </c>
       <c r="C94" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="D94" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E94" s="2">
-        <v>45066.99887041667</v>
+        <v>45031.54272760417</v>
       </c>
       <c r="F94" t="s">
         <v>9</v>
@@ -2877,13 +2877,13 @@
         <v>129</v>
       </c>
       <c r="C95" t="s">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="D95" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="E95" s="2">
-        <v>45060.12382320601</v>
+        <v>45043.196392962964</v>
       </c>
       <c r="F95" t="s">
         <v>9</v>
@@ -2897,13 +2897,13 @@
         <v>130</v>
       </c>
       <c r="C96" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D96" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E96" s="2">
-        <v>45750.43364966435</v>
+        <v>45204.895870555556</v>
       </c>
       <c r="F96" t="s">
         <v>131</v>
@@ -2917,13 +2917,13 @@
         <v>132</v>
       </c>
       <c r="C97" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="D97" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E97" s="2">
-        <v>44948.199726736115</v>
+        <v>44929.925646620366</v>
       </c>
       <c r="F97" t="s">
         <v>9</v>
@@ -2937,13 +2937,13 @@
         <v>133</v>
       </c>
       <c r="C98" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="D98" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E98" s="2">
-        <v>45925.95130509259</v>
+        <v>45835.8027225</v>
       </c>
       <c r="F98" t="s">
         <v>9</v>
@@ -2957,13 +2957,13 @@
         <v>134</v>
       </c>
       <c r="C99" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D99" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E99" s="2">
-        <v>45376.73413805556</v>
+        <v>45086.501720451386</v>
       </c>
       <c r="F99" t="s">
         <v>9</v>
@@ -2977,13 +2977,13 @@
         <v>135</v>
       </c>
       <c r="C100" t="s">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="D100" t="s">
         <v>12</v>
       </c>
       <c r="E100" s="2">
-        <v>45284.32930309028</v>
+        <v>45104.61304674769</v>
       </c>
       <c r="F100" t="s">
         <v>9</v>
@@ -2997,13 +2997,13 @@
         <v>136</v>
       </c>
       <c r="C101" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D101" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E101" s="2">
-        <v>45485.730412743054</v>
+        <v>45295.220789363426</v>
       </c>
       <c r="F101" t="s">
         <v>137</v>
@@ -3017,13 +3017,13 @@
         <v>138</v>
       </c>
       <c r="C102" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D102" t="s">
         <v>12</v>
       </c>
       <c r="E102" s="2">
-        <v>45471.94407869213</v>
+        <v>45659.3377363426</v>
       </c>
       <c r="F102" t="s">
         <v>9</v>
@@ -3037,13 +3037,13 @@
         <v>139</v>
       </c>
       <c r="C103" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D103" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E103" s="2">
-        <v>44984.07630591435</v>
+        <v>45155.052664386574</v>
       </c>
       <c r="F103" t="s">
         <v>9</v>
@@ -3057,13 +3057,13 @@
         <v>140</v>
       </c>
       <c r="C104" t="s">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="D104" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E104" s="2">
-        <v>45693.30002576389</v>
+        <v>45608.08380554398</v>
       </c>
       <c r="F104" t="s">
         <v>9</v>
@@ -3080,10 +3080,10 @@
         <v>7</v>
       </c>
       <c r="D105" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E105" s="2">
-        <v>45647.8305628588</v>
+        <v>46003.01426872685</v>
       </c>
       <c r="F105" t="s">
         <v>9</v>
@@ -3100,10 +3100,10 @@
         <v>7</v>
       </c>
       <c r="D106" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E106" s="2">
-        <v>45234.76553958333</v>
+        <v>45739.81275774306</v>
       </c>
       <c r="F106" t="s">
         <v>143</v>
@@ -3117,13 +3117,13 @@
         <v>144</v>
       </c>
       <c r="C107" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D107" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="E107" s="2">
-        <v>45356.90713854167</v>
+        <v>45100.53655638889</v>
       </c>
       <c r="F107" t="s">
         <v>9</v>
@@ -3137,13 +3137,13 @@
         <v>145</v>
       </c>
       <c r="C108" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D108" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E108" s="2">
-        <v>45638.38134782408</v>
+        <v>44933.57071270833</v>
       </c>
       <c r="F108" t="s">
         <v>9</v>
@@ -3157,13 +3157,13 @@
         <v>146</v>
       </c>
       <c r="C109" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="D109" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E109" s="2">
-        <v>45523.46985637731</v>
+        <v>45065.12355366898</v>
       </c>
       <c r="F109" t="s">
         <v>9</v>
@@ -3177,13 +3177,13 @@
         <v>147</v>
       </c>
       <c r="C110" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D110" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="E110" s="2">
-        <v>45098.57215090278</v>
+        <v>45763.93087628472</v>
       </c>
       <c r="F110" t="s">
         <v>9</v>
@@ -3197,13 +3197,13 @@
         <v>148</v>
       </c>
       <c r="C111" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D111" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E111" s="2">
-        <v>45316.38991462963</v>
+        <v>46015.46855576389</v>
       </c>
       <c r="F111" t="s">
         <v>149</v>
@@ -3217,13 +3217,13 @@
         <v>150</v>
       </c>
       <c r="C112" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D112" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E112" s="2">
-        <v>45901.11137894676</v>
+        <v>45471.93298210648</v>
       </c>
       <c r="F112" t="s">
         <v>9</v>
@@ -3237,13 +3237,13 @@
         <v>151</v>
       </c>
       <c r="C113" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D113" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E113" s="2">
-        <v>45289.725492893514</v>
+        <v>45111.78447400463</v>
       </c>
       <c r="F113" t="s">
         <v>9</v>
@@ -3257,13 +3257,13 @@
         <v>152</v>
       </c>
       <c r="C114" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="D114" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="E114" s="2">
-        <v>45112.38598709491</v>
+        <v>45558.33870226852</v>
       </c>
       <c r="F114" t="s">
         <v>9</v>
@@ -3277,13 +3277,13 @@
         <v>153</v>
       </c>
       <c r="C115" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="D115" t="s">
         <v>12</v>
       </c>
       <c r="E115" s="2">
-        <v>45350.74865983796</v>
+        <v>45242.59115586805</v>
       </c>
       <c r="F115" t="s">
         <v>9</v>
@@ -3297,13 +3297,13 @@
         <v>154</v>
       </c>
       <c r="C116" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="D116" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E116" s="2">
-        <v>44960.11539047454</v>
+        <v>45968.935523125</v>
       </c>
       <c r="F116" t="s">
         <v>155</v>
@@ -3320,10 +3320,10 @@
         <v>14</v>
       </c>
       <c r="D117" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E117" s="2">
-        <v>45083.66727605324</v>
+        <v>44975.541631875</v>
       </c>
       <c r="F117" t="s">
         <v>9</v>
@@ -3337,13 +3337,13 @@
         <v>157</v>
       </c>
       <c r="C118" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D118" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E118" s="2">
-        <v>45153.225753113424</v>
+        <v>45477.8994446875</v>
       </c>
       <c r="F118" t="s">
         <v>9</v>
@@ -3357,13 +3357,13 @@
         <v>158</v>
       </c>
       <c r="C119" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D119" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="E119" s="2">
-        <v>45571.16368668982</v>
+        <v>45791.11059719908</v>
       </c>
       <c r="F119" t="s">
         <v>9</v>
@@ -3377,13 +3377,13 @@
         <v>159</v>
       </c>
       <c r="C120" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D120" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="E120" s="2">
-        <v>45324.40736833333</v>
+        <v>45197.949214004635</v>
       </c>
       <c r="F120" t="s">
         <v>9</v>
@@ -3397,13 +3397,13 @@
         <v>160</v>
       </c>
       <c r="C121" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D121" t="s">
         <v>12</v>
       </c>
       <c r="E121" s="2">
-        <v>45152.86527895833</v>
+        <v>45946.68050296296</v>
       </c>
       <c r="F121" t="s">
         <v>161</v>
@@ -3417,13 +3417,13 @@
         <v>162</v>
       </c>
       <c r="C122" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D122" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="E122" s="2">
-        <v>45369.06387704861</v>
+        <v>45169.05375190973</v>
       </c>
       <c r="F122" t="s">
         <v>9</v>
@@ -3437,13 +3437,13 @@
         <v>163</v>
       </c>
       <c r="C123" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D123" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E123" s="2">
-        <v>45952.73937552083</v>
+        <v>45313.756019328706</v>
       </c>
       <c r="F123" t="s">
         <v>9</v>
@@ -3457,13 +3457,13 @@
         <v>164</v>
       </c>
       <c r="C124" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D124" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E124" s="2">
-        <v>45768.15889295139</v>
+        <v>45202.72132285879</v>
       </c>
       <c r="F124" t="s">
         <v>9</v>
@@ -3477,13 +3477,13 @@
         <v>165</v>
       </c>
       <c r="C125" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D125" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E125" s="2">
-        <v>45328.20966049768</v>
+        <v>45460.47408533565</v>
       </c>
       <c r="F125" t="s">
         <v>9</v>
@@ -3497,13 +3497,13 @@
         <v>166</v>
       </c>
       <c r="C126" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D126" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E126" s="2">
-        <v>45941.83322111111</v>
+        <v>45105.3390234375</v>
       </c>
       <c r="F126" t="s">
         <v>167</v>
@@ -3517,13 +3517,13 @@
         <v>168</v>
       </c>
       <c r="C127" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D127" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E127" s="2">
-        <v>44933.60669211806</v>
+        <v>45279.23010043982</v>
       </c>
       <c r="F127" t="s">
         <v>9</v>
@@ -3537,13 +3537,13 @@
         <v>169</v>
       </c>
       <c r="C128" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D128" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E128" s="2">
-        <v>45636.53265616898</v>
+        <v>45082.08718877315</v>
       </c>
       <c r="F128" t="s">
         <v>9</v>
@@ -3557,13 +3557,13 @@
         <v>170</v>
       </c>
       <c r="C129" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D129" t="s">
         <v>8</v>
       </c>
       <c r="E129" s="2">
-        <v>45080.97970648148</v>
+        <v>45062.358714918984</v>
       </c>
       <c r="F129" t="s">
         <v>9</v>
@@ -3577,13 +3577,13 @@
         <v>171</v>
       </c>
       <c r="C130" t="s">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="D130" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="E130" s="2">
-        <v>45434.88221524305</v>
+        <v>45905.68349335648</v>
       </c>
       <c r="F130" t="s">
         <v>9</v>
@@ -3597,13 +3597,13 @@
         <v>172</v>
       </c>
       <c r="C131" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D131" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E131" s="2">
-        <v>45239.478362696755</v>
+        <v>45205.43582445601</v>
       </c>
       <c r="F131" t="s">
         <v>173</v>
@@ -3617,13 +3617,13 @@
         <v>174</v>
       </c>
       <c r="C132" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="D132" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E132" s="2">
-        <v>45609.7977209838</v>
+        <v>45490.407541203705</v>
       </c>
       <c r="F132" t="s">
         <v>9</v>
@@ -3637,13 +3637,13 @@
         <v>175</v>
       </c>
       <c r="C133" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="D133" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E133" s="2">
-        <v>45504.02472811342</v>
+        <v>45915.94741604167</v>
       </c>
       <c r="F133" t="s">
         <v>9</v>
@@ -3657,13 +3657,13 @@
         <v>176</v>
       </c>
       <c r="C134" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D134" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E134" s="2">
-        <v>45034.250620844905</v>
+        <v>45147.367361655095</v>
       </c>
       <c r="F134" t="s">
         <v>9</v>
@@ -3677,13 +3677,13 @@
         <v>177</v>
       </c>
       <c r="C135" t="s">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="D135" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E135" s="2">
-        <v>45122.9723112037</v>
+        <v>45371.36429104167</v>
       </c>
       <c r="F135" t="s">
         <v>9</v>
@@ -3697,13 +3697,13 @@
         <v>178</v>
       </c>
       <c r="C136" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="D136" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E136" s="2">
-        <v>45864.103865439814</v>
+        <v>45702.90671173611</v>
       </c>
       <c r="F136" t="s">
         <v>179</v>
@@ -3720,10 +3720,10 @@
         <v>11</v>
       </c>
       <c r="D137" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E137" s="2">
-        <v>45859.88566851852</v>
+        <v>44951.40575826389</v>
       </c>
       <c r="F137" t="s">
         <v>9</v>
@@ -3737,13 +3737,13 @@
         <v>181</v>
       </c>
       <c r="C138" t="s">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="D138" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="E138" s="2">
-        <v>45058.685967337966</v>
+        <v>45708.804541875</v>
       </c>
       <c r="F138" t="s">
         <v>9</v>
@@ -3757,13 +3757,13 @@
         <v>182</v>
       </c>
       <c r="C139" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="D139" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="E139" s="2">
-        <v>45059.01743425926</v>
+        <v>45718.64279629629</v>
       </c>
       <c r="F139" t="s">
         <v>9</v>
@@ -3777,13 +3777,13 @@
         <v>183</v>
       </c>
       <c r="C140" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D140" t="s">
         <v>8</v>
       </c>
       <c r="E140" s="2">
-        <v>45954.66003320602</v>
+        <v>45117.51364377315</v>
       </c>
       <c r="F140" t="s">
         <v>9</v>
@@ -3797,13 +3797,13 @@
         <v>184</v>
       </c>
       <c r="C141" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D141" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E141" s="2">
-        <v>45834.46553559028</v>
+        <v>45866.755907280094</v>
       </c>
       <c r="F141" t="s">
         <v>185</v>
@@ -3817,13 +3817,13 @@
         <v>186</v>
       </c>
       <c r="C142" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="D142" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="E142" s="2">
-        <v>45459.17694643518</v>
+        <v>45303.916257268516</v>
       </c>
       <c r="F142" t="s">
         <v>9</v>
@@ -3837,13 +3837,13 @@
         <v>187</v>
       </c>
       <c r="C143" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="D143" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E143" s="2">
-        <v>45640.99325179398</v>
+        <v>45383.74967056713</v>
       </c>
       <c r="F143" t="s">
         <v>9</v>
@@ -3857,13 +3857,13 @@
         <v>188</v>
       </c>
       <c r="C144" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="D144" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E144" s="2">
-        <v>45915.05035445602</v>
+        <v>45396.83874436343</v>
       </c>
       <c r="F144" t="s">
         <v>9</v>
@@ -3877,13 +3877,13 @@
         <v>189</v>
       </c>
       <c r="C145" t="s">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="D145" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E145" s="2">
-        <v>45366.18571457176</v>
+        <v>45323.514683587964</v>
       </c>
       <c r="F145" t="s">
         <v>9</v>
@@ -3897,13 +3897,13 @@
         <v>190</v>
       </c>
       <c r="C146" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D146" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E146" s="2">
-        <v>45407.01464355324</v>
+        <v>45869.27488871528</v>
       </c>
       <c r="F146" t="s">
         <v>191</v>
@@ -3917,13 +3917,13 @@
         <v>192</v>
       </c>
       <c r="C147" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D147" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="E147" s="2">
-        <v>45363.96879295139</v>
+        <v>45442.23598269676</v>
       </c>
       <c r="F147" t="s">
         <v>9</v>
@@ -3937,13 +3937,13 @@
         <v>193</v>
       </c>
       <c r="C148" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D148" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E148" s="2">
-        <v>44995.362212685184</v>
+        <v>45220.314411099534</v>
       </c>
       <c r="F148" t="s">
         <v>9</v>
@@ -3957,13 +3957,13 @@
         <v>194</v>
       </c>
       <c r="C149" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D149" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="E149" s="2">
-        <v>45588.39076627315</v>
+        <v>45600.72355949074</v>
       </c>
       <c r="F149" t="s">
         <v>9</v>
@@ -3977,13 +3977,13 @@
         <v>195</v>
       </c>
       <c r="C150" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="D150" t="s">
         <v>8</v>
       </c>
       <c r="E150" s="2">
-        <v>45484.44575236111</v>
+        <v>45128.62223987268</v>
       </c>
       <c r="F150" t="s">
         <v>9</v>
@@ -3997,13 +3997,13 @@
         <v>196</v>
       </c>
       <c r="C151" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D151" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E151" s="2">
-        <v>44956.94424225694</v>
+        <v>45042.47163914352</v>
       </c>
       <c r="F151" t="s">
         <v>197</v>

--- a/samples/sample.xlsx
+++ b/samples/sample.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="757" uniqueCount="349">
   <si>
     <t>ID</t>
   </si>
@@ -31,580 +31,1033 @@
     <t>Notes</t>
   </si>
   <si>
-    <t>finally your mostly more many without while old would its our get however would suddenly gradually eventually have gradually the through everyone she some its eventually quickly way them while obviously our that these sometimes will that had them its said put totally are especially but first will totally completely had without other gradually eventually always mostly your slowly new should they completely completely out where carefully than normally which this while with where man which you out someone recently without into about there mostly slowly finally let everything eventually use she mainly then with first from see primarily recently</t>
+    <t>Conversation</t>
+  </si>
+  <si>
+    <t>there day than them immediately especially actually particularly always these totally one this which will however new because mostly during did and usually about after basically especially before really have normally absolutely you only each who you absolutely exactly how where our your your another then something put initially therefore will actually definitely see although with other primarily day how mainly fully put from perhaps everyone therefore this are put other anything between you other way first without primarily eventually its when eventually say have new our boy finally completely each that than first there eventually was without and therefore</t>
+  </si>
+  <si>
+    <t>Finance</t>
+  </si>
+  <si>
+    <t>Approved</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Dave: Sounds good to me. Eve: Thanks for the update.</t>
+  </si>
+  <si>
+    <t>actually put his said too them while during would finally they mainly one certainly mostly not therefore each old him had have get from generally can certainly been when could although generally way can immediately immediately more some then can obviously because after especially have which had how actually first absolutely obviously these between mostly each your many that too old man has new these that all get fully always there after put now mostly said his without mainly really your fully all totally get usually sometimes suddenly something during everyone day these something each she finally partly not from</t>
   </si>
   <si>
     <t>Support</t>
   </si>
   <si>
+    <t>Eve: We should discuss this offline. Caline: Sounds good to me. Eve: I have a question about that. Dave: I need to confirm with the team.</t>
+  </si>
+  <si>
+    <t>way can some now slowly way you can other not really entirely during obviously would him therefore obviously really apparently way would entirely another certainly then and her immediately each should fully now anything this not exactly she gradually now from actually primarily been definitely use absolutely slowly see primarily exactly now out there which basically partly use quickly eventually initially usually his certainly day had nothing who say has perhaps had another immediately totally being all let your mostly get should some other many use new normally totally have particularly always gradually especially without gradually did old the way</t>
+  </si>
+  <si>
+    <t>Sales</t>
+  </si>
+  <si>
     <t>Pending</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>many not one therefore her put absolutely get there usually had because the your mostly boy everything its nothing fully obviously initially many should apparently that did before then was than its would quickly gradually before originally normally certainly after generally when many before her fully its perhaps gradually absolutely therefore each use when there her our quickly each completely definitely who anything been out more perhaps see our him then was apparently now particularly during although another can where exactly before recently they before one completely these during old normally completely but sometimes for was then each really will</t>
+    <t>Bob: Thanks for the update. Dave: Can we schedule a follow-up? Caline: I will send the details soon.</t>
+  </si>
+  <si>
+    <t>these more use quickly other would day with everyone sometimes however while then initially have was during but immediately through all each completely who while however than see this them certainly did could that many will after them say about primarily and initially all too put other between perhaps let into boy totally how only recently with usually everyone other did being all exactly put however your they they been but entirely will and already these eventually totally everyone before will way for already with generally suddenly obviously our therefore during exactly another when therefore about had normally usually that</t>
+  </si>
+  <si>
+    <t>Engineering</t>
+  </si>
+  <si>
+    <t>Needs Review</t>
+  </si>
+  <si>
+    <t>Eve: Got it, thanks. Eve: We should discuss this offline. Caline: No problem. Bob: I will send the details soon.</t>
+  </si>
+  <si>
+    <t>gradually therefore his recently for new into had too day exactly your where mostly him into our when quickly could these fully apparently him therefore perhaps some everything would actually normally them primarily totally not although not its had immediately during had immediately originally recently out through new that totally before during after perhaps initially will its only some really carefully being with them slowly primarily how basically sometimes say fully usually that many exactly sometimes his new everyone his before you could boy its especially your suddenly did usually always about are usually while everything someone everything therefore then</t>
+  </si>
+  <si>
+    <t>Note for row 5</t>
+  </si>
+  <si>
+    <t>Bob: I will send the details soon. Dave: I need to confirm with the team.</t>
+  </si>
+  <si>
+    <t>the she already anything been would nothing said originally usually nothing initially usually where originally then would man out everything old and did originally primarily although boy entirely now was which see entirely with usually day that certainly should many him the then entirely normally particularly immediately their than has other quickly how they quickly anything many really who not between then was has first definitely gradually now however basically during too generally other the fully really about new about something all sometimes each but suddenly although more eventually actually another she some which are immediately really always into quickly</t>
+  </si>
+  <si>
+    <t>HR</t>
+  </si>
+  <si>
+    <t>In Progress</t>
+  </si>
+  <si>
+    <t>Dave: Sounds good to me. Bob: Sounds good to me.</t>
+  </si>
+  <si>
+    <t>for many immediately said than your definitely after their not actually when eventually although someone although would out too her had everyone primarily only sometimes nothing completely completely although usually out during first everything would between you exactly usually from too had quickly nothing how should day put than did anything before primarily exactly that put primarily basically certainly have finally first slowly too sometimes than them therefore generally completely the first would when this obviously are old however sometimes generally totally partly put about certainly nothing someone your can are first always would another exactly recently recently anything they</t>
+  </si>
+  <si>
+    <t>Alice: I need to confirm with the team. Alice: Got it, thanks. Caline: Any other items for today? Eve: No problem.</t>
+  </si>
+  <si>
+    <t>someone too man out many how after however are way old was will been definitely been many through gradually her really definitely definitely finally she these had would each will through gradually completely through this new his are his entirely many another boy originally without apparently boy too see especially however eventually when more are between said his now not her perhaps during initially only old and nothing nothing before suddenly had but them these quickly are recently than say when fully get one when this anything too absolutely and only say more has first when let have their actually</t>
+  </si>
+  <si>
+    <t>Eve: I will send the details soon. Eve: I need to confirm with the team.</t>
+  </si>
+  <si>
+    <t>old your slowly particularly had only our for although recently partly out been than exactly suddenly everything suddenly him basically when another suddenly nothing said you she not after carefully many everyone then put completely has more she then eventually primarily mostly between obviously man they recently absolutely nothing the everything day and when through would particularly that too during about about into initially particularly eventually there nothing someone more everyone now she see and some while our for really immediately something his obviously put each could will been mostly fully something into absolutely slowly obviously but will into are</t>
+  </si>
+  <si>
+    <t>Rejected</t>
+  </si>
+  <si>
+    <t>Alice: Let me check and get back to you. Alice: Thanks for the update. Caline: Thanks for the update. Eve: Thanks for the update.</t>
+  </si>
+  <si>
+    <t>now its has did this has all get new are one her obviously absolutely mainly someone man only they has therefore this between finally there use too another initially normally carefully put immediately them her certainly has more these between that exactly let let slowly particularly her than always nothing one before their someone always their who how into not originally between has anything they immediately and who only really slowly obviously not nothing that can sometimes generally the particularly put then something been one our completely originally nothing normally where man gradually get his them some however who obviously</t>
   </si>
   <si>
     <t>Marketing</t>
   </si>
   <si>
-    <t>Approved</t>
-  </si>
-  <si>
-    <t>always use how boy generally his one all basically during these that for primarily definitely these its who carefully only immediately and nothing someone there totally into definitely that about between too man particularly been mainly one should she put before this his without then way only but use first particularly completely would absolutely during was many everything definitely see your put exactly partly being before the partly carefully out them initially another apparently say not everyone first our say she where way there being generally before because them immediately slowly new after had everything absolutely certainly one man old</t>
-  </si>
-  <si>
-    <t>Finance</t>
-  </si>
-  <si>
-    <t>Rejected</t>
-  </si>
-  <si>
-    <t>but entirely although you nothing another eventually usually although into although are and everyone although old when therefore use each slowly absolutely should perhaps everyone anything boy now this slowly could many recently now new when another entirely where completely there quickly could other she someone all but between originally absolutely mainly while slowly their gradually who was mainly their originally you which usually your has slowly you everything slowly put boy all between without therefore they while with partly obviously other mainly would many generally through say now into suddenly for while that their first use really perhaps has</t>
-  </si>
-  <si>
-    <t>Sales</t>
-  </si>
-  <si>
-    <t>some anything usually all when would because obviously totally generally old all quickly way initially you after quickly which more way basically absolutely many during into after usually that however anything particularly apparently while some actually between will especially obviously certainly with that had you initially now already are into old primarily more have from him partly new each where out before out out day while put was will our who are gradually way during basically would more should which eventually his other out everyone say new through without these that because her immediately nothing between carefully where generally normally</t>
-  </si>
-  <si>
-    <t>Note for row 5</t>
-  </si>
-  <si>
-    <t>and immediately first put will where first about immediately some our him through everyone recently did before this how are exactly really through then immediately him should usually through sometimes sometimes has been therefore initially day completely many use one say too not normally slowly they sometimes certainly absolutely apparently put carefully originally apparently suddenly totally but all exactly each mainly something however are let however said everyone recently more now would would use our their anything everything mostly way new after always did our anything someone get fully perhaps would obviously actually let when than always our him eventually</t>
-  </si>
-  <si>
-    <t>Engineering</t>
-  </si>
-  <si>
-    <t>Needs Review</t>
-  </si>
-  <si>
-    <t>did boy finally immediately slowly immediately quickly way see therefore its with certainly which old actually immediately something carefully not finally normally old totally that all has recently been put other normally only let boy only quickly see but the from and how mostly day primarily sometimes which another see their been but mainly usually for perhaps each usually them they did him basically him them another definitely its fully not being another between should especially would although when originally there primarily use you other boy see new who another which said entirely during her their where could there the</t>
-  </si>
-  <si>
-    <t>another because completely immediately them that about boy many normally mostly day certainly you all day have his but nothing now new always have who eventually said they something immediately recently someone than into immediately did say one therefore the totally him new eventually and from primarily should other out anything before sometimes initially boy basically another another each been generally mainly apparently from mostly from each each recently him completely because generally basically and where during slowly absolutely too fully with generally everyone new actually get said out how recently how which was through before them basically entirely perhaps</t>
-  </si>
-  <si>
-    <t>how has have slowly him all would basically new should the immediately sometimes immediately sometimes therefore being quickly the really originally old without between get completely without everything had however has they your recently her when their basically anything get slowly all certainly already too entirely who slowly how these them him entirely now everyone certainly she its how this immediately but these normally where has has her partly are actually did through said see absolutely say especially can recently about exactly quickly into the exactly all get completely without definitely primarily should basically that gradually finally anything she apparently</t>
-  </si>
-  <si>
-    <t>In Progress</t>
-  </si>
-  <si>
-    <t>particularly only you through some put this immediately our see now before how new from now absolutely than suddenly exactly after quickly been its nothing when mostly while not therefore between already suddenly carefully some many use had have however from fully suddenly where recently originally mostly fully exactly been will can how said not sometimes should partly with which for said finally eventually our did recently how our she immediately after although say normally our will too she because slowly always initially eventually man quickly while without said normally mostly will sometimes your particularly primarily into during immediately who</t>
-  </si>
-  <si>
     <t>Note for row 10</t>
   </si>
   <si>
-    <t>fully him apparently normally many who other there usually fully his use out someone have other where after where day anything only put initially use other perhaps and been should always absolutely day gradually suddenly especially immediately although slowly let suddenly mainly this now boy each not into other certainly they are him their way perhaps for are its originally more suddenly did our been basically our originally out being some that but let certainly already particularly day normally actually anything are him completely entirely totally use after first was did way said absolutely generally slowly there originally actually see</t>
-  </si>
-  <si>
-    <t>but their put that everyone slowly for only obviously someone carefully not then new get you being one said the quickly especially old our originally from suddenly recently for many normally immediately has they new always they basically slowly should recently can would definitely mostly although mostly however another boy perhaps this during without will have obviously finally another finally been man man always everyone everything normally did let therefore your one old you her did while but these him the where there from then will who how are particularly the had get everyone everything absolutely man are are not</t>
-  </si>
-  <si>
-    <t>did quickly anything which through completely and use all obviously but carefully totally her basically she one way suddenly way him apparently how being recently eventually not slowly actually our who not when carefully old fully usually slowly have way and fully being but then fully basically being entirely some one after however with now boy where that with especially nothing everything primarily really eventually absolutely obviously absolutely quickly primarily gradually for they another been fully apparently completely certainly they many while perhaps suddenly only are your eventually man basically they for how should usually into was basically said someone</t>
-  </si>
-  <si>
-    <t>slowly them through not mainly these totally really especially our how old always apparently immediately absolutely out his than everything exactly then man sometimes anything man totally did suddenly all will although because nothing did partly their quickly would everything from man did which something all although said its have obviously was originally will always some someone day new said perhaps with him let can while sometimes say boy primarily entirely when everything but recently apparently actually something suddenly the especially suddenly him how perhaps but normally each already out only the the actually where her everything another mainly their</t>
-  </si>
-  <si>
-    <t>this only initially she through had fully boy generally basically carefully already was their said which then everything them perhaps out from eventually someone without slowly generally the for but slowly the particularly put sometimes his could really boy mostly sometimes quickly slowly everyone gradually fully always was was let not primarily other their someone then and although after first between when some him another everything immediately totally old perhaps nothing mostly immediately absolutely mainly than said for generally have someone has old see already exactly one his you get say would absolutely they there immediately old these absolutely particularly</t>
+    <t>Bob: I will send the details soon. Caline: Let me check and get back to you.</t>
+  </si>
+  <si>
+    <t>because get has which from you but definitely where these has eventually something one mainly not especially these many perhaps these many use recently really which something only entirely his without which being recently during they that was boy partly them did there should some you our than about are immediately initially obviously that obviously immediately too you basically his old primarily how anything they for entirely another you certainly you basically and this after old old for with first out this eventually let one was nothing although her who someone therefore each absolutely than him was than day perhaps</t>
+  </si>
+  <si>
+    <t>Eve: We should discuss this offline. Alice: Any other items for today?</t>
+  </si>
+  <si>
+    <t>are always everyone carefully when new when therefore each where finally man that basically everyone should immediately his other use out how everyone first not suddenly basically who her another how can being way eventually initially immediately mainly but apparently day see are new particularly have many many everything everything each always way man one during had did absolutely his before out when them did absolutely gradually perhaps obviously something being they definitely apparently normally said these into partly say would which then apparently boy use everyone man about everyone there basically therefore then without was and the really these</t>
+  </si>
+  <si>
+    <t>Bob: Thanks for the update. Dave: Let me check and get back to you. Alice: I have a question about that. Bob: Thanks for the update.</t>
+  </si>
+  <si>
+    <t>for only basically obviously could initially someone primarily was then recently are particularly boy which totally while while and gradually one should particularly some they into use way nothing exactly their recently now slowly therefore each them many for certainly have quickly they had new immediately everyone all his generally actually while see usually mostly suddenly initially because originally other definitely immediately man new all generally always perhaps however already especially but they totally during not too gradually mainly mostly absolutely one everyone new usually while primarily quickly being say see nothing each being but partly especially way therefore while</t>
+  </si>
+  <si>
+    <t>Alice: I need to confirm with the team. Bob: That works for me. Dave: No problem.</t>
+  </si>
+  <si>
+    <t>there way there was put anything had initially already however but then someone usually into normally way first totally someone during them let another you has the all him this between anything everyone absolutely each recently they way being other someone everything their and sometimes however see their our would anything not man did the should said obviously would see other with definitely however definitely boy will finally with certainly through other will would usually are which was way than you they they that more did during especially for when completely many many than perhaps before into finally her that</t>
+  </si>
+  <si>
+    <t>Alice: Thanks for the update. Dave: I will send the details soon. Dave: Sounds good to me. Caline: I will send the details soon.</t>
+  </si>
+  <si>
+    <t>without more however had fully has while how where boy new there are about has other immediately perhaps how did then new this between because originally partly absolutely only mostly nothing therefore there was especially another sometimes was everything between immediately before its mainly apparently recently through them perhaps you then could use before where obviously another his originally use recently some all who carefully that actually not actually and which this completely they someone mostly suddenly use see usually through can carefully than carefully usually put sometimes man eventually these they certainly which when actually therefore nothing all had</t>
   </si>
   <si>
     <t>Note for row 15</t>
   </si>
   <si>
-    <t>all gradually day immediately our really their your has definitely however which too immediately carefully fully perhaps this initially how too between someone use carefully slowly everyone normally these where but certainly than her put while who however who each actually and day being his before already someone there use slowly actually all how not particularly old let primarily him can one all obviously more his there already absolutely our say too out totally fully its although always say been she through someone while our too being after them already gradually now them primarily finally man old which first you</t>
-  </si>
-  <si>
-    <t>between immediately get anything suddenly during immediately entirely let generally immediately originally immediately now the between suddenly however finally mainly everything new get how see man let really could into immediately when man totally other her immediately exactly immediately initially had too perhaps being carefully something from our too for than because put finally completely anything our they sometimes said out something how definitely this sometimes from can anything about boy she another during not use before gradually anything many entirely she immediately into there before nothing your quickly this use exactly mostly normally after someone because let can but</t>
-  </si>
-  <si>
-    <t>totally should other for quickly carefully another now them her into her someone therefore suddenly obviously immediately her old then new that obviously old mainly everything being between other sometimes too perhaps another primarily can can who generally being these for will her some basically how perhaps can then suddenly for other generally way mostly was everything mainly put gradually suddenly her now mainly suddenly how initially exactly there than however especially although eventually first how sometimes not how really each way how did old for which let without without suddenly after all gradually more all that after are totally</t>
-  </si>
-  <si>
-    <t>completely use will about other than these anything who should day mainly way new this put use certainly but exactly especially partly therefore could everyone all through suddenly say although when who however the say about everyone finally therefore already originally had someone can all when our our they while other another eventually suddenly and first recently although then him mainly everything only all his before these one immediately about then actually she during this other primarily old nothing where their mostly and first however into who old obviously really should now while someone before where are than exactly really</t>
-  </si>
-  <si>
-    <t>definitely because suddenly has being was new the his which while immediately fully but especially basically particularly more other certainly sometimes from see because into say out first them all during did they especially then him her our who day day eventually suddenly out boy exactly especially them especially each another can perhaps boy the you someone would mostly basically let who how each suddenly your have there another these could where all they had another should because anything and although therefore which how already and without about exactly who apparently before say gradually nothing carefully man all carefully however</t>
+    <t>Alice: Any other items for today? Bob: Got it, thanks.</t>
+  </si>
+  <si>
+    <t>something than you old basically other you when from really than actually before completely that would fully suddenly everyone way get them had its she because actually slowly would although there all can before then each how only use mostly fully his first primarily see not would new when where they let through originally when normally before first sometimes usually normally are while definitely him something each particularly actually usually not about between put gradually another mainly first although normally first completely for not them normally completely when completely new its will said between has while where had however him</t>
+  </si>
+  <si>
+    <t>Bob: Got it, thanks. Eve: Sounds good to me. Bob: Sounds good to me.</t>
+  </si>
+  <si>
+    <t>are everything fully particularly basically did definitely been because really always out always your had could are sometimes sometimes actually say something absolutely although actually each are and finally where particularly immediately during perhaps there entirely that suddenly new always their through entirely during your because nothing however someone who therefore while another are carefully your out man perhaps perhaps get could when them put usually immediately these primarily sometimes only primarily for completely eventually the into quickly which gradually who him initially some absolutely them was some already can could apparently but now through particularly their see carefully which</t>
+  </si>
+  <si>
+    <t>Alice: Let me check and get back to you. Eve: We should discuss this offline. Alice: That works for me.</t>
+  </si>
+  <si>
+    <t>really quickly way had will initially quickly could mostly our she use mainly slowly some put the this into mostly mostly out see about obviously way that mainly more apparently certainly has exactly especially could use you totally originally through day primarily initially absolutely usually its let too everything first for how from for your absolutely apparently although said they something boy then let entirely initially although can slowly before their your because exactly sometimes not some finally her absolutely especially you especially some normally immediately really although which had actually entirely initially will absolutely only therefore basically are some</t>
+  </si>
+  <si>
+    <t>Dave: We should discuss this offline. Bob: We should discuss this offline.</t>
+  </si>
+  <si>
+    <t>see have slowly with immediately fully through have mainly then apparently only totally being generally normally although get could therefore other there been completely one there usually your his would actually and mainly especially but really really therefore have say finally where everyone will because many and she totally primarily quickly eventually nothing already certainly would only however before way into because had basically already recently who normally anything some their these absolutely put through obviously however basically now although see another nothing originally because already recently said not immediately finally someone too other out our always her primarily than</t>
+  </si>
+  <si>
+    <t>Bob: We should discuss this offline. Dave: No problem.</t>
+  </si>
+  <si>
+    <t>definitely from our some obviously too would during new there everyone his especially could him which while basically everything suddenly therefore has your another actually use get exactly new exactly always usually although could especially some have new although while have put more completely they old from sometimes particularly always without new originally way him immediately one one without would say with actually for than after has put entirely mainly for should particularly nothing this always exactly exactly the these boy with apparently between eventually then always nothing fully old where has many while someone although should basically entirely everyone</t>
   </si>
   <si>
     <t>Note for row 20</t>
   </si>
   <si>
-    <t>his basically been basically however way quickly their many where for because everything first too slowly however particularly everyone nothing first new will therefore her being one too them from someone certainly these through perhaps you man now definitely immediately totally its how which immediately let finally exactly her now through him but during being can partly exactly gradually where about your for where really this partly only which you usually our many certainly these each get old during her sometimes entirely after see our the while say get use through said the some not has without first but say</t>
-  </si>
-  <si>
-    <t>who gradually because for because say entirely about while perhaps you more without entirely our into you where then but had without totally have all will mostly then have because perhaps after your because after totally immediately have sometimes before certainly perhaps his however there everyone immediately normally this day from suddenly who they has generally recently his before had boy that then basically too she had really their your between mostly let obviously this first about normally absolutely said but their carefully old particularly say finally only where another before let entirely especially this everything everyone see their than</t>
-  </si>
-  <si>
-    <t>was being too into usually recently their apparently boy definitely mostly exactly eventually exactly how first should other about while and because did how into her your originally did not our could apparently although always although many someone completely therefore can usually through with another carefully finally being basically anything slowly will normally already their him after mostly but and could they its said finally immediately its totally only basically when initially being should say without the let something boy new always than primarily them for there particularly your exactly absolutely has this first its only already eventually between sometimes</t>
-  </si>
-  <si>
-    <t>however way let for was primarily already now not him the these initially there too are recently has gradually should completely all after basically did about always certainly finally and particularly other more however could something all for will between into however someone out say but obviously then during generally and because have get someone than originally carefully these many who another let boy finally now into however let through old now usually especially finally get with than will someone but many definitely everything has particularly can boy was obviously after are him has already certainly mostly more the always</t>
-  </si>
-  <si>
-    <t>HR</t>
-  </si>
-  <si>
-    <t>obviously has them which certainly only originally boy definitely usually particularly each quickly therefore partly have usually only use some already because more about all and which with nothing immediately has generally say initially one could there her will with therefore can certainly where and recently eventually this anything another boy actually new out because primarily with him quickly through eventually but use too all who therefore now old all anything after already when another now been into our perhaps from only after for its recently old everyone fully the some anything during only man did recently other you mostly</t>
+    <t>Dave: We should discuss this offline. Alice: I need to confirm with the team. Dave: I need to confirm with the team.</t>
+  </si>
+  <si>
+    <t>immediately exactly slowly originally each from many have had old normally someone from say immediately however their for completely only originally now already before can absolutely use have quickly day way something one which each see only our finally already definitely totally with definitely for another certainly boy basically sometimes they day nothing say day mostly old during see can are too was their had each more was being initially actually where should how said during everyone all everyone for and too gradually absolutely for get into another mainly because about immediately mostly particularly originally old another her from after</t>
+  </si>
+  <si>
+    <t>Caline: Any other items for today? Dave: I need to confirm with the team. Eve: We should discuss this offline. Eve: No problem.</t>
+  </si>
+  <si>
+    <t>could quickly everyone you day with something because suddenly could see however had will not for our for her not see obviously more fully this its have way exactly after therefore already they let there then these can certainly their apparently way when this mostly has the apparently partly without say sometimes would other usually get but could these only that boy man generally have then each then about how way normally certainly although she fully after nothing had then all some apparently especially apparently was into absolutely absolutely generally new immediately normally definitely without slowly his anything its especially</t>
+  </si>
+  <si>
+    <t>Eve: Can we schedule a follow-up? Alice: We should discuss this offline. Bob: No problem. Eve: We should discuss this offline.</t>
+  </si>
+  <si>
+    <t>they who had them and about obviously have sometimes are more particularly the him did been during get then suddenly when everything perhaps totally could suddenly these perhaps normally apparently now because your everyone through there completely initially will how already normally because get into the other where boy absolutely about absolutely old old have therefore who because fully immediately one fully fully her these has out anything sometimes fully one apparently her because another absolutely completely perhaps his was sometimes quickly eventually had another can put your recently eventually had their many will from definitely basically other have something</t>
+  </si>
+  <si>
+    <t>Bob: That works for me. Alice: Let me check and get back to you.</t>
+  </si>
+  <si>
+    <t>without his that other before say this between should usually should get each particularly originally normally quickly had certainly generally mainly not had already each initially generally originally definitely originally originally should originally and before another him therefore partly them partly apparently can can normally basically each normally man say actually initially through get his see basically say and basically quickly one where completely will therefore always because put basically that not without actually usually some your you been without another because old nothing but their immediately could him all obviously can usually especially always should but originally partly anything</t>
+  </si>
+  <si>
+    <t>Caline: We should discuss this offline. Eve: Any other items for today? Bob: Any other items for today? Eve: We should discuss this offline.</t>
+  </si>
+  <si>
+    <t>all immediately day boy sometimes and their entirely him there too especially they fully where you say new usually day new completely its everything quickly therefore will totally for your from first everyone all slowly this originally said where however nothing will slowly our immediately absolutely about nothing without nothing let your when you more anything before originally definitely this way gradually too especially would our out should had each into day everyone could particularly because normally primarily should recently their could from between obviously eventually but slowly now them recently something between some would anything although mainly your are</t>
   </si>
   <si>
     <t>Note for row 25</t>
   </si>
   <si>
-    <t>basically obviously this definitely suddenly them use the than suddenly day suddenly let which are before mostly particularly old that has out that was will quickly originally did where have generally this that definitely actually there slowly for and not however our which too immediately are old let how some said mostly between old into after apparently man now suddenly new all into there say generally who being especially other can which totally only apparently completely into because another after everyone one how initially through finally basically particularly she see because for than mostly was many gradually certainly through certainly</t>
-  </si>
-  <si>
-    <t>because has your have our did totally quickly through totally then use our quickly quickly his from absolutely through see are the your finally there partly obviously someone therefore fully carefully which see certainly can more basically them new only partly put has gradually however however slowly old their did did boy primarily their him some when fully his see your during during boy more originally see between before when immediately everything while another nothing which anything they perhaps perhaps this with these not see after you your immediately day more can something through will totally this sometimes should being</t>
-  </si>
-  <si>
-    <t>who because especially him generally recently because partly always exactly only mostly without them between fully between everything who slowly man was more therefore already man way put are should already this through these can other than how was partly day and eventually then are how however sometimes entirely say when first exactly perhaps will between completely finally her from how mainly apparently been finally always for primarily apparently primarily certainly recently new nothing when only will without something day primarily all many put boy now use this boy eventually had the said get first fully for boy totally the</t>
-  </si>
-  <si>
-    <t>carefully boy basically absolutely originally because not immediately she nothing new everything should therefore but about when recently now them initially only for could someone without has there one not you fully before day has his quickly after not now but really completely however way could nothing then into entirely especially get out him his see where and being one way and apparently not how with exactly suddenly too will which new have which between she quickly had too with already all being after finally certainly something although did see where during quickly being originally initially generally let are while</t>
-  </si>
-  <si>
-    <t>one another therefore this that obviously completely its each generally way use and during through for always therefore said fully the immediately our they all immediately anything them new too during from have then our boy therefore who now now day slowly totally the totally while old being generally she which him before from therefore nothing something too when while something although can therefore they basically has originally another someone entirely because through everyone only suddenly there quickly before everyone gradually immediately recently said had see fully get the because many recently see everything them definitely for now only said</t>
+    <t>Dave: No problem. Caline: We should discuss this offline.</t>
+  </si>
+  <si>
+    <t>boy only definitely should exactly first and has anything through where are perhaps slowly suddenly mostly really her definitely partly should let these and usually been way immediately will where your say then one had where has totally more finally his particularly mostly nothing actually but always old originally that although usually did get partly you being not already especially quickly its usually first while you exactly her did old not originally initially get slowly absolutely will said fully something partly now put the its immediately gradually only where quickly usually many said finally about with while you without basically</t>
+  </si>
+  <si>
+    <t>Eve: We should discuss this offline. Bob: No problem. Bob: I need to confirm with the team. Bob: No problem.</t>
+  </si>
+  <si>
+    <t>let use someone perhaps usually someone apparently basically who before but said our his anything absolutely already however his because mostly could everyone because way way finally everyone anything would carefully nothing many actually man another about suddenly her now this with although man them that has therefore for primarily have there their everything usually immediately particularly too more sometimes each more quickly which with had should completely therefore had nothing where always which where which carefully really apparently nothing therefore are something there usually for can each one him said now already entirely then without finally not should say</t>
+  </si>
+  <si>
+    <t>Eve: I need to confirm with the team. Bob: We should discuss this offline.</t>
+  </si>
+  <si>
+    <t>out really however another partly see now way after their during not out the our completely you recently recently into should with usually get exactly fully immediately something entirely had everyone you after although put your without one old man normally but your get only have basically them anything through but particularly primarily without initially was was fully get many did would could these way into first eventually all completely day who out carefully immediately nothing day has without generally are anything are everything our sometimes something put will when that however during everyone this too finally old see had</t>
+  </si>
+  <si>
+    <t>Dave: Any other items for today? Bob: That works for me.</t>
+  </si>
+  <si>
+    <t>carefully generally always you carefully say then perhaps after him fully did now recently originally mostly say usually during more but more being out him eventually totally say generally especially all anything man slowly our about actually which entirely should mostly was usually during has anything entirely actually but has you however him during suddenly quickly everyone suddenly put let gradually each the certainly say all said totally old between therefore although was other are something certainly boy suddenly would been gradually one mainly where however more exactly our was you was before nothing too could use way carefully day</t>
+  </si>
+  <si>
+    <t>Eve: I will send the details soon. Bob: That works for me. Alice: Can we schedule a follow-up?</t>
+  </si>
+  <si>
+    <t>entirely put should actually mostly totally through for her her eventually between carefully normally slowly all who before many after really for their immediately between was other did can only generally this normally but its while all eventually however that would this because already was will each could through however was being get are say always everyone from mostly perhaps more finally too boy him after her exactly first originally other always some each certainly primarily sometimes someone him put between immediately too are was then particularly totally his mostly everyone all these let finally each after can recently they</t>
   </si>
   <si>
     <t>Note for row 30</t>
   </si>
   <si>
-    <t>therefore basically than now from them partly already there you gradually totally without more was actually see his primarily carefully one that first primarily has the man primarily from already everything get see then usually our generally during nothing her mainly our said some way for when way immediately said been she before your apparently partly would gradually your already mainly other this however normally entirely before apparently quickly immediately slowly can only one all are during them and entirely everything get mainly you way the should initially been partly was where slowly anything man many could than old new</t>
-  </si>
-  <si>
-    <t>really some with from everyone gradually when did generally carefully already she too other through fully another not into will mainly its perhaps everyone this another its you but normally there generally was immediately however many put get especially these during nothing old was for that fully would her man for really between way between before then with should because has definitely mainly after that was some apparently way first first completely nothing obviously him really you gradually you one let immediately who way which first partly therefore get put eventually boy use carefully gradually than out from before too</t>
-  </si>
-  <si>
-    <t>immediately use without that therefore because their them the been between nothing and being them basically their these with partly but new that always everything day through could through primarily now absolutely her perhaps out use while other new without its would originally everyone day some something eventually for before put generally between while there these everyone exactly who new the way his quickly between generally exactly during about some old partly really its slowly where other our let when only this was their then this more mainly more them use slowly immediately quickly let how suddenly these where there</t>
-  </si>
-  <si>
-    <t>see man obviously how gradually who immediately without now everyone basically quickly something immediately use definitely some another who recently could into their for suddenly usually its everyone been certainly and originally the absolutely suddenly will mainly certainly everything these more mainly who because not about had been because say let obviously man absolutely when about said had obviously and will these out could more man because her absolutely how immediately the there particularly would been immediately completely however partly eventually she gradually old but too let before for some are something finally boy really said particularly for from really</t>
-  </si>
-  <si>
-    <t>completely everyone sometimes because first new boy obviously apparently can old first perhaps did always everyone where its totally immediately anything she way only with apparently when who these always everyone anything its apparently actually about totally each perhaps not his their its absolutely your another day partly into and without something put while that between more she suddenly many way apparently say should more how old although have something more originally about apparently them after not can during initially while other many suddenly anything normally exactly way these definitely where these absolutely already usually way who carefully during more</t>
+    <t>Caline: Let me check and get back to you. Alice: Let me check and get back to you.</t>
+  </si>
+  <si>
+    <t>normally had always will but because really your sometimes into one however which eventually one suddenly too all apparently immediately finally really although they about too with mainly out always his nothing generally sometimes perhaps because have she primarily something her eventually some how another get because already recently definitely carefully through certainly when completely however her entirely already suddenly then would way did more these now completely you someone how all did suddenly from always many another perhaps while nothing from carefully the your are something exactly than more did especially always really their way definitely originally before obviously</t>
+  </si>
+  <si>
+    <t>Alice: Thanks for the update. Eve: No problem. Dave: That works for me.</t>
+  </si>
+  <si>
+    <t>finally has for with basically obviously first mostly when basically eventually totally can has that partly would partly immediately everyone already initially between how already more day exactly some after everyone mainly they mostly get mainly without before immediately actually are its normally then nothing actually really something absolutely always some exactly had been your then have through first could out certainly there said and did apparently without can and would primarily would suddenly his now now really because without that new would generally between which should between because which day nothing way has this from are without should normally</t>
+  </si>
+  <si>
+    <t>Bob: Thanks for the update. Eve: No problem. Caline: I will send the details soon. Dave: I need to confirm with the team.</t>
+  </si>
+  <si>
+    <t>normally slowly out for out man can suddenly while some something eventually only then someone there been they will totally gradually actually where her after new one would apparently him his then said during was gradually our too but way originally his quickly its not man that apparently during gradually something boy how everything gradually their him therefore completely usually boy first through but basically everyone these that initially between more did but exactly exactly entirely man been how with our initially especially them partly slowly first new already then after recently not its everyone then gradually certainly obviously other</t>
+  </si>
+  <si>
+    <t>Eve: Sounds good to me. Alice: Can we schedule a follow-up?</t>
+  </si>
+  <si>
+    <t>all normally actually his which first with old you eventually they totally their our into always put been perhaps however recently usually she some fully basically obviously one through obviously have her absolutely apparently should nothing immediately only was all all their because for certainly eventually therefore nothing initially between apparently immediately all with way partly fully generally man everyone been would basically sometimes get say way did could about boy everything way initially perhaps each everyone could let not mainly gradually should another out while already him everyone was gradually actually immediately get eventually say fully old nothing really</t>
+  </si>
+  <si>
+    <t>Bob: I need to confirm with the team. Bob: That works for me. Dave: Any other items for today? Dave: Any other items for today?</t>
+  </si>
+  <si>
+    <t>always gradually eventually their anything already was old originally absolutely everything she absolutely put apparently because normally everyone and definitely normally say perhaps could anything these our how their particularly another one therefore she say everything something nothing their other but already absolutely quickly than one one had are other being therefore say suddenly have the through could nothing more totally however our completely where put other anything this between normally someone actually particularly someone really always not basically mostly from gradually entirely particularly with everything they mainly originally them him too perhaps then definitely sometimes where many after should</t>
   </si>
   <si>
     <t>Note for row 35</t>
   </si>
   <si>
-    <t>generally than slowly the definitely when fully before mostly for the can while did that perhaps been put always especially obviously one have completely his said not eventually entirely gradually totally some therefore already would completely with gradually from which suddenly where you partly these out however first say finally could fully initially immediately especially everyone put first however eventually originally already this someone did usually let definitely obviously boy where where already her finally from before slowly this then way their they obviously will they some than how would about partly into say how some than obviously eventually man</t>
-  </si>
-  <si>
-    <t>really put them certainly have these but exactly each each certainly another these apparently although primarily been let him more being while been because usually old obviously where mainly too where she who has initially initially man your slowly his how into apparently quickly way finally get they being always your day initially some someone where usually about see after use perhaps not than which could him really how however had without nothing carefully nothing partly but with she immediately out all basically they another them really obviously before always let eventually always sometimes suddenly other was quickly certainly more</t>
-  </si>
-  <si>
-    <t>one sometimes apparently had before basically let usually said said therefore normally than day actually someone everyone other while someone could only our our without have definitely already been has see been recently from sometimes will has its other primarily there would say his definitely them completely first someone some initially not slowly could boy while usually and especially through suddenly totally fully before our when usually generally exactly because primarily normally actually how been boy would immediately see you carefully nothing would there said about then sometimes perhaps everyone another her there new many day after them someone its</t>
-  </si>
-  <si>
-    <t>always before exactly sometimes everyone this how him completely therefore will would many obviously completely without although each finally said did only its too them between the another sometimes primarily someone finally the nothing absolutely there totally her initially these this put other new now before mainly who will out there boy for for you they this without all gradually get its that without originally normally some man originally let than between generally her than the already therefore which boy nothing sometimes one has now that said something they nothing normally each than see its primarily said obviously then being</t>
-  </si>
-  <si>
-    <t>than old the completely where their particularly than you totally which can absolutely first could actually originally something about about other immediately see new everything will all finally all slowly particularly could certainly put completely had has quickly said let been immediately actually say recently which can them without mostly see can particularly and did the between where certainly where this him them definitely into absolutely with always recently who finally boy our however obviously anything absolutely get immediately have put with however she perhaps through that without has exactly carefully carefully she primarily did into see between because into</t>
+    <t>Dave: Let me check and get back to you. Eve: Thanks for the update. Caline: I need to confirm with the team. Eve: I will send the details soon.</t>
+  </si>
+  <si>
+    <t>all immediately totally because other her will let recently our definitely therefore fully apparently get has another her did her everyone there with exactly for was something there now always said really all basically that them should now gradually her through did these initially everyone than recently while for than before everyone they being its particularly have should their let she did him immediately get use day get first nothing someone you without therefore get many too originally its totally let for apparently perhaps another out before actually let during mostly especially slowly everyone normally another nothing slowly been quickly</t>
+  </si>
+  <si>
+    <t>Alice: I will send the details soon. Caline: Can we schedule a follow-up? Eve: Can we schedule a follow-up?</t>
+  </si>
+  <si>
+    <t>could its mainly especially something where totally apparently than fully sometimes usually there said originally initially other out always gradually more boy can basically that she originally each between said should our usually totally them would the first originally did into not especially while now immediately they completely with from and been originally therefore basically did exactly our your entirely see perhaps she particularly when through her from many let through each other him slowly had other fully all them because our where then her when before before into normally recently generally old many how have say should their fully</t>
+  </si>
+  <si>
+    <t>Caline: Thanks for the update. Alice: I need to confirm with the team. Alice: I have a question about that. Bob: I need to confirm with the team.</t>
+  </si>
+  <si>
+    <t>primarily sometimes see have particularly has with from usually obviously each therefore fully new see fully old recently basically before while now suddenly this boy entirely exactly one from actually who boy where not anything has especially initially are while certainly say now first normally immediately during actually absolutely boy although especially them than but normally her between eventually partly perhaps really for there man being quickly only another these these eventually already other our could did its get one first because this into always perhaps had would mostly been originally where nothing certainly particularly something between see all obviously</t>
+  </si>
+  <si>
+    <t>Alice: Let me check and get back to you. Caline: Let me check and get back to you.</t>
+  </si>
+  <si>
+    <t>more while been that recently too recently through originally eventually absolutely partly you during from see their during this originally them too how normally then would partly already basically slowly while these although they suddenly only from actually through other immediately say how already many should about old let absolutely when generally there while its initially totally other then exactly him boy primarily between immediately sometimes one between her already usually these primarily absolutely use she can particularly not all other his however mostly one old this with sometimes someone has new obviously all however primarily nothing recently let let</t>
+  </si>
+  <si>
+    <t>Eve: I need to confirm with the team. Dave: Can we schedule a follow-up? Bob: That works for me.</t>
+  </si>
+  <si>
+    <t>been immediately slowly are one many through being which everyone now everyone that say has first everything exactly have old slowly more always from where more that another about exactly before eventually something say from carefully after your not old therefore everything say these already the him day new all would partly mostly old day she because through the immediately get exactly between day from day their first them certainly other definitely initially the was boy did primarily apparently only something eventually particularly actually for will boy through but them other have have new the that eventually too many finally</t>
   </si>
   <si>
     <t>Note for row 40</t>
   </si>
   <si>
-    <t>have her without nothing only therefore immediately everyone have generally out suddenly she sometimes this certainly another sometimes exactly how with where without particularly completely many you exactly her they everything nothing each for completely can out many immediately put obviously generally old has slowly you too was too some someone completely could perhaps mainly say all really always you has something gradually too basically you after use put suddenly each immediately already and apparently immediately many its from another day suddenly through she put and first them quickly immediately his actually into use that quickly completely particularly these before</t>
-  </si>
-  <si>
-    <t>therefore out carefully are did because partly old originally nothing normally because only because him out originally everything she more everyone exactly some all will put into the apparently everything then their without suddenly nothing there man get obviously put use where did everything especially already without anything who out slowly would although therefore about new for some will while immediately definitely quickly immediately should completely generally however had something finally but way without entirely her after you through perhaps really now too recently our new basically particularly another its boy its mainly quickly quickly see this really completely between</t>
-  </si>
-  <si>
-    <t>one did between our carefully use now nothing only have let mostly she slowly initially their nothing had first but should about would many him initially other put which absolutely then you especially generally old use with therefore finally would normally after therefore you carefully really where then normally quickly our her its with your suddenly way originally being about should generally after with after already more someone everything during recently day absolutely usually him now generally say man finally before particularly basically then her another fully into put all normally originally before into already usually there being these but</t>
-  </si>
-  <si>
-    <t>only entirely but how their nothing said this immediately man has certainly their perhaps mainly everything they mainly its because actually certainly usually which have too only partly during had everyone because that did was mostly during your before too after would see basically this into not where too you always although use normally primarily did the being especially completely with they its not put they now him therefore should can did sometimes not some particularly apparently should gradually without your finally only get should some and not this these will nothing that been will however said its all way</t>
-  </si>
-  <si>
-    <t>some another out they definitely one obviously about how finally quickly now had new where see new let mostly will eventually was some gradually about everything that therefore boy these nothing perhaps with although where entirely being recently after they was everyone immediately not really said absolutely some that recently everything certainly eventually did they totally anything the will you how will put recently everything usually partly many your get the will therefore usually fully boy although can from however obviously initially day would there really someone can however generally before certainly where have new mainly could will someone would</t>
+    <t>Bob: No problem. Dave: Let me check and get back to you. Eve: I have a question about that.</t>
+  </si>
+  <si>
+    <t>certainly fully boy usually initially they could they about however initially exactly between into old entirely everyone everyone she there has between definitely now immediately about really definitely really entirely they your usually too can than them finally gradually for particularly basically especially did these with have certainly can mostly for being her always before something man many all because have there had many finally another can through certainly totally boy his nothing now from many this obviously completely have originally said been had him say some the entirely totally they its nothing actually been let partly then from gradually</t>
+  </si>
+  <si>
+    <t>Dave: I need to confirm with the team. Alice: I have a question about that. Alice: I need to confirm with the team. Dave: I have a question about that.</t>
+  </si>
+  <si>
+    <t>who their finally therefore man there have let while but day was absolutely mostly quickly which will day something totally into about you she now after particularly originally these after was although use from they where its carefully exactly how some immediately sometimes suddenly then these obviously initially and who eventually fully you someone perhaps certainly particularly how partly been out because could sometimes many all without really said their new finally after primarily because therefore actually only way then however boy your while there before say certainly which from too definitely its has your now this about did especially</t>
+  </si>
+  <si>
+    <t>Dave: I will send the details soon. Eve: Any other items for today?</t>
+  </si>
+  <si>
+    <t>now basically its when and between apparently say only everyone should from was initially the completely after your mostly however everyone without him should absolutely usually has already too who should out immediately after although during you she one one without has another these suddenly usually which said for everything now boy first already exactly finally especially see let another originally day between however mostly after originally about where get carefully but apparently especially mostly him finally apparently without generally your before all before someone more fully being suddenly gradually nothing you primarily everything too see actually before say all</t>
+  </si>
+  <si>
+    <t>Bob: I will send the details soon. Dave: We should discuss this offline.</t>
+  </si>
+  <si>
+    <t>immediately into nothing although fully her the its than our could however was particularly our him her how then these then during with way put other would old way how actually should see mostly entirely this there there will entirely first into always before each particularly completely man everyone from new his basically however that then into which normally you which basically exactly totally its through her after one now only not through our apparently their originally are originally this normally gradually put and how where did see primarily basically other everyone everyone her their mainly exactly eventually mainly only</t>
+  </si>
+  <si>
+    <t>Eve: Can we schedule a follow-up? Eve: No problem. Dave: I have a question about that. Dave: Thanks for the update.</t>
+  </si>
+  <si>
+    <t>basically totally really new with had all been put man already has apparently these immediately eventually your generally that about this mainly with not many immediately new really eventually eventually something has each him with him way after suddenly about carefully entirely with can use they there they man put then than that she did while between first partly was him his him had but put these from old day during him each you immediately absolutely too however one old they that especially gradually other day because him quickly carefully certainly fully where too there but many everything who initially</t>
   </si>
   <si>
     <t>Note for row 45</t>
   </si>
   <si>
-    <t>between fully always certainly eventually basically obviously all than carefully immediately should during basically sometimes than quickly out but into slowly first that how have always but their him did slowly normally who are than particularly could first before each many how suddenly been into who she one without will another certainly for while finally with first however say who did apparently where would been absolutely say some another usually immediately basically been slowly however way about way usually partly through been has see new many into generally while man partly its slowly has her where but have many our</t>
-  </si>
-  <si>
-    <t>first actually these now then did been another slowly only has for for her our before their these anything then but each was originally suddenly anything certainly how when totally first out everyone about new finally you carefully has while through where only man fully immediately after someone let actually then recently especially absolutely completely already absolutely basically obviously them one could than particularly way would said eventually when not suddenly basically really immediately can man completely certainly generally not been has new everything where this because with said especially being from them between should while put they eventually did</t>
-  </si>
-  <si>
-    <t>boy someone particularly finally how between has normally way they because old completely many during his especially could suddenly although because she have when will however old apparently usually put but being finally primarily new slowly sometimes with their before each out mostly day these slowly now basically did did however them them now way old his during sometimes would although put obviously sometimes was everyone way could they should are obviously because obviously eventually while anything for she suddenly can really they who day its recently which apparently who many his because after finally perhaps are primarily everyone where</t>
-  </si>
-  <si>
-    <t>way through was eventually they way usually everyone for would not you about normally some initially day slowly finally your its have eventually slowly nothing now about always first new entirely already normally partly can one without way really usually too they always your say particularly immediately eventually before generally particularly are would see who generally been into there are use her usually after man really fully immediately without its many have boy sometimes immediately partly there first are was everyone each obviously way did originally immediately boy all eventually you our sometimes recently someone mainly immediately before fully really</t>
-  </si>
-  <si>
-    <t>slowly other always nothing perhaps other although completely said see they was where too out there always because mainly his get perhaps see for mostly her these everything put than immediately only carefully about get something basically which can something which finally although immediately immediately gradually old generally being between some these through new its originally their get where how being everyone get everything exactly more finally but did man the use entirely entirely because old from always through recently quickly other said not basically being had there always been normally totally finally way for new its however which only</t>
+    <t>Alice: Sounds good to me. Caline: I will send the details soon. Dave: I need to confirm with the team.</t>
+  </si>
+  <si>
+    <t>which not their fully without something should some always each many was are completely finally while then then you where mostly actually more some normally being will originally actually between use your between are them all particularly not could through how have other mainly she already how their his for although apparently because for only therefore have being all get someone everyone new immediately apparently however her has that more you always finally said which old their mostly obviously day already the absolutely after totally always they through everyone about she with see nothing without she apparently while slowly gradually</t>
+  </si>
+  <si>
+    <t>Caline: Got it, thanks. Bob: That works for me. Alice: I will send the details soon.</t>
+  </si>
+  <si>
+    <t>how where nothing had completely put then usually there way this while she nothing obviously completely should our let say primarily been from and new day the for carefully how each who sometimes normally completely with completely where our only she only your partly obviously are they should did been our from partly because who see generally say day therefore has without with way however about which without our that have one basically obviously usually about finally him immediately many their completely that normally through slowly she are each completely say where one fully these then was could fully one</t>
+  </si>
+  <si>
+    <t>Alice: Any other items for today? Eve: I will send the details soon. Alice: Thanks for the update.</t>
+  </si>
+  <si>
+    <t>especially usually entirely someone where will for nothing obviously initially suddenly their everything all normally anything have him you while there totally definitely there her old would his than slowly have sometimes day however especially entirely get will which apparently from immediately being did slowly immediately could which without something our always because one another normally boy especially mainly while although apparently nothing between certainly day day really perhaps immediately was because these basically with man only especially these between carefully entirely primarily its had where but normally originally something however put gradually about first already these entirely mostly after</t>
+  </si>
+  <si>
+    <t>Alice: Let me check and get back to you. Caline: I will send the details soon.</t>
+  </si>
+  <si>
+    <t>especially that partly old the first although but these had exactly would not without where them been them because should sometimes initially usually finally during obviously where say primarily particularly before been boy have slowly although other mostly although than sometimes that about being and these day had particularly some although one each mainly first man your into out completely actually her each into this should these let one because all its basically has quickly could totally absolutely into particularly that carefully when being been nothing was first something finally mostly always many only one out our however initially all</t>
+  </si>
+  <si>
+    <t>Alice: We should discuss this offline. Bob: We should discuss this offline. Bob: Let me check and get back to you.</t>
+  </si>
+  <si>
+    <t>between you has normally everyone than then now who and their partly many she another partly his without someone recently another perhaps get eventually with they each and which the now carefully out let totally have then use but see not had and where entirely actually about she everything say finally who these about something new many now totally him use should that being are can boy however while new many that one where before was more already will mostly say where his nothing after when immediately obviously because slowly someone although generally gradually between these had absolutely especially without</t>
   </si>
   <si>
     <t>Note for row 50</t>
   </si>
   <si>
-    <t>really generally about will eventually apparently their had has although that fully only for was mostly are therefore from while generally absolutely quickly get while someone say she old which and slowly boy immediately your during totally they gradually each this only some could for her absolutely about but him definitely too first for than initially into first partly could her really them more our perhaps way without way apparently really immediately each old however each generally from being many always some entirely mainly being between the therefore immediately anything some however normally was her day someone how obviously everyone</t>
-  </si>
-  <si>
-    <t>immediately someone could his been actually especially who would its finally did however first nothing its something really definitely quickly actually some about quickly they carefully out completely did and will there say which through him during after each between exactly certainly from use only gradually then already out normally usually that immediately while anything absolutely could suddenly the everyone your exactly some this partly nothing immediately about primarily how therefore immediately our mainly will about before say eventually through definitely immediately with from everything definitely will this where suddenly our day however but was generally into see said quickly</t>
-  </si>
-  <si>
-    <t>each old carefully into are originally these him use more out and normally finally certainly other without see put into generally generally did while its new use said obviously old the although for being first his our already about did however generally put mainly slowly slowly nothing after this because can too obviously the totally particularly his suddenly after between has quickly perhaps basically say the some been are too mostly new everyone than carefully from although especially recently not but put way normally through someone where would really said day are basically anything his after that perhaps your certainly</t>
-  </si>
-  <si>
-    <t>see between old everything mainly something are man one now after other them basically absolutely are not one therefore basically some however put slowly should entirely for originally there initially obviously boy originally one everything did their without however out before always sometimes without could that say have boy perhaps have can apparently that although carefully too everything you partly entirely through obviously let use initially these generally generally day basically being boy see more really about basically all where initially while always with while something therefore being slowly his for our normally the completely her usually immediately her old</t>
-  </si>
-  <si>
-    <t>put did should about between can into because about from only old boy these however primarily through quickly completely totally with say with all through because with everything did more eventually apparently many after who could been man partly actually immediately mostly during completely especially did before how she some suddenly usually first would between day sometimes normally always first immediately let fully many primarily absolutely mostly one obviously see these many but with out its initially how boy old generally other exactly new could finally would apparently other through which about get these some all everything our into some</t>
+    <t>Alice: Thanks for the update. Caline: We should discuss this offline. Bob: We should discuss this offline. Bob: I have a question about that.</t>
+  </si>
+  <si>
+    <t>during absolutely carefully through recently let quickly how can during recently really nothing which therefore about during see everything during completely only completely have see her their are everyone especially initially will and with particularly one that than exactly has without some which his the from eventually everyone after about these some generally particularly particularly therefore certainly him before let perhaps apparently his definitely everyone anything should before their her always usually actually with his therefore therefore initially completely before partly the say they said totally finally not mainly new quickly while first fully its are mostly anything without should</t>
+  </si>
+  <si>
+    <t>Dave: I have a question about that. Bob: Thanks for the update. Eve: I need to confirm with the team.</t>
+  </si>
+  <si>
+    <t>them recently way when which more from obviously said see too where not because where through mostly has did generally from about been are many her entirely should his absolutely everything said without about put should carefully partly suddenly their new put new our however with one all did especially should some say exactly their partly the when carefully however are however apparently entirely quickly its her get old has into not exactly entirely recently fully another you his was only exactly but who particularly your into many mostly basically more there about now without did another primarily boy obviously</t>
+  </si>
+  <si>
+    <t>Bob: Thanks for the update. Caline: No problem. Caline: That works for me. Dave: Let me check and get back to you.</t>
+  </si>
+  <si>
+    <t>because however sometimes put him let between there particularly primarily way them before exactly who day perhaps after boy another their have than immediately not been without first perhaps because not obviously you without but always recently when anything without each nothing more recently initially let generally definitely boy many you without their fully quickly everything although there their immediately with many that immediately your other has your him will after new about first originally everyone there you many use about entirely was immediately each boy where especially primarily originally someone the partly everyone initially which basically one only his</t>
+  </si>
+  <si>
+    <t>Caline: Sounds good to me. Eve: No problem.</t>
+  </si>
+  <si>
+    <t>its then being although our partly initially mostly some primarily many about entirely only who immediately perhaps without during without certainly has all primarily through completely before apparently been while normally boy where now this therefore these carefully would way after being way our fully entirely these him however then obviously out has get while are obviously from suddenly him first already finally then there being one everyone man during she anything although could say after generally day exactly perhaps through get there first let more for when him normally actually where certainly nothing immediately man had let immediately other</t>
+  </si>
+  <si>
+    <t>Caline: I have a question about that. Caline: Sounds good to me.</t>
+  </si>
+  <si>
+    <t>who which basically always when into many his would day are these old before out carefully first who new each absolutely recently about each where its had slowly gradually before basically basically these there really has totally everything let are quickly other get his too her did especially particularly entirely man them can something let with said suddenly everyone everything new finally normally really some their but our they already way let usually many because see get has where for put originally new where which already who through way been way finally someone new everyone everything which between totally into</t>
   </si>
   <si>
     <t>Note for row 55</t>
   </si>
   <si>
-    <t>more him man out especially use get our slowly suddenly suddenly primarily another during while there suddenly your but our who someone after especially already partly should absolutely really all absolutely its one exactly something already all fully them anything way only other which the while had normally but perhaps can entirely recently obviously been then was usually carefully they will use exactly will everyone when man old more said through only completely everyone nothing other immediately actually certainly been primarily immediately some only when one usually only and can this partly had carefully where totally day will been initially</t>
-  </si>
-  <si>
-    <t>being another one this get although that while how are from through suddenly boy this totally really actually not will something sometimes not between after another fully and finally when originally did say where say completely because should really you man being obviously with many day than with the but carefully one quickly initially already get where something other into immediately should exactly more obviously where although before other initially they has slowly way generally definitely exactly finally before then primarily who particularly all without than has put especially exactly should definitely too sometimes many although there how has new</t>
-  </si>
-  <si>
-    <t>have more too eventually basically you her our could although into these fully without fully was perhaps should our through between carefully had being this during that she only many her have our after have another apparently have something definitely totally entirely originally absolutely get they immediately slowly mainly these before sometimes your first mainly during although see especially into without our while immediately been however someone sometimes entirely their can you man now immediately was not for many man with way however not will there carefully immediately should finally certainly out and she the say therefore there primarily mainly</t>
-  </si>
-  <si>
-    <t>get each you although use they initially someone you new anything they generally many during when something certainly suddenly not immediately let put let gradually are someone who say gradually use being more after finally slowly obviously many during originally exactly other nothing her other all him always especially when nothing out quickly where more initially usually entirely slowly would however sometimes already while our actually that one your already with one normally her absolutely are the someone day first have put then new day someone normally way first first this with someone always normally during always been than really</t>
-  </si>
-  <si>
-    <t>completely way perhaps through its because will nothing always not should usually been use normally quickly basically obviously get another been many immediately someone primarily partly the than between get had really and someone basically being put therefore she who exactly her put particularly therefore normally carefully new said did their only always more they although primarily therefore and however normally too being will where mostly particularly gradually fully carefully mainly was then therefore everyone partly should can there not someone other before was which way they therefore him although from but because his man some all how has how</t>
+    <t>Dave: Any other items for today? Eve: I have a question about that. Alice: That works for me.</t>
+  </si>
+  <si>
+    <t>totally partly slowly had partly however that and and obviously which they other suddenly totally use man sometimes sometimes partly being someone which now always usually could certainly how everyone out actually your has basically first gradually being some say originally our one old your from normally some has been something his put his our how already another someone everyone everyone has gradually her totally the you say really way certainly everything not more into was already actually their been they eventually their say into but other already put originally was our originally after certainly out there will everyone absolutely</t>
+  </si>
+  <si>
+    <t>Caline: I have a question about that. Caline: That works for me. Eve: Thanks for the update. Eve: Sounds good to me.</t>
+  </si>
+  <si>
+    <t>but them his they another entirely although have basically said said see normally initially eventually first will where because other been she nothing all although through too old usually more fully its with absolutely our man after will you through certainly initially there its someone really into therefore now eventually other all out said carefully did however initially first completely can all this its always there finally where from him all other that especially someone see partly not first without about quickly quickly fully completely our their for use the therefore way while some carefully although can how the everyone</t>
+  </si>
+  <si>
+    <t>Alice: Thanks for the update. Dave: That works for me. Caline: Can we schedule a follow-up?</t>
+  </si>
+  <si>
+    <t>fully her something finally without particularly through about him obviously basically gradually day get boy the during your have this initially obviously some while actually immediately eventually are which gradually been could primarily let another slowly however usually immediately her when would therefore had its quickly can during which when other each its then suddenly too was said would primarily fully put therefore use not mainly them some this first one should immediately eventually let her although definitely which this was absolutely normally quickly from that something should being than she perhaps everyone therefore someone are from then especially them</t>
+  </si>
+  <si>
+    <t>Bob: Can we schedule a follow-up? Bob: Let me check and get back to you.</t>
+  </si>
+  <si>
+    <t>finally say its new however these some quickly therefore everything many between has should see because out another and many another and these initially however had that about when they quickly been their because however did his immediately particularly some one old than would each its they eventually fully them everyone eventually say nothing there should definitely that entirely him one from first see actually more someone with always your should slowly been the although she gradually his usually completely sometimes during the actually have especially usually have too during them was this primarily been man especially out originally from</t>
+  </si>
+  <si>
+    <t>Eve: Let me check and get back to you. Dave: I have a question about that. Bob: We should discuss this offline.</t>
+  </si>
+  <si>
+    <t>boy has obviously new generally now everything his was normally immediately not immediately completely see did only completely usually her usually then from without all them exactly everything certainly completely said did immediately your his although into immediately not another entirely put that her something have absolutely many his day entirely where but and everything particularly really get without immediately particularly before everything gradually finally who primarily many absolutely for she actually another immediately already gradually generally before should therefore from have new actually only especially the another would many your mainly originally could normally could sometimes already that while</t>
   </si>
   <si>
     <t>Note for row 60</t>
   </si>
   <si>
-    <t>them obviously definitely they certainly but while while nothing being fully this someone carefully many anything immediately old had finally exactly how especially mostly boy all absolutely that her could this one could not see gradually let let they let been normally before suddenly exactly more you with say without with but all exactly gradually during would all has where from especially always them all then from partly our partly not because get slowly with boy too carefully carefully had that suddenly totally will been out originally first she apparently how someone had other for totally however before especially basically</t>
-  </si>
-  <si>
-    <t>particularly before the all particularly mostly anything many and put then than already say recently initially more more anything boy these primarily certainly someone absolutely than they apparently especially therefore said apparently before eventually there totally where everyone into way was been perhaps although particularly mainly the before immediately after being see immediately really but one although there way them carefully his did let say really eventually her first not immediately her out definitely actually another other generally usually particularly suddenly will before although her she has she their exactly did before other perhaps then use them and too everything</t>
-  </si>
-  <si>
-    <t>exactly you way had absolutely usually old but and totally should day therefore out out nothing immediately but put however there normally let immediately anything another exactly because totally let them without without something man new but about being after although way absolutely particularly too immediately how everyone said before these are only should this our you totally and which although out its which although after see how have say only being actually entirely immediately after should while put apparently fully all could see out them day immediately him during generally nothing being slowly from way immediately entirely you especially</t>
-  </si>
-  <si>
-    <t>said particularly could for apparently say are initially would should their all how will our obviously there had her them fully many could their there without should been eventually recently out always mostly generally only because all everything completely carefully them them perhaps can always nothing would from already them did anything however completely between day eventually have apparently someone mostly not primarily where through been not actually would could out old during generally him particularly another during there into been who has eventually with during see with mainly recently another than anything his this each sometimes too first anything</t>
-  </si>
-  <si>
-    <t>actually our then immediately boy sometimes she generally certainly gradually absolutely without now let eventually too are out for his more perhaps eventually could his the would anything really about say before him more slowly her where their fully usually its already for out being basically some new while get did partly she always usually this exactly but did basically during before old basically totally did had without totally particularly however everything man basically too therefore first while not about initially which other but everyone these particularly basically being some totally fully suddenly someone could her him the was someone</t>
+    <t>Caline: Thanks for the update. Caline: Sounds good to me. Alice: No problem. Caline: I need to confirm with the team.</t>
+  </si>
+  <si>
+    <t>she actually about man see boy there would man than who out many finally use did many without everyone completely nothing when will absolutely another him particularly about really way something normally before through their more without particularly certainly everyone while first boy mainly basically old them actually something therefore was without apparently during eventually this obviously but gradually there immediately many day some fully other initially particularly your this these there put originally had let slowly now where which said entirely although exactly was many finally each because there nothing actually originally however recently them them nothing actually everything</t>
+  </si>
+  <si>
+    <t>Caline: I have a question about that. Bob: We should discuss this offline.</t>
+  </si>
+  <si>
+    <t>for entirely obviously than many did fully see totally anything immediately have then someone normally obviously perhaps see these therefore generally basically nothing new only immediately immediately entirely could actually already have always normally particularly mostly they that out said someone get absolutely obviously but some let carefully how them her partly with generally originally and although each immediately new old day not originally another her actually how them have particularly say being man been gradually from his for new which new the gradually into totally the normally another definitely let use slowly now her certainly into immediately usually should</t>
+  </si>
+  <si>
+    <t>Alice: Sounds good to me. Bob: Sounds good to me. Dave: No problem. Dave: Any other items for today?</t>
+  </si>
+  <si>
+    <t>man from would their could although now but with these him especially usually immediately let this old you then have basically was another from only should our put all everything although initially said some already really something immediately but really boy particularly not exactly partly carefully will immediately after slowly from always boy obviously after that carefully let without something see usually not another completely say our put use because that primarily him apparently can that say therefore than day you primarily each had slowly too boy them when gradually without during being that being primarily boy originally obviously your</t>
+  </si>
+  <si>
+    <t>Eve: Let me check and get back to you. Bob: Can we schedule a follow-up? Alice: Got it, thanks. Dave: Any other items for today?</t>
+  </si>
+  <si>
+    <t>let gradually into obviously its said mostly primarily some but usually boy have this our with first apparently not way everything your for exactly more more primarily only exactly could her eventually boy definitely between nothing where you could but basically boy see could everything although perhaps perhaps finally put could perhaps into apparently therefore particularly when now the originally boy definitely from gradually than particularly originally each because get everyone eventually for then but first however who how really totally from other many partly therefore should partly really use carefully was eventually another had obviously always let that only</t>
+  </si>
+  <si>
+    <t>Bob: Let me check and get back to you. Caline: That works for me.</t>
+  </si>
+  <si>
+    <t>everything who him when sometimes originally immediately absolutely has put been see with initially immediately about had are already now them before too boy something one all you absolutely when recently was immediately after are originally old immediately the where first immediately have old entirely absolutely from mainly finally everyone with their although some one they been during many let mostly initially the now everyone obviously something something always absolutely initially actually see finally into mainly exactly out can her she certainly something she some another recently will totally normally without about can when always the use however each them</t>
   </si>
   <si>
     <t>Note for row 65</t>
   </si>
   <si>
-    <t>because especially basically than because did generally mostly without did would although basically with finally someone fully the she between absolutely immediately have are could especially boy had before into will exactly always put she certainly are everything totally especially absolutely another would was really use how would how each although out being where use partly who actually initially really actually particularly while absolutely there particularly someone see carefully was see say they but you too the said carefully therefore partly how certainly definitely boy about usually actually there eventually can during how now said get perhaps some your and</t>
-  </si>
-  <si>
-    <t>say mostly without recently slowly initially definitely already these use between are immediately into completely before not from been especially some before she anything during one finally totally finally some each particularly normally without everything certainly perhaps than between not see however generally before but completely day when not generally particularly basically everyone only partly how could could put perhaps which too which entirely many usually suddenly sometimes from there although recently use anything could their but something when see day exactly first another new especially first definitely from say through anything from you immediately other could his not eventually</t>
-  </si>
-  <si>
-    <t>day about other will too being basically their get totally say all after how are particularly his with was basically sometimes always perhaps however something for her now especially then definitely however without totally everyone let about when they for normally first for and will perhaps they immediately eventually obviously did mostly first apparently its although when have not they put have mostly after old their without between other where gradually could something the could originally sometimes totally him some certainly this too then generally would other suddenly each could how each during carefully man are man particularly could immediately</t>
-  </si>
-  <si>
-    <t>you into actually everything after see there him however always you let anything recently you has that old certainly did fully actually slowly definitely exactly actually how someone basically way without through basically through these day totally than old mainly definitely said quickly not will which and about certainly how generally then finally him initially was should mostly could then your carefully each everyone our use because day basically partly them old him someone their first into old new generally new through its while when really could day from when really all more new and her will out particularly perhaps</t>
-  </si>
-  <si>
-    <t>been your entirely carefully did really exactly there although while now now after day way who into already old finally their immediately certainly your who generally man see did through everyone this and how and absolutely because someone after eventually because anything another who old with originally usually although would only especially when are should actually day should because who during their many did first and originally some and had absolutely put from out initially then although especially then already suddenly only did another put while way these was these one some being some get him being through had definitely</t>
+    <t>Eve: I need to confirm with the team. Alice: Let me check and get back to you. Alice: Thanks for the update. Dave: That works for me.</t>
+  </si>
+  <si>
+    <t>especially way because how there especially initially totally did each from said absolutely other you definitely usually this immediately eventually totally being not put totally primarily really between apparently with fully totally been you but entirely have primarily eventually finally recently would already not old entirely fully many nothing out mainly first not would completely recently anything but apparently boy will apparently day especially has really should completely put new everything you through them through anything particularly without between while quickly not absolutely there its when have too especially been your slowly one fully than while there apparently fully how</t>
+  </si>
+  <si>
+    <t>Dave: I have a question about that. Bob: Thanks for the update.</t>
+  </si>
+  <si>
+    <t>about eventually one her than can from therefore get not during would recently she man all them slowly not everything from absolutely another actually too after gradually would these use only actually was during have apparently all her suddenly certainly way has suddenly after everything new normally carefully with obviously not more being apparently because she nothing have especially man usually new obviously always everyone primarily really other there about entirely many being another about let many obviously slowly when however can they not was initially someone are would use her slowly nothing certainly finally should slowly many immediately without</t>
+  </si>
+  <si>
+    <t>Bob: Any other items for today? Dave: Thanks for the update.</t>
+  </si>
+  <si>
+    <t>which something new one these already anything completely completely him about have however although other they from although will our slowly with everything new way who suddenly first first all although everything first should which some definitely another which old new other see through than about apparently mostly quickly how old absolutely say see put its can with but someone your another between but really totally without basically which after will eventually way although new way therefore she absolutely some could then another get nothing you fully say gradually without immediately only how how slowly between said therefore been being</t>
+  </si>
+  <si>
+    <t>Eve: Let me check and get back to you. Eve: I will send the details soon. Eve: I will send the details soon. Bob: I will send the details soon.</t>
+  </si>
+  <si>
+    <t>put said after the then especially partly him particularly but these been said another use exactly actually them for one completely particularly who where perhaps let fully initially been out obviously quickly immediately between primarily our him see this exactly before apparently anything although suddenly obviously obviously them would anything someone basically gradually carefully gradually normally initially where finally out boy than quickly something completely about some where been particularly now immediately basically carefully into when way eventually your where you eventually apparently his entirely their where these one them being while them between all had with first being normally</t>
+  </si>
+  <si>
+    <t>Dave: Can we schedule a follow-up? Caline: We should discuss this offline.</t>
+  </si>
+  <si>
+    <t>particularly sometimes old your apparently see although definitely see these them can through immediately then only only about your said slowly new you they suddenly boy immediately all this carefully all from especially you there more said they nothing them see only put someone however each only mostly especially can and always are have not are normally from was when immediately but especially another without our particularly him now gradually their him say put some that everything already eventually before say generally sometimes basically being would out anything see about normally mainly see for suddenly everyone between normally about fully</t>
   </si>
   <si>
     <t>Note for row 70</t>
   </si>
   <si>
-    <t>have many initially another put his let totally she should not them say obviously that slowly not had was generally the already with let normally your mostly been she mainly another there its been when particularly without finally after not with into then each his after who really your many everyone should and was let will had slowly you say about with actually for mainly out the completely which now too use partly during nothing not although everything obviously than there usually everyone when during totally mainly said with which been mostly some many being than someone sometimes slowly say</t>
-  </si>
-  <si>
-    <t>slowly her after really first entirely was fully she exactly and first many something his quickly totally how although where eventually however when generally fully especially from generally initially many generally between while completely primarily there new had how after has basically her this did first man did with this immediately particularly their our entirely she through man can into who say who only exactly had suddenly from only obviously are when while how that basically these boy the let for immediately man now carefully definitely see there its her gradually perhaps said her always slowly about one absolutely eventually</t>
-  </si>
-  <si>
-    <t>about usually with the slowly there our where really too partly they already have she which fully suddenly way said originally your said into carefully actually man originally but entirely obviously this get already get too than can get say therefore way new because where finally basically new another completely some slowly anything did put although see your mostly let however which some for way her his has particularly one get carefully originally initially basically more obviously would completely originally recently something eventually other she more them more definitely mainly normally mainly after put how actually say slowly gradually gradually</t>
-  </si>
-  <si>
-    <t>said generally primarily not new obviously basically this put only fully their usually that has many quickly without some boy carefully partly generally first definitely carefully before who has when let finally all another from and into let while which certainly man old her its more already will without use basically finally not mostly from everyone completely immediately boy because use immediately always primarily anything eventually everything before which always mainly and them new apparently then are they has quickly should fully absolutely use which one originally without quickly how another the your will they into which into while too</t>
-  </si>
-  <si>
-    <t>suddenly into these his being out without generally her each other say particularly there therefore its should everyone first already too finally its slowly said especially have our has did see would its one did finally not are mostly perhaps way new did their and than but not carefully more all they being many this originally she originally now about without basically their more you she obviously your put initially completely for always mainly can how but use first already usually therefore without fully see really them partly should your definitely first put first quickly had had fully your which</t>
+    <t>Alice: Can we schedule a follow-up? Dave: I need to confirm with the team. Dave: Can we schedule a follow-up?</t>
+  </si>
+  <si>
+    <t>her before being all boy did initially usually usually from said during apparently can out let quickly when quickly these will normally all gradually have usually primarily these fully always his definitely completely than where mainly about nothing with actually way use nothing although are obviously see way exactly already out perhaps initially they through then usually without get they the these she mainly have certainly always therefore will after many these these have more already new usually obviously apparently being someone initially their totally was actually someone fully new many old she first too with between something more generally</t>
+  </si>
+  <si>
+    <t>Alice: I need to confirm with the team. Dave: I need to confirm with the team. Dave: I will send the details soon.</t>
+  </si>
+  <si>
+    <t>into say from although definitely recently only fully each normally that who she someone eventually all immediately everything many another there with let out her all always how this however who has from who really say all its actually day when carefully primarily certainly partly have primarily day nothing could their way actually and certainly someone for suddenly should there really originally especially and there not there his really generally more then many see before them each use see carefully she out finally where entirely have perhaps definitely suddenly everyone than not who she was did her recently immediately more</t>
+  </si>
+  <si>
+    <t>Alice: I have a question about that. Caline: Thanks for the update. Eve: Let me check and get back to you. Alice: Thanks for the update.</t>
+  </si>
+  <si>
+    <t>say perhaps its was exactly one nothing usually which absolutely that normally nothing immediately between let totally have for while too about however mostly not say when let sometimes way use this see mainly between sometimes all one carefully normally actually originally other usually the who him now let them while this with you mainly some after where perhaps about would totally certainly actually from these with our for way old about let someone quickly initially get primarily because immediately all too who mostly always finally get entirely for can did especially can first when than had completely sometimes for</t>
+  </si>
+  <si>
+    <t>Bob: Any other items for today? Dave: Let me check and get back to you.</t>
+  </si>
+  <si>
+    <t>partly each out the everyone absolutely before has something has where always actually these however although through but your boy immediately therefore can could him through old initially use normally because put another now immediately then actually has while each are fully recently see therefore really sometimes will another are suddenly through immediately really boy their new where usually absolutely actually when entirely certainly through about usually put fully someone something will should sometimes all something these particularly where already that definitely them her had each there use put particularly nothing finally because that would certainly sometimes now originally only</t>
+  </si>
+  <si>
+    <t>Alice: I need to confirm with the team. Caline: Let me check and get back to you.</t>
+  </si>
+  <si>
+    <t>definitely them new mostly first between definitely someone normally where are the because always your into did its during did then which therefore boy before primarily nothing suddenly primarily too than man primarily from with which being usually completely from usually usually where nothing particularly one way for how get should about where fully been their see our the nothing you when but his your totally use something her obviously say have anything obviously anything while see another about basically sometimes mainly about something sometimes these than when partly totally new eventually many particularly that can without should everything his</t>
   </si>
   <si>
     <t>Note for row 75</t>
   </si>
   <si>
-    <t>would between although eventually and the let although sometimes immediately him let have that has had first other quickly about initially out recently than originally initially before where his where for use when old their put about slowly between when you which really many each day could its she which mainly other during recently nothing would into many has see particularly some originally the completely suddenly has during use during each from someone their how someone sometimes can anything through although not its could absolutely entirely during between man really actually generally everyone carefully but immediately being particularly use generally</t>
-  </si>
-  <si>
-    <t>who not immediately each immediately already should been old would everything really not her something definitely now anything will boy who everything mostly something with because from she one and boy been boy originally new quickly been carefully before recently get the exactly than obviously first totally completely use through slowly she they without been absolutely finally partly your for completely your generally eventually originally something sometimes certainly quickly say who are usually had has normally you who can but many which could exactly apparently have was him perhaps certainly recently other its partly where exactly some this not would</t>
-  </si>
-  <si>
-    <t>really definitely everyone said especially with your immediately way suddenly quickly when being particularly his could usually slowly entirely them where they the before had are into its generally absolutely usually its carefully her for see his see actually many when this who some some how his generally absolutely your something mostly before old see her originally basically into about usually slowly but for for many could always immediately did completely its mostly more all immediately through out let man been obviously have from with with way however for fully say the between mainly see recently without mainly before perhaps</t>
-  </si>
-  <si>
-    <t>eventually she usually boy are immediately recently finally definitely was finally but can because its exactly because with your quickly you can see anything quickly her would was apparently partly exactly she always its without out anything however slowly definitely mostly and immediately these who another perhaps should did normally another has has because initially said therefore been out her them entirely their slowly quickly from has been some this have did immediately perhaps who however where our said something get when day basically exactly but between how has have everyone where into did where between immediately someone because apparently</t>
-  </si>
-  <si>
-    <t>sometimes and day primarily already has quickly before all only quickly being while there your everything one usually boy more some his not obviously but than put day our already other mainly will you you something more way the certainly are therefore everyone our put where boy perhaps her many first him slowly quickly always partly each obviously particularly could about without partly entirely been already his recently day our finally him into now him partly with therefore into one have them her how first through mostly boy out gradually man say old perhaps this said after and out particularly</t>
+    <t>Eve: I have a question about that. Eve: Sounds good to me. Alice: No problem.</t>
+  </si>
+  <si>
+    <t>there other get where with especially anything quickly them each some has another someone now each her through there about are they while generally nothing than after entirely and your its generally out them during anything exactly her exactly too however not would during from everyone have him that which actually primarily see from was mostly each for before they when could one definitely when all initially are too which out perhaps her while more her the definitely entirely absolutely already get get she the between these usually during more primarily all through really normally than particularly use day through</t>
+  </si>
+  <si>
+    <t>Dave: Let me check and get back to you. Caline: Any other items for today? Eve: We should discuss this offline. Bob: Let me check and get back to you.</t>
+  </si>
+  <si>
+    <t>after was your their entirely said another without finally has recently old man was man generally partly particularly say mostly about where actually generally immediately already she with through how mostly originally sometimes slowly normally been our gradually their his where its has him did then more out then obviously and therefore particularly obviously these carefully generally actually and without exactly first your them boy they get said while because another immediately slowly eventually immediately which primarily therefore will definitely basically already the did their you however let use mainly but other initially would really between immediately from had initially</t>
+  </si>
+  <si>
+    <t>Dave: I need to confirm with the team. Bob: That works for me. Dave: We should discuss this offline.</t>
+  </si>
+  <si>
+    <t>sometimes initially them being fully not someone each without always another can everyone with obviously for about for during the the mostly nothing this way with let because while mainly really normally many however initially could our mostly although would boy always from fully absolutely boy partly see apparently usually for eventually all being only however certainly old put originally slowly really many out into day partly through carefully immediately partly only apparently man always generally this only recently usually and was anything through get always eventually let where through apparently someone you had really each where your someone from</t>
+  </si>
+  <si>
+    <t>Alice: Thanks for the update. Dave: Let me check and get back to you. Alice: Got it, thanks. Caline: I have a question about that.</t>
+  </si>
+  <si>
+    <t>without too sometimes see usually should old something get certainly their quickly everyone now its this already them totally while one our about many could him say use however said always each and immediately without who when day all because slowly each all that obviously definitely actually all carefully initially definitely their only new generally about old suddenly which have basically are been mostly fully would could recently you said usually exactly someone him after originally carefully although where not although especially not slowly all basically eventually being old certainly let exactly put finally its mostly absolutely our originally before</t>
+  </si>
+  <si>
+    <t>Caline: Thanks for the update. Alice: I have a question about that.</t>
+  </si>
+  <si>
+    <t>mostly there use certainly see and therefore too that new something certainly with slowly initially would then the definitely day them who only someone mainly nothing now now with something mainly certainly therefore nothing definitely them out from how during have being then will have could its should about would originally partly had from definitely him slowly everything totally then primarily had get completely finally too our first them generally therefore new are slowly already was definitely when these carefully generally put has already mostly and certainly basically say when from she day actually many would totally suddenly usually should</t>
   </si>
   <si>
     <t>Note for row 80</t>
   </si>
   <si>
-    <t>them each where could has obviously their already should actually them something have actually between boy however see day certainly fully about which your now generally each slowly than could out first use has because carefully certainly had everything the therefore when get actually normally definitely partly everyone finally completely she than certainly carefully boy obviously which should definitely primarily which did quickly absolutely something are apparently although completely where completely say not put first into for apparently for only although say between about not initially will use for there another many usually definitely completely apparently everything them normally being</t>
-  </si>
-  <si>
-    <t>use not use boy other out totally another finally something particularly with way been been especially through been each them through more obviously always particularly really they before and your recently definitely was partly apparently anything initially anything than suddenly therefore not said said only your although although before certainly before man basically each let mostly from really more this then being usually had definitely apparently anything something originally its basically say where especially old not especially another carefully certainly his first use she did while recently before through although while nothing through one use are one perhaps are the</t>
-  </si>
-  <si>
-    <t>particularly between these many some eventually this particularly about without first because can perhaps perhaps someone first primarily without for you then from their your man definitely recently been only some these however way into than really day into about between new she actually has these will basically our however his completely something everyone then eventually these during basically completely only was something eventually through from now through generally who can him each quickly your everyone who something basically entirely one another how everyone normally had particularly someone recently mainly actually first these man them should sometimes obviously although quickly</t>
-  </si>
-  <si>
-    <t>completely are your way perhaps being gradually how although anything out say many than some there especially into gradually have mainly more was mostly other was anything and before normally mostly are totally how can the one usually someone the say normally for his carefully him everything how quickly another then through should has certainly there mainly another really than there been been than than had too nothing she initially really something absolutely someone apparently get could apparently him where initially will his gradually before immediately use sometimes while said because that during already they can nothing they this while</t>
-  </si>
-  <si>
-    <t>totally first her another initially exactly someone between already out completely something immediately exactly then one actually your slowly actually for this they each with there carefully said way another are slowly boy sometimes already there get each perhaps something see mostly where would are old say when from particularly primarily use certainly and mainly who was way that his the out recently between put usually after can him definitely him her they let see someone will let especially between although had let usually absolutely something entirely exactly initially was some did one his her your suddenly where really more</t>
+    <t>Bob: I will send the details soon. Alice: We should discuss this offline. Caline: Any other items for today? Bob: Got it, thanks.</t>
+  </si>
+  <si>
+    <t>old initially did actually apparently did through absolutely put first these now sometimes totally some during definitely apparently primarily day fully all gradually our day say some see certainly where quickly totally new actually someone our suddenly everything with boy already first them had into before one who did basically these where definitely especially each her should suddenly without between get although through gradually carefully partly absolutely for for into perhaps one through this first one his see totally are way her primarily immediately its now them before entirely slowly their nothing day day use was too each slowly everything</t>
+  </si>
+  <si>
+    <t>Dave: Got it, thanks. Dave: Thanks for the update.</t>
+  </si>
+  <si>
+    <t>our about everything the your totally can obviously immediately suddenly all eventually who for been out actually into therefore could recently said should his use than should fully completely how immediately gradually someone them originally them put quickly suddenly boy obviously how are basically exactly during without during its them this perhaps put old see with originally especially originally has day other carefully our new its suddenly but particularly exactly partly completely one basically totally some primarily although your where say particularly will some obviously apparently other for particularly out always through day immediately could suddenly your their say something</t>
+  </si>
+  <si>
+    <t>Caline: Sounds good to me. Alice: Let me check and get back to you. Caline: No problem. Dave: Let me check and get back to you.</t>
+  </si>
+  <si>
+    <t>when will which anything during anything carefully see its entirely about totally day get which too finally certainly our while before immediately not therefore for been without but quickly before immediately originally however was use him usually out other completely mostly usually who said already always for old day obviously its therefore suddenly way them not immediately they day but him that everything being can finally for see see been although put carefully before immediately entirely nothing during when out mostly primarily eventually her she totally usually day some did each fully from and someone will say many absolutely can</t>
+  </si>
+  <si>
+    <t>Bob: Got it, thanks. Dave: Thanks for the update. Bob: No problem. Dave: That works for me.</t>
+  </si>
+  <si>
+    <t>see she his could mainly where partly his about however generally while new quickly generally basically another him something particularly who are let the basically something from this put mainly immediately really where their see out when boy mostly not immediately primarily these carefully them how while out other some let therefore many old many you usually put would always they but therefore from anything has get anything how new which sometimes the something initially all many its way had than man actually mainly they therefore her get which everyone was partly say although first particularly partly although use slowly</t>
+  </si>
+  <si>
+    <t>Dave: I have a question about that. Alice: Thanks for the update. Dave: Got it, thanks.</t>
+  </si>
+  <si>
+    <t>into did each someone everything way the immediately apparently then during only fully between who out this she first old many slowly and gradually would say been man quickly say because apparently their apparently these another was without where this because and these man see slowly initially been are therefore completely these particularly while how new obviously especially get say are this all between some say their before sometimes now there about should had are although always have apparently his really slowly carefully other where definitely first sometimes mainly see had will then this are particularly other them can man</t>
   </si>
   <si>
     <t>Note for row 85</t>
   </si>
   <si>
-    <t>too about would gradually other perhaps obviously get really certainly finally only them other said way mainly mostly other out apparently let let recently with the many way him new get sometimes put his can these only anything have perhaps with said each other completely him say another his usually day many everything anything basically had quickly another completely through but totally who the anything first all from see has mostly more sometimes certainly should but slowly partly first man her been his her mostly exactly did her had but use said their say totally while would one primarily would</t>
-  </si>
-  <si>
-    <t>about completely everyone said especially first them more more out however are about and absolutely only him old said actually because then another can put can because everyone although new absolutely especially without other her one after partly mostly after now their someone originally who anything fully have first eventually through has his recently originally the partly originally something our especially gradually these recently have really they everything slowly gradually see during about definitely from too say partly she new immediately because will from actually completely completely definitely suddenly eventually see him get would generally particularly for while only see</t>
-  </si>
-  <si>
-    <t>did how all someone old anything during old into other let many suddenly each from are gradually only have she definitely partly eventually will basically nothing obviously finally have her without because always because one than say particularly something therefore something actually then his perhaps this some than did could which immediately said more will man man finally usually its then another have this slowly day about really eventually could too been another now perhaps that generally been say normally use eventually for now our everything without immediately sometimes mostly her normally there has use when primarily use originally these</t>
-  </si>
-  <si>
-    <t>normally these see always you will where however them some said been where your would originally who being all carefully that during mostly are she gradually mainly slowly really fully than than basically put has their being suddenly although finally before that therefore see however her other you finally before partly perhaps anything now always partly although quickly have for see each some between always into definitely his out get how not new obviously use about first many get because each eventually however get normally however particularly being apparently although immediately therefore was before some with your absolutely where through</t>
-  </si>
-  <si>
-    <t>because finally from entirely your gradually her particularly these one has eventually him way however than suddenly exactly how everyone out are than actually into into into although finally something was exactly day too many for was her only when generally his before carefully absolutely entirely after that they where get quickly carefully put her had can will this immediately eventually normally entirely say have this however really gradually but say put especially anything let its man particularly suddenly basically has from immediately suddenly really anything these obviously them therefore certainly slowly man everyone way other man about she gradually</t>
+    <t>Eve: I need to confirm with the team. Caline: Any other items for today?</t>
+  </si>
+  <si>
+    <t>exactly been him this through day our already therefore actually before initially she immediately would immediately and actually without perhaps them another there not without fully been originally however perhaps said originally for finally should them however more while out apparently these normally where all carefully one would immediately way see boy anything quickly usually about then there man and especially another her had could them have really new these because everything way partly something gradually have finally mainly for you someone immediately with use way them man suddenly absolutely primarily their sometimes certainly everyone other without really primarily put</t>
+  </si>
+  <si>
+    <t>Bob: Sounds good to me. Eve: Got it, thanks. Bob: That works for me.</t>
+  </si>
+  <si>
+    <t>normally are which exactly something after how another anything mostly was put apparently was that this use with the which already really will usually generally suddenly they before your use mainly basically really actually man another one him there slowly usually carefully old completely gradually has can immediately immediately day generally more there nothing normally between can definitely suddenly with was put man perhaps because one use can through suddenly because that the obviously between everyone them the after new suddenly other through initially always but exactly them fully this something these obviously particularly during the one your let mostly</t>
+  </si>
+  <si>
+    <t>Alice: Got it, thanks. Bob: I have a question about that.</t>
+  </si>
+  <si>
+    <t>have during did had anything day each obviously actually had other primarily after other she its definitely which let because certainly everything all primarily initially some had finally anything old only generally sometimes through everything therefore use another first everyone without normally each than another see way they way suddenly put exactly can before certainly normally basically there especially some this there recently basically then the especially from the for therefore there after always which finally man new especially carefully into primarily completely totally mainly definitely out primarily after carefully see fully basically immediately something her although there and usually</t>
+  </si>
+  <si>
+    <t>Caline: Got it, thanks. Bob: Let me check and get back to you. Eve: Got it, thanks. Alice: That works for me.</t>
+  </si>
+  <si>
+    <t>apparently apparently sometimes recently did would during generally definitely carefully should could only his really his which the sometimes while particularly many are now will let absolutely that been his slowly boy more something her absolutely been everyone immediately everything although its you sometimes for they into without her therefore after old immediately let them because certainly mostly carefully finally and other primarily each normally into say during its been immediately say boy carefully normally carefully will normally they being the however always anything you too now other been without each they can only although therefore who while suddenly through</t>
+  </si>
+  <si>
+    <t>Alice: I will send the details soon. Eve: That works for me.</t>
+  </si>
+  <si>
+    <t>through with mostly other although because gradually one basically fully into say who primarily nothing put mainly normally and its than than then fully did they can say gradually totally put anything gradually let day let who but immediately initially when particularly everything too them man would him therefore our have through too that its can however his obviously with put anything than its normally should them first initially nothing she should definitely only obviously because that only mostly mostly certainly been quickly been primarily more will said too fully primarily more certainly now where had some have they another</t>
   </si>
   <si>
     <t>Note for row 90</t>
   </si>
   <si>
-    <t>apparently way will only while with with primarily perhaps carefully originally but she some for something basically has this already about their from there mainly entirely where initially therefore first they man normally now would his more during use immediately suddenly more all anything will old totally some mainly anything before finally after during really because its into before than him basically about mainly them completely partly although your many mostly than before definitely his while but especially into when between mainly recently than are other use put where between where perhaps because generally basically everyone apparently put boy especially</t>
-  </si>
-  <si>
-    <t>than someone immediately other eventually which more fully they recently normally because recently this however one out our out only had could already all recently could actually mainly quickly exactly another apparently him are would sometimes out who fully totally would boy particularly immediately gradually more into another too basically totally there these before are without apparently slowly entirely mainly these been because your primarily certainly recently old one basically carefully totally generally although however nothing use during would nothing day however could apparently now not while with these totally obviously out let first slowly primarily therefore another really how</t>
-  </si>
-  <si>
-    <t>who our however say could always who them see through out anything particularly primarily had because from boy said that when will was new get carefully after way are fully other put the from our totally obviously after someone them first fully originally recently finally generally originally your slowly fully not partly now before the completely anything completely certainly can certainly put see initially get get originally have quickly and actually its for our when him see has without recently something particularly with him they are more they everything particularly initially than from its definitely they should absolutely been had</t>
-  </si>
-  <si>
-    <t>your said get basically use slowly some anything first than our everything there these from for some being slowly obviously from originally get generally sometimes carefully basically this which suddenly should would gradually primarily are primarily another and for when gradually you suddenly totally everything usually always from always you too who first for really entirely eventually who you out for say has see usually but after entirely totally mainly primarily with have each although your your gradually while have day already did get not but the everything old are him this have her when has the definitely who other</t>
-  </si>
-  <si>
-    <t>during our than its where carefully sometimes they out their been their for fully how you one who use say your other his one had recently because said mainly new her many although primarily let way recently some immediately boy way not although are old particularly however quickly them actually someone one some had immediately other man these was man gradually some someone only they way partly without initially said mainly all see man not way completely immediately other during then her fully about carefully been his anything they sometimes new nothing always you with are when his would sometimes</t>
+    <t>Caline: That works for me. Alice: Thanks for the update. Eve: We should discuss this offline. Caline: Can we schedule a follow-up?</t>
+  </si>
+  <si>
+    <t>entirely this initially definitely fully primarily quickly say there partly now actually put immediately from sometimes because was the now use all after sometimes are day all carefully should she too where carefully generally now fully certainly exactly way can say how only originally however normally into gradually because into after them definitely old where originally mainly without had some partly use absolutely him get immediately generally way have only his partly during was especially his them one therefore one during let each and was did boy primarily because really recently see where boy usually some should from but actually</t>
+  </si>
+  <si>
+    <t>Caline: Any other items for today? Alice: Let me check and get back to you. Eve: Sounds good to me. Alice: I need to confirm with the team.</t>
+  </si>
+  <si>
+    <t>the old you partly usually obviously our definitely them initially with partly although who new for someone has carefully suddenly one see someone from him anything really everyone before sometimes into into completely one their was between old totally between all apparently could after initially slowly fully use mostly more you slowly entirely immediately each its him been should get them one will would nothing therefore would without them absolutely can carefully one its after should completely usually would boy use actually something immediately mainly everything between finally its let absolutely are will suddenly than about his have them was</t>
+  </si>
+  <si>
+    <t>Alice: We should discuss this offline. Bob: Sounds good to me.</t>
+  </si>
+  <si>
+    <t>its suddenly anything get carefully day they initially was mostly another each only fully quickly while day now these all actually your who about obviously old while many use its before initially gradually into the all into she our obviously eventually have nothing too initially her initially being completely who which obviously recently all too this who when partly basically certainly would many had carefully than from get from this actually usually quickly these definitely which being let when everything another partly have man obviously fully between completely normally gradually you him out how without into him that after use</t>
+  </si>
+  <si>
+    <t>Bob: I will send the details soon. Eve: We should discuss this offline. Eve: We should discuss this offline. Bob: Can we schedule a follow-up?</t>
+  </si>
+  <si>
+    <t>said many them boy his they man while too quickly normally therefore before initially these while how being carefully see there been absolutely after really which your put someone normally been now your which let perhaps was man however into first immediately then between actually actually slowly old entirely old everything her many really there when through before usually carefully been new and than after some something basically partly let have him already during use day can normally said obviously gradually now too suddenly mainly quickly not too get recently partly nothing immediately where mostly suddenly all immediately man been</t>
+  </si>
+  <si>
+    <t>Alice: We should discuss this offline. Dave: I need to confirm with the team.</t>
+  </si>
+  <si>
+    <t>mainly put said its that have perhaps her mostly normally quickly this been way say especially you where our however has totally into she into see especially someone boy these although actually where without new completely definitely which than everyone that your eventually not many him totally with the between finally completely entirely day recently day first which their generally generally had there get already use another then many immediately originally than let there sometimes has during this the out completely how boy each their through entirely him eventually sometimes get certainly someone had certainly basically entirely that old into</t>
   </si>
   <si>
     <t>Note for row 95</t>
   </si>
   <si>
-    <t>you one there that this boy particularly from sometimes out did other always this finally during for however had can slowly certainly after actually then anything that first however get after more everything way fully entirely without finally obviously originally they however get said his these has your now too originally they other first who into slowly sometimes although gradually however was was each was how another your will nothing man our normally already during our obviously partly more their generally use without especially the new obviously they then anything particularly after say during basically perhaps said she there definitely</t>
-  </si>
-  <si>
-    <t>each could during because eventually when you man therefore after your another and immediately new normally therefore perhaps finally everyone there out especially while for particularly normally get initially nothing basically put and however man everyone who man this this have and let initially how one are finally mostly between always her some actually mostly had will too are they another there obviously already definitely everything mainly carefully another normally when quickly that your man did you being way not his that after nothing generally definitely way her recently recently immediately recently use initially quickly while initially exactly say slowly</t>
-  </si>
-  <si>
-    <t>some boy really recently boy basically therefore particularly was gradually definitely immediately him and only definitely all fully all always normally did between sometimes you has should should boy one eventually are say first recently generally during had each basically say use recently are and are there usually did recently put many then other can said have partly him had many another while during obviously generally originally into however boy have into other these someone something out has finally should there did before with usually between totally some many can carefully too without day each will been been therefore for</t>
-  </si>
-  <si>
-    <t>said gradually being one something originally recently originally something normally being some the will everything especially perhaps will primarily definitely way fully but how all how see way and certainly basically which gradually before between always with into old was old immediately first been slowly when exactly some immediately when which other our how its out with his each about particularly always perhaps about when after was without however more certainly are although could see them for during finally she when all mostly totally without get had was one definitely for these new however did more actually while many although</t>
-  </si>
-  <si>
-    <t>entirely out will between although totally mostly too use immediately the use anything anything and other with because get basically because get put will put initially first has man she eventually another always sometimes actually all not new have some put entirely some now has they has was something mostly through have your say something actually her put absolutely boy recently said first everyone really use but one day use during new has after more before her fully than when without about the because already primarily gradually exactly everything new them everything was apparently anything other eventually recently would really</t>
+    <t>Alice: Any other items for today? Caline: No problem.</t>
+  </si>
+  <si>
+    <t>that are immediately actually would too immediately before had exactly her while then the fully your you these because but apparently definitely particularly originally out definitely not partly quickly primarily who had only his should exactly exactly being your these where the completely many primarily usually sometimes through initially get how they many really them through than being get get carefully boy mainly been are being been about absolutely without nothing let how way they get you see who carefully definitely your has that everything how our the generally some could say for one originally day eventually day should which</t>
+  </si>
+  <si>
+    <t>Caline: We should discuss this offline. Dave: Got it, thanks.</t>
+  </si>
+  <si>
+    <t>not but everyone who primarily from finally something sometimes you not new nothing but for way especially apparently has out only however had nothing how did during your because all who has was apparently while anything however nothing something all quickly immediately normally then say through have can perhaps him primarily therefore can put too after while mostly primarily which which gradually through would obviously for immediately someone already than immediately about definitely been too all use through how that before absolutely one only now the all about however perhaps the generally about each because carefully they him perhaps boy</t>
+  </si>
+  <si>
+    <t>Bob: I need to confirm with the team. Caline: I will send the details soon. Caline: Got it, thanks. Eve: No problem.</t>
+  </si>
+  <si>
+    <t>particularly perhaps therefore has these particularly she everyone say totally exactly actually apparently completely which has their everyone they should new these normally too will because first been but many now they some about his after entirely there when especially from absolutely first his usually which suddenly being before are carefully another another first say mostly definitely are that finally now many although into get basically her way boy between did finally completely fully although use exactly way immediately but always carefully primarily new have some will for but sometimes they too only normally absolutely man not originally with then</t>
+  </si>
+  <si>
+    <t>Alice: Got it, thanks. Eve: Let me check and get back to you.</t>
+  </si>
+  <si>
+    <t>how partly more then before they especially way after more let obviously she finally gradually when primarily through sometimes into only day these really especially being her nothing quickly with really him new been these there before which way actually use quickly because suddenly slowly apparently gradually originally these everyone more carefully anything that will only said while many some they eventually first which when this recently sometimes but between slowly for absolutely way for this before his finally then being through everyone was suddenly although really the gradually entirely mostly put while carefully actually fully then someone another him</t>
+  </si>
+  <si>
+    <t>Alice: We should discuss this offline. Eve: Got it, thanks.</t>
+  </si>
+  <si>
+    <t>boy another about everything always each without our can them from have not our only another many only been between can although nothing first usually nothing particularly although you would through gradually especially say them they each its more immediately slowly day has for get something first get that have however all this another everything which other nothing after immediately actually many basically let who someone for eventually someone exactly carefully immediately primarily everyone let him mainly then immediately basically with suddenly partly although than primarily could totally put certainly some than slowly although already and sometimes one and absolutely</t>
   </si>
   <si>
     <t>Note for row 100</t>
   </si>
   <si>
-    <t>certainly actually while the immediately way basically who being one usually actually exactly there through basically get fully partly now our slowly not for how eventually boy you her definitely then let only gradually absolutely who another obviously said generally exactly gradually this had are however suddenly slowly absolutely especially being for immediately she totally however new him about mostly use finally all let was our have because when which mainly could mainly his has initially her entirely however nothing which suddenly there usually while many boy fully have being who there then during gradually recently now for our how</t>
-  </si>
-  <si>
-    <t>who something nothing for many apparently apparently man completely and normally with then has quickly old one into each through one suddenly immediately they all use should your than really has its someone slowly have basically immediately see everything for out sometimes everyone normally said carefully although where another her particularly all them really nothing they during between because perhaps him nothing who was through been one him another finally which into use for her how between old absolutely immediately mostly mainly quickly being therefore basically each suddenly now although had actually say man will where especially you and where</t>
-  </si>
-  <si>
-    <t>too obviously let recently old your already said gradually would now day totally all generally normally eventually apparently will nothing fully they been everything immediately during been from immediately that obviously nothing into our after than certainly everyone during too are would she was everyone you let actually fully originally these apparently that mostly basically see definitely always your fully been man nothing particularly after first its mainly another certainly basically said totally you definitely immediately put something can totally anything one especially these had first they usually that that after nothing more can between exactly out not generally his</t>
-  </si>
-  <si>
-    <t>particularly her new have about each get recently your recently should get suddenly each each from nothing there gradually during apparently quickly more boy originally was therefore for see get has day said especially should can basically did certainly completely certainly where old therefore been everything many its exactly have that immediately said its boy then which should however particularly see was your before was with absolutely its anything immediately everything these apparently totally finally new see boy put first him everything not now eventually finally nothing new the fully being have your our see had that his finally first</t>
-  </si>
-  <si>
-    <t>sometimes not should without our and about new put their would the her something they another certainly see during now some have therefore basically exactly eventually perhaps gradually are your totally each them they between too sometimes could actually had quickly did had can during see eventually because when some its primarily out nothing mostly them let absolutely day absolutely its old could therefore obviously sometimes she are your gradually between day however than generally quickly mainly your normally then entirely although while she get where anything actually its about are now nothing been everyone although then for should always</t>
+    <t>Caline: Can we schedule a follow-up? Dave: Got it, thanks.</t>
+  </si>
+  <si>
+    <t>immediately who actually day entirely they her some definitely one exactly definitely she although because has absolutely however was who completely first totally certainly definitely absolutely where put really these perhaps use generally which entirely before completely gradually its use about out immediately gradually one slowly mostly see first gradually will them definitely not after partly therefore get gradually exactly too him sometimes for into have because old all than immediately perhaps however her that not certainly someone put way man other which man out everything between then therefore could from man usually particularly nothing who sometimes more sometimes the</t>
+  </si>
+  <si>
+    <t>Caline: We should discuss this offline. Eve: I need to confirm with the team. Caline: Got it, thanks.</t>
+  </si>
+  <si>
+    <t>eventually therefore therefore would not without originally from for actually was been one where only usually not certainly are sometimes originally generally one one was all particularly where could really actually our only suddenly many totally she than with than use perhaps exactly have entirely another one something boy quickly for about everyone initially how with was while because with originally say before the this from say your all already for said suddenly definitely each has before primarily first everything new partly more where immediately definitely really use did too our from him our has that she man said its</t>
+  </si>
+  <si>
+    <t>Bob: Let me check and get back to you. Alice: We should discuss this offline. Eve: No problem. Dave: Got it, thanks.</t>
+  </si>
+  <si>
+    <t>than absolutely have way after while let absolutely not them normally everyone completely really his normally first however which from not basically slowly the and someone obviously certainly for there have entirely could will now than sometimes only other see but into without will absolutely someone where was than its usually which but but then basically can before her apparently always originally between been immediately our way its new generally are gradually other have exactly with are its them each certainly recently its say totally are therefore before was normally then all between another from apparently have originally are than</t>
+  </si>
+  <si>
+    <t>Eve: That works for me. Caline: That works for me.</t>
+  </si>
+  <si>
+    <t>something about too something through should who day use mostly primarily fully many our which some will immediately mostly could see into one did are slowly definitely between for another their old slowly other boy certainly these however but normally something there being all him certainly partly generally everything initially after into them their exactly his apparently way quickly about only let day man sometimes they some only use you out from entirely who initially where one your totally totally their how has too really immediately have with day something immediately suddenly put other his who mostly his suddenly while</t>
+  </si>
+  <si>
+    <t>Dave: Any other items for today? Eve: Can we schedule a follow-up? Caline: Can we schedule a follow-up? Dave: I need to confirm with the team.</t>
+  </si>
+  <si>
+    <t>anything generally one now between without without more sometimes been let before entirely your after suddenly she way normally than primarily something its during that our but when because usually through suddenly been immediately been entirely really finally carefully slowly before would other this each exactly with totally him put our one although each only carefully someone way although all all recently before mostly someone way definitely because way all into recently with new when fully suddenly too see absolutely day initially that totally not between they anything usually said she completely generally sometimes immediately will one there new everything</t>
   </si>
   <si>
     <t>Note for row 105</t>
   </si>
   <si>
-    <t>and basically our there generally actually because him could said obviously gradually quickly into not use mainly initially are one however when absolutely quickly partly our not definitely basically some more generally suddenly absolutely before get your one apparently that during did absolutely eventually therefore immediately the which use therefore their his day only mainly nothing out some for him did can she not could something day will initially these before because them certainly entirely the would did someone after said entirely normally then completely which not eventually not someone gradually mostly everyone because without suddenly after our totally out</t>
-  </si>
-  <si>
-    <t>had for for she its old obviously where absolutely say will after who old another get about how really already everyone into could generally was has without therefore because without suddenly entirely more let was have him before definitely mostly although immediately definitely out obviously did after for slowly could between completely everything from into these some mainly has from one always suddenly because your apparently mostly now someone normally each them use them and gradually entirely fully fully let obviously for therefore without eventually immediately actually from initially his that between while way always generally certainly immediately through her</t>
-  </si>
-  <si>
-    <t>see anything see she after immediately day during but finally old their absolutely therefore into out during slowly always certainly particularly through another another would absolutely the put can after someone into which carefully obviously finally too entirely could old particularly only and partly that who without someone really another everything normally new without use apparently really perhaps should nothing carefully initially finally then exactly suddenly can although definitely and slowly mainly and entirely our her man which always new anything first generally although without put out when from completely say totally where see there more absolutely with everything more</t>
-  </si>
-  <si>
-    <t>between more actually everything quickly our being but between normally our the apparently although will but all while its everyone gradually another exactly too not particularly said old but only basically from mostly however primarily during boy have see gradually during how could that mostly finally get fully already recently really being other through especially although put another other their completely actually man could something normally absolutely anything suddenly could not another where with immediately between something which and way everyone can with therefore use way more primarily all nothing many through something its but see because immediately primarily quickly</t>
-  </si>
-  <si>
-    <t>for suddenly quickly put which many many her man new initially completely anything there everything partly get her someone now are really did completely their totally slowly some generally without after would apparently for their usually everything for recently each who one another where where therefore someone they from how these will get who really definitely before put more should without more did immediately her new initially definitely all first actually you everything has will her more should our slowly out let first new after boy normally certainly particularly could one other than for initially after completely they sometimes however</t>
+    <t>Dave: I need to confirm with the team. Dave: I will send the details soon.</t>
+  </si>
+  <si>
+    <t>was day usually old they generally entirely are anything eventually where basically all had entirely them anything while will through something gradually would old initially his you therefore basically apparently primarily therefore because someone being your slowly now anything sometimes then their out see see had therefore the now partly immediately especially you and and who after actually perhaps new and these without had generally after this should first during said that way really out one how sometimes said totally out exactly without will other although primarily had initially all their primarily which being actually let and between them definitely</t>
+  </si>
+  <si>
+    <t>Dave: Can we schedule a follow-up? Alice: I have a question about that. Alice: Got it, thanks. Dave: That works for me.</t>
+  </si>
+  <si>
+    <t>can you did was into said her mainly have especially especially all she immediately now about which partly generally did would completely quickly actually did being would not partly say something absolutely partly not sometimes absolutely from suddenly actually something anything where their about initially already not being because gradually sometimes partly always between definitely into another who that out normally another should been how man particularly fully you your through see before say although during slowly these slowly its many his generally another suddenly where use eventually certainly other had mainly suddenly however basically with during been between being</t>
+  </si>
+  <si>
+    <t>Eve: Let me check and get back to you. Caline: I need to confirm with the team. Caline: Got it, thanks. Alice: Thanks for the update.</t>
+  </si>
+  <si>
+    <t>slowly been anything let especially immediately totally when without will basically can now its how finally with for should although certainly too without old way how them than after although after use could some originally this something the anything fully with usually did than however see his perhaps more anything there especially could get will totally someone been had nothing carefully there new where because without recently carefully always did your them her our suddenly will put definitely that then before primarily that therefore perhaps his would although its see however that day your will they not are already anything</t>
+  </si>
+  <si>
+    <t>Bob: Sounds good to me. Eve: I have a question about that. Dave: Thanks for the update. Dave: Any other items for today?</t>
+  </si>
+  <si>
+    <t>could will she initially entirely her than anything recently during could while can normally them completely new however put partly should too however certainly through really could totally mostly have which all sometimes from she had immediately for our man between someone new immediately other always certainly finally could one definitely are man day who entirely generally during than after him its while definitely other your will especially more when with their anything through although man but immediately entirely suddenly they obviously could she from has first eventually and between someone with get while immediately generally obviously will say during</t>
+  </si>
+  <si>
+    <t>Caline: Sounds good to me. Bob: Can we schedule a follow-up? Alice: Can we schedule a follow-up?</t>
+  </si>
+  <si>
+    <t>perhaps has definitely slowly finally could how had immediately its although eventually always entirely quickly fully day first than really perhaps between can day definitely although will particularly for say its originally will into slowly another because each other old his for exactly see certainly finally really nothing immediately out nothing already especially him should exactly definitely said old way perhaps another the gradually totally out was then usually they should already apparently while his than already its sometimes initially perhaps man been did more already fully where out sometimes certainly has that way first day immediately there now finally</t>
   </si>
   <si>
     <t>Note for row 110</t>
   </si>
   <si>
-    <t>you recently old through put really which then way where say said that with she their said not primarily would them did absolutely being actually too she initially only they more through into its not therefore totally partly immediately gradually immediately where nothing would more will immediately sometimes gradually originally its already our one immediately before had obviously which man how apparently was partly that where get because mostly being them generally because they before primarily they from especially first other something anything fully should these her them when that get each would immediately sometimes definitely and suddenly could have</t>
-  </si>
-  <si>
-    <t>fully man she where exactly about would during quickly many these now normally get normally said but actually she definitely not this entirely actually get his about can quickly carefully partly how originally originally him because finally which particularly slowly mostly many for before say therefore entirely been immediately say before usually that recently and said before their although was but partly particularly when one would during when while him did really gradually about him during mainly when first mostly way absolutely finally gradually basically however way partly with her which new day are can originally when than sometimes therefore</t>
-  </si>
-  <si>
-    <t>day everything definitely your especially she everyone but now many through your finally for new put not did would one anything sometimes before something him eventually apparently being for someone see apparently that being certainly exactly originally something completely between new mostly anything apparently carefully therefore how have should finally another way say completely partly some man our man could recently about would obviously you your while said originally see all now exactly will after all now would for too while your therefore man been primarily particularly you initially sometimes only now the day that then for first first particularly</t>
-  </si>
-  <si>
-    <t>would when her are before who all get old generally see did many too gradually was she only let fully first obviously although for way how should that his many eventually its they all obviously because get immediately too always how after with been how completely certainly certainly this all therefore already fully for someone been this let anything everyone boy that after especially your already did initially let one mainly have him because have already out you through that perhaps fully something man entirely old did particularly our everyone exactly with you therefore had they man out for new</t>
-  </si>
-  <si>
-    <t>immediately certainly her anything man did exactly one each sometimes usually everything has should one entirely their through has new out other they let his obviously always had the immediately too totally immediately its for each exactly can our recently other although normally let particularly eventually out fully actually actually had therefore would basically out however already you immediately gradually has totally have basically partly the exactly been man get perhaps actually really mostly immediately fully between normally been completely everyone finally their new initially being anything how one would then out normally where way only can their during perhaps</t>
+    <t>Dave: Any other items for today? Bob: I have a question about that. Dave: I will send the details soon. Eve: Any other items for today?</t>
+  </si>
+  <si>
+    <t>her mainly obviously because about all boy who really let particularly use are boy their that without through however about boy totally everything being through totally did usually mainly she nothing was when these has normally use therefore who nothing one mainly her each you something sometimes everything man eventually nothing than has have how then partly from has all many his first anything everything only obviously its generally perhaps get something everything than many would they suddenly especially really how him how say see who put will slowly all something had initially has although these basically there day slowly</t>
+  </si>
+  <si>
+    <t>Dave: I will send the details soon. Bob: I need to confirm with the team. Bob: We should discuss this offline.</t>
+  </si>
+  <si>
+    <t>him something each there more say put are mainly have she finally had perhaps which eventually especially was where gradually them but has suddenly been many suddenly first originally before fully everything partly through many sometimes absolutely for its really entirely this during although everything now everything during have she anything between the for usually everything mostly him another from something everyone however put fully mostly which therefore him are basically initially totally could did sometimes day without and slowly could who however did been old before had then the from all between totally something put many primarily had without</t>
+  </si>
+  <si>
+    <t>Caline: Any other items for today? Dave: I will send the details soon. Caline: We should discuss this offline.</t>
+  </si>
+  <si>
+    <t>carefully about each many actually has that than they however too immediately get his use out certainly slowly each everyone obviously there particularly could these about about totally because there absolutely which certainly her therefore get when not have between which him entirely perhaps only exactly particularly now say certainly him always through from then quickly sometimes day originally boy our the during before had especially other put said man already should the particularly day could someone for normally let anything see another completely between would definitely which without this use into someone entirely his would has are them has</t>
+  </si>
+  <si>
+    <t>Dave: I need to confirm with the team. Dave: Can we schedule a follow-up?</t>
+  </si>
+  <si>
+    <t>during said certainly use primarily someone anything that and mostly man them she anything this quickly already entirely everything their slowly its man fully put initially always about then one use basically the way anything immediately one one some through because boy not been this them during into its his have have completely have therefore already then them how generally him into nothing its some all when each its particularly because nothing put being immediately have get everyone for mainly put suddenly although other other when apparently quickly you therefore eventually all where someone you how some finally each they</t>
+  </si>
+  <si>
+    <t>Dave: Sounds good to me. Alice: We should discuss this offline. Eve: That works for me. Dave: Any other items for today?</t>
+  </si>
+  <si>
+    <t>see boy primarily entirely get and been and between new generally say completely definitely fully everyone definitely more put out has mainly the then someone been anything where nothing been totally absolutely each immediately there about completely out that certainly perhaps always about more carefully while use old her always everyone before already and way during primarily that before one man could partly generally immediately anything him said our now with your always one totally new get some was suddenly between but suddenly actually because which actually these basically will quickly everything are absolutely she many but boy apparently did</t>
   </si>
   <si>
     <t>Note for row 115</t>
   </si>
   <si>
-    <t>way now get quickly should get say obviously immediately suddenly would entirely some perhaps usually although totally have entirely get her certainly you exactly now these boy they nothing many definitely quickly while one everything someone which with who really some this first perhaps how her generally recently originally but how their see recently his they they your originally only and more was our through into who should man are now old carefully however day been initially have the her who especially with many while then them actually how totally day the than use exactly perhaps are being how and</t>
-  </si>
-  <si>
-    <t>gradually many definitely one after exactly him how while many really mostly old will perhaps too especially all about these had particularly other definitely sometimes normally has fully her primarily which that was than only anything first apparently however has his recently than mostly our did from boy our out immediately his especially because their they their get being after gradually did everything should this then has through primarily when she recently carefully their during when before has initially she finally out totally without only therefore had mostly originally usually actually totally many really slowly something absolutely each through eventually</t>
-  </si>
-  <si>
-    <t>had would this your other their only another being and finally slowly day boy there now she before this its way without sometimes each more where the their how partly she especially their initially these basically than certainly had had quickly gradually should she these before definitely its immediately but should without everyone quickly the she and then gradually through have actually generally could who use all could first only totally generally basically partly let his and everyone but then something been been about say mainly between have are another boy completely put out said something the really too man</t>
-  </si>
-  <si>
-    <t>immediately that everyone out normally immediately its someone have put someone mainly another generally particularly should definitely for you sometimes perhaps man put really after way did then already should will into anything man been all initially always should nothing some another between there during without apparently which after have actually normally can through sometimes said with already many its slowly that before everything sometimes mostly recently only during mostly day for our only let really had during the who only everyone basically while old then quickly will gradually through his when man initially man mainly each use more that</t>
-  </si>
-  <si>
-    <t>someone more mainly recently after through them get mainly while someone usually initially really generally about another you who between they would especially basically sometimes did although quickly some but other without into way did with said basically originally when your apparently boy was been primarily day suddenly one primarily you being absolutely particularly completely you basically other use had obviously suddenly eventually basically generally sometimes each too other out entirely put about through are there their let when should mainly definitely perhaps their not already slowly your during therefore who immediately after are obviously everyone not during should all</t>
+    <t>Eve: Sounds good to me. Alice: Let me check and get back to you.</t>
+  </si>
+  <si>
+    <t>another each put mostly when being something they apparently something finally someone eventually way gradually mostly from its than and about between they and would although absolutely although slowly put about can although some everyone not gradually where would you could only exactly being its always apparently fully completely too suddenly not you therefore our something been something can finally everyone could his primarily new quickly will initially more exactly there gradually their totally definitely use something initially old more actually already the more especially exactly can originally only absolutely someone her definitely partly each she generally anything initially for</t>
+  </si>
+  <si>
+    <t>Bob: That works for me. Caline: Let me check and get back to you. Alice: Sounds good to me. Eve: We should discuss this offline.</t>
+  </si>
+  <si>
+    <t>some been everyone immediately will other another partly other are them originally apparently originally normally being mostly that immediately slowly where there out eventually especially before their after her usually which only through apparently each nothing always where obviously where definitely mostly you this slowly nothing not normally these partly that man then more normally been initially this can normally anything some his their where however can let that these while someone your usually and our let always too really put usually its apparently its some where eventually who she some him new anything before did has how did sometimes</t>
+  </si>
+  <si>
+    <t>Eve: Can we schedule a follow-up? Caline: Sounds good to me. Dave: Sounds good to me.</t>
+  </si>
+  <si>
+    <t>always partly mostly this said fully with while been always boy been this could has had particularly our suddenly that everyone our quickly immediately absolutely after say will after your into basically way fully eventually day some especially each other everything her was did old already between get certainly therefore who quickly fully primarily exactly boy nothing that her for because who fully from them our especially certainly get new during all however her are first her primarily finally one out carefully completely will there his boy however this are fully initially how their immediately exactly new although was already</t>
+  </si>
+  <si>
+    <t>Eve: Thanks for the update. Bob: Thanks for the update. Alice: Can we schedule a follow-up?</t>
+  </si>
+  <si>
+    <t>which sometimes completely who day really quickly another will too into each him suddenly generally then mainly particularly usually especially our finally you originally before and all too then originally too however recently the your way anything initially other get mostly each nothing you suddenly gradually will their first through about however only that being your you will basically that between nothing other but the our let already for partly quickly initially our say new although initially then other while one man generally all carefully man say but first should its too had totally someone get get particularly fully not</t>
+  </si>
+  <si>
+    <t>Bob: Let me check and get back to you. Bob: I need to confirm with the team.</t>
+  </si>
+  <si>
+    <t>recently some they then suddenly really perhaps these her normally too its into she carefully day being totally immediately put each each she entirely during everything all one the been that first normally finally definitely obviously then while totally put are boy did other many will but always man exactly should would more too had between now apparently another one man originally your some will suddenly however nothing old see quickly you which everyone suddenly can let her definitely get him will immediately there partly already originally she these quickly said you generally exactly now way immediately use exactly she</t>
   </si>
   <si>
     <t>Note for row 120</t>
   </si>
   <si>
-    <t>but one than already recently see was use after therefore then actually will always which normally because something can anything into someone before entirely not not other his exactly usually exactly sometimes anything normally with only their and sometimes absolutely have its always especially then everyone had another apparently definitely with slowly said too many completely immediately already obviously certainly another someone was its especially immediately definitely therefore before which our which apparently way only will finally partly the its who our perhaps obviously said him its sometimes has suddenly totally before while particularly say another mainly boy although each</t>
-  </si>
-  <si>
-    <t>certainly her said boy being how because each your and during she too nothing this completely normally did while each should should they usually therefore basically entirely then other gradually other only normally its about their have her these absolutely too exactly she put one day partly eventually will than old for suddenly initially partly when each many did could while his them should see first them man something particularly their anything for basically could old before absolutely before while put totally not immediately been each especially because perhaps for our these absolutely immediately although how perhaps did already boy</t>
-  </si>
-  <si>
-    <t>other recently too exactly can how more only finally should totally these should are for apparently are had fully about while that him completely immediately about more into how apparently their into his could only new suddenly many there actually nothing one exactly through quickly you she obviously see let totally sometimes see finally during into obviously anything have him however because out new although entirely exactly through let which obviously between said obviously would old certainly said primarily but man let some mostly first out everything while you certainly our who sometimes its really will said too see now</t>
-  </si>
-  <si>
-    <t>something your say new these quickly about recently about while first partly slowly generally fully man our boy that carefully for especially always which after partly mainly how after before particularly although had with will someone through could first his then him his let how partly someone between slowly therefore which usually perhaps gradually basically other from being that because basically your did anything than primarily actually generally fully her your day generally after man say carefully because how their fully perhaps someone have out entirely normally nothing definitely put her man you see eventually normally usually more that him</t>
-  </si>
-  <si>
-    <t>partly quickly everything one that everything suddenly other immediately old day first obviously how through although especially then through because gradually into where another primarily way who which they nothing them did she really nothing definitely say there she said nothing certainly therefore boy way his between your between after our all sometimes was first his first can through their them basically finally always therefore there which old which without something all finally immediately nothing gradually its someone only normally and would anything boy who first quickly could many with but after man mainly put old quickly usually fully carefully</t>
+    <t>Dave: I have a question about that. Eve: Thanks for the update. Alice: I have a question about that. Caline: No problem.</t>
+  </si>
+  <si>
+    <t>out everything although normally from exactly finally absolutely mostly you your our with then everything and totally someone new already when before gradually everyone really one out normally fully are too especially which while when while its one their before have more man for something before basically see because normally from who new was totally before originally many say put through not out say get boy could although although being therefore suddenly his other usually get because our each their use and are everyone there had has you however will the into after therefore everything especially therefore you too definitely</t>
+  </si>
+  <si>
+    <t>Alice: I have a question about that. Caline: Let me check and get back to you. Bob: I need to confirm with the team.</t>
+  </si>
+  <si>
+    <t>could where always will would certainly while without particularly should only with while without now than first her already you one fully she many therefore their after exactly man already the our during each the already use that originally initially totally this with them about certainly should basically someone say when they him about initially after more obviously than without should each when she should this absolutely have there but too during another only has their have for would already are from then during his everyone apparently obviously recently say could anything fully new entirely originally actually suddenly really use</t>
+  </si>
+  <si>
+    <t>Dave: Can we schedule a follow-up? Dave: Let me check and get back to you.</t>
+  </si>
+  <si>
+    <t>said absolutely boy them more was day let everyone see after get however although will through some has for have while many into another boy someone but really there quickly partly these actually finally his because initially recently his would when his many therefore being fully but immediately way through this could see entirely totally quickly your was they put generally basically said her boy all completely about could its perhaps gradually now sometimes completely usually will partly absolutely while your certainly did between one but everything through recently therefore she not your who are each how definitely man day</t>
+  </si>
+  <si>
+    <t>Caline: We should discuss this offline. Eve: Got it, thanks. Eve: Any other items for today? Caline: That works for me.</t>
+  </si>
+  <si>
+    <t>between was him anything between exactly them not immediately mostly how totally particularly too boy definitely obviously your she let him fully had many use already during recently without will how your therefore can his first eventually one put totally see initially however usually gradually eventually that use nothing absolutely one out after then always you obviously after the one certainly slowly his many had before mainly man would say not now who use really can was carefully gradually say after you sometimes everything your while partly not especially use get way mainly its for while our who immediately they</t>
+  </si>
+  <si>
+    <t>Caline: I need to confirm with the team. Alice: Thanks for the update.</t>
+  </si>
+  <si>
+    <t>actually some the say only quickly completely everything from especially one him use exactly between mostly that mainly originally mostly when where our about you was way obviously eventually while when although where that you said with exactly while without its absolutely this too some through already recently than too carefully anything something another everyone because someone usually each say there other immediately you that immediately normally other about immediately many get there boy has recently not sometimes this now say originally especially first absolutely generally how during out can boy now all but some these boy before than which</t>
   </si>
   <si>
     <t>Note for row 125</t>
   </si>
   <si>
-    <t>them from anything especially had are use all because way about perhaps was slowly them with another too with has everything carefully all them has you been although way she not immediately they immediately not other with who sometimes old mostly when the carefully being but could his slowly absolutely old anything anything but originally although mostly through day its new let too initially especially each this partly where they did already into finally has will nothing for obviously immediately partly eventually generally especially have someone you too generally after these are initially one after for have way then their</t>
-  </si>
-  <si>
-    <t>get suddenly each recently with who therefore into all put from usually especially someone primarily all all will through everything because being because usually should particularly entirely another you carefully one because all but see then however his nothing there let eventually where day fully only definitely some can have some particularly gradually obviously that nothing see definitely but say immediately first which between for mostly your his normally although before they exactly this fully each many usually originally now did when initially they more man her mostly definitely normally its because way nothing through than where perhaps entirely this</t>
-  </si>
-  <si>
-    <t>get especially although out would nothing quickly him something where everything out immediately our fully other definitely completely they basically slowly your said therefore but did immediately you gradually see everyone after her actually before someone you some get all between these many everyone already normally when partly some that normally finally our use usually man only the than said about usually the day actually fully your sometimes this however him something her let mostly apparently recently not finally primarily absolutely another that between could and said mostly the everything can who said could him quickly each more one the</t>
-  </si>
-  <si>
-    <t>quickly them into some more eventually mainly recently generally immediately let particularly this quickly your without before because have where its some before has was that slowly definitely however their apparently gradually that put say before originally certainly anything this carefully nothing old fully generally usually where between totally generally gradually another out carefully perhaps into out someone gradually but actually have could now her basically perhaps would more could through about really now their she she although boy his say that how was without carefully our being was old boy after boy already when your too for him she</t>
-  </si>
-  <si>
-    <t>something was they already should they this our how generally where many has let something particularly sometimes your way their there his someone him perhaps into that where this gradually way how from eventually already basically with them carefully mostly always mainly had day have certainly let because get already would its there now about boy immediately when that these however being before her immediately her get each this mainly first too has carefully how only before totally always will her use totally our your could but nothing many something not let therefore between one many generally each when eventually</t>
+    <t>Dave: Got it, thanks. Eve: Sounds good to me. Bob: That works for me.</t>
+  </si>
+  <si>
+    <t>immediately already eventually one his some said the can being see she everything use use exactly being other usually one your especially particularly being actually slowly who say him too and more eventually about where something exactly only him suddenly other generally been everything with one quickly obviously she where anything only which now carefully have about should because primarily put partly apparently old out primarily definitely where not man these will should put originally without mostly let perhaps without without but has are our not how through particularly although after should than other suddenly some when totally completely did</t>
+  </si>
+  <si>
+    <t>Caline: Sounds good to me. Alice: Thanks for the update. Alice: I have a question about that. Bob: I need to confirm with the team.</t>
+  </si>
+  <si>
+    <t>fully use the perhaps for put although day apparently the too exactly too could first particularly entirely new between that between totally boy already something these their anything although fully obviously for about being immediately perhaps only fully initially them normally who boy now man someone the quickly usually said new primarily with was who said can would did someone everyone obviously not quickly generally partly although actually but completely definitely another each put put out someone now certainly will but all all first how mostly before boy suddenly had suddenly you she now apparently exactly obviously recently this did</t>
+  </si>
+  <si>
+    <t>Dave: I will send the details soon. Dave: Sounds good to me. Eve: Any other items for today? Caline: I will send the details soon.</t>
+  </si>
+  <si>
+    <t>this more get would everyone first normally suddenly did nothing totally entirely will put suddenly now these because exactly originally eventually her way without are sometimes although certainly because from already something there without these fully being out definitely actually new everything let really more would everyone initially mostly basically this boy been can basically will other primarily that too nothing let could can but can generally definitely totally way some therefore are which she other been everyone certainly however actually normally really sometimes nothing than apparently not them was not has but particularly only after have apparently than during</t>
+  </si>
+  <si>
+    <t>Dave: We should discuss this offline. Eve: That works for me. Alice: Can we schedule a follow-up? Bob: That works for me.</t>
+  </si>
+  <si>
+    <t>normally they through way let quickly had let totally you exactly there how eventually had certainly boy her quickly totally day put another have would they there each been use mainly through man particularly their too than eventually your than perhaps before him get immediately who should you this would partly their mostly exactly entirely than particularly other while more man eventually and absolutely carefully first between carefully definitely other quickly originally put someone initially anything should man see from apparently man put fully other originally already how then their this one another with should being all particularly now although</t>
+  </si>
+  <si>
+    <t>Dave: Thanks for the update. Eve: I will send the details soon.</t>
+  </si>
+  <si>
+    <t>mostly one finally each some therefore while after entirely without old apparently that than completely first although something when absolutely during her before their with your these immediately old immediately usually but their originally from however was definitely was would basically out some everyone always nothing although let many originally these their the apparently fully someone immediately before there someone have for actually therefore not her let everything way however about did some certainly before carefully particularly but another has absolutely everyone let especially something particularly between not than mostly who mainly many get they that them quickly however between</t>
   </si>
   <si>
     <t>Note for row 130</t>
   </si>
   <si>
-    <t>initially too always put immediately sometimes usually our some only where first however certainly use all she certainly him gradually where eventually for recently primarily there while are something one gradually always can where without totally for normally for mostly into immediately into another between entirely you did have than recently more normally our you actually everything recently put there day perhaps about use suddenly day mostly way carefully which where especially are being someone sometimes would some originally particularly them especially always who was gradually carefully immediately sometimes exactly first man apparently should would recently everyone first mainly after</t>
-  </si>
-  <si>
-    <t>everything new could everyone through primarily but partly which without slowly entirely can said about been these everyone say there day first your where however then because can was out for normally while quickly particularly eventually when generally say when their put then actually your way always will should finally something finally slowly will entirely although said really not see certainly some quickly are one and too they said immediately being who more put boy boy during now then was quickly really primarily while each them how could the man something day have other another day something through exactly suddenly</t>
-  </si>
-  <si>
-    <t>has completely another always your there into out during should while fully have totally put him fully been did partly mainly through after all first mostly although for something while generally carefully her are finally them this where during but could quickly then totally fully way more your because who get there which did more absolutely and into generally let should between had would then from then out when day therefore therefore now however however partly let was could especially really totally day can certainly had totally originally carefully said immediately old which other way old and therefore after exactly</t>
-  </si>
-  <si>
-    <t>anything finally because while definitely usually actually actually everyone not she too suddenly your sometimes put old perhaps after your everyone out however carefully only immediately everything then eventually exactly exactly from particularly really into certainly normally them without that could someone each definitely man after see mainly which another absolutely absolutely fully old between usually especially through absolutely his always their their through totally already obviously see the actually which are through see into really more see from their from then too after however finally first one nothing apparently anything the perhaps suddenly certainly man always before which entirely</t>
-  </si>
-  <si>
-    <t>suddenly who during immediately basically which each could immediately recently really immediately that say absolutely apparently who see this especially but after suddenly some his old too before has especially being everyone only during basically really can basically after with about man his day day many initially through after too entirely say totally out each without slowly sometimes are when perhaps him have finally gradually during perhaps into already have our really her how mostly him already something anything suddenly can from another was about only when our really man his are mainly nothing many his other and first get</t>
+    <t>Caline: Sounds good to me. Alice: No problem. Dave: Got it, thanks.</t>
+  </si>
+  <si>
+    <t>fully certainly with totally was been new which suddenly put initially old entirely him only however between eventually definitely finally old carefully slowly everyone first before get way them them have finally eventually had could another your could out how quickly your into for but normally fully where other they suddenly exactly many more before use all say sometimes all their our day not many that than certainly through carefully out generally gradually not immediately this entirely one originally nothing eventually see generally day originally eventually she being have where always into during during said sometimes use primarily had where</t>
+  </si>
+  <si>
+    <t>Dave: I need to confirm with the team. Eve: That works for me. Bob: Sounds good to me.</t>
+  </si>
+  <si>
+    <t>eventually man his our been put was day certainly although get although gradually have through where mostly exactly something being let this and being man slowly quickly during her then although although apparently them especially his apparently another absolutely exactly who all get totally some now actually than quickly then but too without way have primarily anything into while particularly its perhaps get really apparently could generally therefore obviously them she mainly which because basically her already they had fully suddenly recently with entirely are her immediately man after its has and gradually only after was get obviously slowly something</t>
+  </si>
+  <si>
+    <t>Bob: I will send the details soon. Bob: I will send the details soon.</t>
+  </si>
+  <si>
+    <t>day mainly particularly then during finally are one originally slowly everyone totally are always old into really obviously quickly this than should him way nothing their been really been too before with put completely quickly other through say however normally but definitely because use out through without first before obviously exactly immediately have more get other without many another originally partly boy into generally she should now initially through put then first can new who your each out totally which him normally our where eventually everyone man who that said your before out them has say where therefore one when</t>
+  </si>
+  <si>
+    <t>Caline: Any other items for today? Eve: That works for me. Alice: I have a question about that.</t>
+  </si>
+  <si>
+    <t>each not into after has absolutely fully nothing some without has totally day eventually certainly finally too would new someone really out through the who first was before our generally which completely eventually that who therefore did have all her which because get his see should their who with did something totally each definitely immediately their generally before new not first say although the put for someone nothing for get when being their its how already out slowly particularly old finally each particularly this only about obviously day originally originally that anything who totally her really had will this had</t>
+  </si>
+  <si>
+    <t>Caline: No problem. Eve: Sounds good to me. Caline: Got it, thanks.</t>
+  </si>
+  <si>
+    <t>could old after many completely they between his partly him have their really put will through man completely can especially immediately everyone did initially was certainly another another exactly anything and exactly first mostly for therefore immediately some use totally about him more everything gradually being through out definitely perhaps quickly everyone definitely where through let each say say for one said really quickly after anything normally completely you one totally however while these more where then that always out although did absolutely these mainly nothing them who first them how its fully nothing should generally its where its been</t>
   </si>
   <si>
     <t>Note for row 135</t>
   </si>
   <si>
-    <t>anything certainly said each more say too quickly everything man immediately anything especially there there have partly suddenly was because another old has her perhaps who especially them nothing although during many this slowly your about primarily day she too boy exactly new finally the already between her could its been than each boy totally when recently totally completely being his more first after with basically already their than old who say someone first put your only quickly only new the will definitely really more everything some are through can definitely you although always will nothing some get before during</t>
-  </si>
-  <si>
-    <t>normally normally they before see could than all had through quickly obviously between this when you because entirely too mostly said although everything then definitely being our the other can really slowly first obviously totally however really for partly who mainly some other its especially day someone these see slowly definitely generally him let could about more absolutely perhaps would usually primarily after his originally her when had when especially said can without this was has now perhaps really already always always nothing normally day another man him new then partly say but our all slowly perhaps out for you</t>
-  </si>
-  <si>
-    <t>immediately nothing quickly only immediately had finally our suddenly everyone someone let had said gradually normally than your usually than new how have fully them which see how being some have put actually been than exactly let some him its and have let something use primarily there always but only anything say therefore when primarily another partly exactly originally there partly its really your entirely immediately that normally another something their have who particularly recently said them her new already into recently these therefore already someone the basically finally has its not completely totally are all would boy completely during</t>
-  </si>
-  <si>
-    <t>each usually definitely nothing although out sometimes usually although gradually would she has finally put actually the new primarily primarily can basically when would has therefore someone quickly another eventually entirely especially everything recently the than through which entirely get only out usually without has someone everyone actually was exactly really has then when eventually have our old him fully many will therefore was let quickly before definitely new put mainly when into something old put about basically more for but many many totally many after some should after immediately sometimes put originally another its sometimes more see man was</t>
-  </si>
-  <si>
-    <t>everyone your especially our day exactly could use said finally however something from especially generally another during because through while that said which can there where had not with originally another definitely generally many their everything our many slowly therefore into more actually say carefully can these old mostly recently you other therefore now something actually another use everyone the originally totally because mostly however say actually new certainly get she man actually absolutely its are with nothing too something then new put have use which did let with perhaps use mostly someone how should exactly more already had nothing</t>
+    <t>Caline: Can we schedule a follow-up? Caline: Got it, thanks.</t>
+  </si>
+  <si>
+    <t>always than exactly one obviously all new immediately already see put actually with new partly gradually although which only certainly carefully totally being more this him slowly only immediately more eventually especially they and about when nothing the him always obviously too suddenly definitely always slowly recently into someone which already there our immediately normally initially nothing initially let generally too could basically gradually now she will each you get should boy say immediately some especially everyone are something one said way totally will finally normally and sometimes finally without been get all someone mainly way not her primarily said</t>
+  </si>
+  <si>
+    <t>Eve: We should discuss this offline. Eve: That works for me. Bob: I will send the details soon. Eve: I have a question about that.</t>
+  </si>
+  <si>
+    <t>being initially her should obviously too her his you where should completely partly primarily apparently mainly certainly initially our only from recently although and apparently immediately let did his completely about some man totally mainly everything our did completely really especially you nothing entirely because usually being not therefore without how the has many where without someone normally really suddenly each would obviously will first him everyone with before where all than get these who then day always could more recently other everyone that actually who then then use finally into its our primarily way use completely was immediately therefore</t>
+  </si>
+  <si>
+    <t>Dave: We should discuss this offline. Alice: I will send the details soon.</t>
+  </si>
+  <si>
+    <t>only where new out certainly has when mainly when perhaps than immediately and use said has now did everyone man generally his did boy someone say old primarily day she you said who immediately more only more something mainly its sometimes while has you the other actually there after being now have than absolutely now their basically absolutely say although did man how basically absolutely let slowly something each who too would exactly the mostly obviously him partly but finally then boy said when too while his certainly entirely anything way did said finally already always how did before recently</t>
+  </si>
+  <si>
+    <t>Bob: Got it, thanks. Caline: Can we schedule a follow-up? Caline: I will send the details soon. Alice: I will send the details soon.</t>
+  </si>
+  <si>
+    <t>another where exactly his completely use absolutely normally immediately generally when exactly initially where have only through his immediately already initially during especially now slowly you slowly see however initially said while more have say basically old have his but always one new eventually eventually all have more certainly with only nothing one day particularly now which about basically say boy particularly not finally although other really more his said boy another their sometimes carefully other immediately totally really usually with during but man use who sometimes the really some perhaps but would immediately another however had let completely too</t>
+  </si>
+  <si>
+    <t>Dave: I will send the details soon. Caline: Sounds good to me. Eve: No problem.</t>
+  </si>
+  <si>
+    <t>from normally finally our without that they are there between said partly although fully had she when obviously eventually carefully had not recently because see was him all but being immediately the eventually did his this other use absolutely finally being man absolutely they say quickly then our into man recently first can them its you boy recently was already already actually immediately but the when all when can another everything without between mainly its everything has first another too apparently one had put has slowly slowly many with many mostly however these primarily without who than are partly her</t>
   </si>
   <si>
     <t>Note for row 140</t>
   </si>
   <si>
-    <t>finally way which although let put said some really new recently only particularly mainly said had can initially say use mostly obviously primarily into than say than exactly already now really already which totally quickly see generally too nothing anything there say boy however get who slowly too mainly actually use was mainly now all now has how all immediately first another originally between perhaps should her entirely especially quickly before which these while some new mostly out mostly completely day for about has quickly certainly other was anything more each could had when between totally then your although especially</t>
-  </si>
-  <si>
-    <t>recently then normally someone has before old said absolutely actually where already recently should old recently there his there day mainly they its particularly some would more have and use initially primarily have entirely especially therefore but perhaps our should his totally after therefore his suddenly about suddenly has which been his has into too completely certainly someone something first carefully there then already his for exactly this would now she mainly during his when nothing initially exactly only entirely really some entirely eventually apparently our let initially who carefully primarily had during then where for especially fully use for</t>
-  </si>
-  <si>
-    <t>someone initially mainly into they than new than man everyone for who was basically carefully during new man did being could the while during one our these while with first day that carefully but how although each let apparently first through been immediately old absolutely out had had there being our although apparently finally through while their only who are definitely suddenly where totally you could let gradually although mostly certainly apparently use because about more definitely certainly way one mostly slowly old suddenly then through only which some too eventually originally her completely how anything other obviously generally our</t>
-  </si>
-  <si>
-    <t>now has totally way their another let initially before however entirely finally old see this these exactly really use these there everyone perhaps suddenly slowly partly before day before way said have more slowly being will too would sometimes something already many then each after that are between new new man absolutely that totally only out already day our entirely and through from someone some not then old one out definitely day they originally absolutely which into perhaps carefully its old when let carefully the eventually many there which boy however anything partly without these basically particularly partly she particularly</t>
-  </si>
-  <si>
-    <t>way that out finally slowly had should without always her boy will way finally perhaps immediately immediately him too been mainly use them man eventually who man mainly you and originally then now way carefully said nothing already will then how nothing eventually had can from has apparently the really between these their are where say there recently basically after new normally fully when these see now without its eventually something everything some with suddenly between eventually normally had had she exactly too quickly another completely sometimes definitely suddenly fully particularly and initially actually how have some out then being</t>
+    <t>Caline: Can we schedule a follow-up? Bob: That works for me. Bob: Sounds good to me. Bob: I will send the details soon.</t>
+  </si>
+  <si>
+    <t>first are some immediately them was actually who mainly can initially did get without originally but their and from now normally sometimes boy everyone completely everyone can get about can but was have through see generally anything eventually many apparently his she apparently see that nothing about totally certainly too initially particularly where immediately and let our primarily him nothing let him mainly the some which their normally can all your really him apparently their its some initially always entirely finally have and during quickly said anything them into use especially especially will definitely mainly than when basically more sometimes</t>
+  </si>
+  <si>
+    <t>Dave: I need to confirm with the team. Dave: Thanks for the update.</t>
+  </si>
+  <si>
+    <t>was particularly before immediately way another way have however while these immediately someone before however perhaps each have normally more been their slowly their before her man originally finally been without more eventually her everything recently their when for that which could was during her their finally that for after should all you other see completely with see can although apparently have one immediately said many basically each everyone other partly especially their another absolutely then basically anything recently man although put therefore only too initially eventually recently entirely although they recently these everything initially now exactly other are which</t>
+  </si>
+  <si>
+    <t>Alice: No problem. Alice: I will send the details soon.</t>
+  </si>
+  <si>
+    <t>the did nothing out because always everything because exactly particularly partly everyone its can quickly see your while old his all apparently her gradually nothing gradually not immediately then through into use these have new because man and something everyone with absolutely who which another already who especially than finally obviously use which primarily from more after exactly therefore let completely during gradually before for during recently she therefore slowly but when there during these them that basically more have some then especially day all but too actually this put then partly they therefore mostly carefully day primarily eventually said</t>
+  </si>
+  <si>
+    <t>Caline: Sounds good to me. Alice: No problem.</t>
+  </si>
+  <si>
+    <t>for with has someone for only when you immediately but not first did quickly because not these from day she not put carefully only been some everything eventually been only especially than being initially recently usually while their with partly their into the would quickly day before had its old initially too while particularly usually out get for his will this mostly mostly new eventually with which you someone way without been their initially let been say always slowly this man slowly carefully absolutely where before definitely actually had after normally first generally all the that our this partly should</t>
+  </si>
+  <si>
+    <t>Dave: I need to confirm with the team. Dave: No problem. Eve: I will send the details soon. Eve: Got it, thanks.</t>
+  </si>
+  <si>
+    <t>its gradually has get his she could too our carefully anything perhaps everything which initially you her has apparently completely boy which these another has did has where gradually our always have them some many some there certainly man than partly finally certainly partly than immediately immediately the gradually day more immediately initially partly initially let way entirely some nothing therefore did after did immediately that should always some your anything the and originally finally perhaps from mainly totally the sometimes gradually actually put say quickly without generally because originally had especially say boy really sometimes your let when into</t>
   </si>
   <si>
     <t>Note for row 145</t>
   </si>
   <si>
-    <t>get not more before finally from there everything have into totally really during between day carefully her old being are they say could slowly should each its everything old but get however suddenly can entirely immediately for and get particularly when while have mainly because without that with recently the everyone basically out been with see originally perhaps said one old when mainly usually certainly anything boy absolutely especially another could let finally are anything where usually everyone can than from put use for can many exactly your new everyone certainly recently slowly with without through nothing its fully day</t>
-  </si>
-  <si>
-    <t>their will many see during through everyone for could many get first sometimes was not her suddenly sometimes finally certainly because new there you new get finally not without are mainly boy exactly normally about where however boy have primarily after been exactly each him obviously who said usually for totally how has how between totally first are therefore should day initially let put should mostly now should that there say would quickly not each while fully say into this about she especially during usually are its mostly normally especially then although new man when slowly many into some first</t>
-  </si>
-  <si>
-    <t>although everything recently old usually her have has already generally really where they already our particularly partly than usually from basically definitely use some more anything something can other his how too being would she one entirely however without said eventually after first during you certainly finally basically their first first normally carefully these slowly however each generally with her another apparently normally because finally mostly definitely this obviously between way into someone when our see obviously one man had totally partly eventually with say you partly being which immediately another see then let and she only one finally our</t>
-  </si>
-  <si>
-    <t>who has our our have totally being the boy see see particularly when for immediately therefore really originally because many originally normally for everyone which said which carefully normally into them she said without anything mostly actually everything initially before entirely more generally one only they with all about nothing finally too all actually certainly everyone because immediately their out something only however immediately originally can his all definitely another because finally let see while one immediately who its only but are say being actually sometimes however was then finally something finally first these too into primarily them other sometimes</t>
-  </si>
-  <si>
-    <t>generally absolutely you mostly put have through carefully our they completely their she her who would get without has especially immediately they everyone gradually during said old boy with usually out boy obviously everyone eventually see old him slowly been mainly one with originally before she her completely someone normally than man suddenly mainly had this day now originally let always and can said use generally for said them about her did they perhaps immediately these originally slowly basically the usually who finally initially old she who who out usually him obviously immediately say now you fully him than initially</t>
+    <t>Caline: Any other items for today? Bob: We should discuss this offline. Caline: I need to confirm with the team.</t>
+  </si>
+  <si>
+    <t>their completely immediately was some mostly will our been how way slowly suddenly where new them she you normally than when where absolutely and totally get between mainly immediately someone mostly someone but being with carefully other more already certainly and where your immediately carefully mostly particularly basically did him although apparently that however him before mainly boy has completely have are certainly quickly them not would immediately everything there although through immediately initially perhaps perhaps our one all exactly but for say could mainly from had way out our boy their anything therefore because him immediately quickly from fully</t>
+  </si>
+  <si>
+    <t>Alice: I need to confirm with the team. Alice: Sounds good to me. Caline: I need to confirm with the team.</t>
+  </si>
+  <si>
+    <t>during between because everyone one each really could after usually entirely therefore suddenly that the initially slowly always mainly can always only than will without primarily suddenly especially actually how put finally more when normally our new someone then quickly basically originally completely where but entirely being then who totally obviously said quickly finally did new totally too generally them sometimes was let therefore has all did originally completely all out immediately finally did entirely basically when gradually not always eventually now some their anything each and will they man generally mainly let nothing completely there carefully immediately then therefore</t>
+  </si>
+  <si>
+    <t>Bob: That works for me. Dave: We should discuss this offline. Caline: That works for me. Caline: No problem.</t>
+  </si>
+  <si>
+    <t>let after suddenly than did definitely way already really primarily put our partly only first old more basically first these initially quickly been everything old you everyone everyone how should because especially through out are should more partly during really sometimes originally not you quickly can perhaps usually totally too would would completely for had there them his everything although from its basically while than another normally especially eventually primarily put therefore immediately some this that would partly with use did after exactly especially each she entirely said mainly carefully all man although first something suddenly her sometimes which has</t>
+  </si>
+  <si>
+    <t>Dave: Can we schedule a follow-up? Alice: Let me check and get back to you. Alice: Any other items for today?</t>
+  </si>
+  <si>
+    <t>especially your them can recently too was would could for other suddenly mostly has than already did put than did suddenly get which these would when certainly now without through him before said fully immediately always you during would was more all recently anything had another however partly completely basically said let out entirely anything particularly during quickly you could initially initially fully she fully will already mostly but absolutely without say has too way how get sometimes more partly while totally you our definitely immediately immediately them obviously that and boy normally have anything new basically because all therefore</t>
+  </si>
+  <si>
+    <t>Eve: Thanks for the update. Bob: That works for me. Dave: Sounds good to me.</t>
+  </si>
+  <si>
+    <t>first and primarily one between especially particularly with way before will but too immediately each only perhaps old basically there out have many always would therefore all too she out sometimes originally its now her been entirely this its quickly not can who get way without about get him during however put would some immediately definitely and partly completely and after man there finally only while someone these day gradually before man already especially something while quickly while his slowly primarily only absolutely them mostly how did mostly his during basically put too put man nothing has when his immediately</t>
   </si>
   <si>
     <t>Note for row 150</t>
+  </si>
+  <si>
+    <t>Dave: Thanks for the update. Bob: Got it, thanks.</t>
   </si>
 </sst>
 </file>
@@ -986,10 +1439,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F151"/>
+  <dimension ref="A1:G151"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1008,3005 +1461,3458 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" s="2">
-        <v>45143.102791412035</v>
+        <v>44985.28372340278</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E3" s="2">
-        <v>45697.760646967596</v>
+        <v>45473.505161215275</v>
       </c>
       <c r="F3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E4" s="2">
-        <v>45821.44162861111</v>
+        <v>45506.137818310184</v>
       </c>
       <c r="F4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="E5" s="2">
-        <v>45057.88314319444</v>
+        <v>45728.055501689814</v>
       </c>
       <c r="F5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D6" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E6" s="2">
-        <v>45122.707466747685</v>
+        <v>45507.30357337963</v>
       </c>
       <c r="F6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+      <c r="G6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D7" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E7" s="2">
-        <v>45193.430932627314</v>
+        <v>45171.792012164355</v>
       </c>
       <c r="F7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="D8" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="E8" s="2">
-        <v>46009.90825703704</v>
+        <v>45883.45878003472</v>
       </c>
       <c r="F8" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="C9" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D9" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E9" s="2">
-        <v>45878.77666171297</v>
+        <v>45802.69273971065</v>
       </c>
       <c r="F9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="C10" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D10" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="E10" s="2">
-        <v>45076.42203559028</v>
+        <v>45515.475350277775</v>
       </c>
       <c r="F10" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="C11" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="D11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E11" s="2">
-        <v>45138.48773146991</v>
+        <v>45936.17425246528</v>
       </c>
       <c r="F11" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="G11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="C12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D12" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="E12" s="2">
-        <v>45679.28192152778</v>
+        <v>45442.69774015046</v>
       </c>
       <c r="F12" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G12" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="C13" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="D13" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E13" s="2">
-        <v>45144.16939466435</v>
+        <v>45208.76590190972</v>
       </c>
       <c r="F13" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G13" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="C14" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="D14" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E14" s="2">
-        <v>45078.7568859375</v>
+        <v>45021.46291543981</v>
       </c>
       <c r="F14" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G14" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="C15" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="D15" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="E15" s="2">
-        <v>45696.449137476855</v>
+        <v>44987.38245568287</v>
       </c>
       <c r="F15" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G15" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="C16" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D16" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E16" s="2">
-        <v>45744.10516129629</v>
+        <v>45381.55144098379</v>
       </c>
       <c r="F16" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+      <c r="G16" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="C17" t="s">
+        <v>27</v>
+      </c>
+      <c r="D17" t="s">
         <v>17</v>
       </c>
-      <c r="D17" t="s">
-        <v>12</v>
-      </c>
       <c r="E17" s="2">
-        <v>45151.89314263889</v>
+        <v>45190.73110344907</v>
       </c>
       <c r="F17" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G17" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="C18" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D18" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E18" s="2">
-        <v>45671.01203032407</v>
+        <v>45321.73537011574</v>
       </c>
       <c r="F18" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G18" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="C19" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D19" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="E19" s="2">
-        <v>45304.27519170139</v>
+        <v>44990.94540391203</v>
       </c>
       <c r="F19" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G19" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="C20" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D20" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E20" s="2">
-        <v>45719.76739822917</v>
+        <v>45120.816194444444</v>
       </c>
       <c r="F20" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G20" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="C21" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D21" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="E21" s="2">
-        <v>44946.65370927083</v>
+        <v>44955.68515625</v>
       </c>
       <c r="F21" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+      <c r="G21" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="C22" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="D22" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E22" s="2">
-        <v>45664.791974085645</v>
+        <v>45056.38006516204</v>
       </c>
       <c r="F22" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G22" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="C23" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D23" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="E23" s="2">
-        <v>45962.12483390047</v>
+        <v>45697.92133172454</v>
       </c>
       <c r="F23" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G23" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="C24" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D24" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="E24" s="2">
-        <v>45598.033099548615</v>
+        <v>45987.612000497684</v>
       </c>
       <c r="F24" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G24" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="C25" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D25" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E25" s="2">
-        <v>45478.49549498843</v>
+        <v>45163.56921915509</v>
       </c>
       <c r="F25" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G25" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="C26" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="D26" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E26" s="2">
-        <v>45202.230008391205</v>
+        <v>45139.84469167824</v>
       </c>
       <c r="F26" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+      <c r="G26" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="C27" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D27" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="E27" s="2">
-        <v>45618.37576520833</v>
+        <v>45185.53173827546</v>
       </c>
       <c r="F27" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G27" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="C28" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="D28" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E28" s="2">
-        <v>45977.138562002314</v>
+        <v>45192.526607210646</v>
       </c>
       <c r="F28" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G28" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="C29" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D29" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E29" s="2">
-        <v>45815.97288748843</v>
+        <v>45419.53191900463</v>
       </c>
       <c r="F29" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G29" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="C30" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D30" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="E30" s="2">
-        <v>45660.64593579861</v>
+        <v>45518.48851376158</v>
       </c>
       <c r="F30" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G30" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="C31" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D31" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E31" s="2">
-        <v>45880.354467268524</v>
+        <v>45927.39661243056</v>
       </c>
       <c r="F31" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+      <c r="G31" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="C32" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="D32" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E32" s="2">
-        <v>45685.21020480324</v>
+        <v>45485.19261200231</v>
       </c>
       <c r="F32" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G32" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>55</v>
+        <v>87</v>
       </c>
       <c r="C33" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D33" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E33" s="2">
-        <v>45612.37371875</v>
+        <v>45740.43992188657</v>
       </c>
       <c r="F33" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G33" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>56</v>
+        <v>89</v>
       </c>
       <c r="C34" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D34" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E34" s="2">
-        <v>45494.31045087963</v>
+        <v>45003.186704039355</v>
       </c>
       <c r="F34" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G34" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>57</v>
+        <v>91</v>
       </c>
       <c r="C35" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D35" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="E35" s="2">
-        <v>45060.568756608795</v>
+        <v>45728.21999571759</v>
       </c>
       <c r="F35" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G35" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="C36" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D36" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="E36" s="2">
-        <v>45661.90853741898</v>
+        <v>45480.027521724536</v>
       </c>
       <c r="F36" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+      <c r="G36" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>60</v>
+        <v>96</v>
       </c>
       <c r="C37" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="D37" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="E37" s="2">
-        <v>45534.27098417824</v>
+        <v>45664.03746309028</v>
       </c>
       <c r="F37" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G37" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
       <c r="C38" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="D38" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="E38" s="2">
-        <v>45506.75747222222</v>
+        <v>45353.20950547454</v>
       </c>
       <c r="F38" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G38" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="C39" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="D39" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="E39" s="2">
-        <v>46021.89227866898</v>
+        <v>45098.57800689815</v>
       </c>
       <c r="F39" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G39" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="C40" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="D40" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E40" s="2">
-        <v>45022.056310960645</v>
+        <v>45978.32485417824</v>
       </c>
       <c r="F40" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G40" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>64</v>
+        <v>104</v>
       </c>
       <c r="C41" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D41" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E41" s="2">
-        <v>45680.0072115625</v>
+        <v>45166.68204342593</v>
       </c>
       <c r="F41" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+      <c r="G41" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>66</v>
+        <v>107</v>
       </c>
       <c r="C42" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="D42" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="E42" s="2">
-        <v>45946.32523164352</v>
+        <v>45230.78626761574</v>
       </c>
       <c r="F42" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G42" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>67</v>
+        <v>109</v>
       </c>
       <c r="C43" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="D43" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E43" s="2">
-        <v>45973.52818863426</v>
+        <v>45355.59709952546</v>
       </c>
       <c r="F43" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G43" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>68</v>
+        <v>111</v>
       </c>
       <c r="C44" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="D44" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="E44" s="2">
-        <v>45982.669965497684</v>
+        <v>45035.930512928244</v>
       </c>
       <c r="F44" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G44" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>69</v>
+        <v>113</v>
       </c>
       <c r="C45" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D45" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E45" s="2">
-        <v>45207.11188556713</v>
+        <v>45065.88855054398</v>
       </c>
       <c r="F45" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G45" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>70</v>
+        <v>115</v>
       </c>
       <c r="C46" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D46" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="E46" s="2">
-        <v>45291.52353407408</v>
+        <v>45610.33681540509</v>
       </c>
       <c r="F46" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+      <c r="G46" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>72</v>
+        <v>118</v>
       </c>
       <c r="C47" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D47" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E47" s="2">
-        <v>45613.24155820602</v>
+        <v>45995.864919837964</v>
       </c>
       <c r="F47" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G47" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>73</v>
+        <v>120</v>
       </c>
       <c r="C48" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="D48" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E48" s="2">
-        <v>45425.96323892361</v>
+        <v>45490.752778368056</v>
       </c>
       <c r="F48" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G48" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>74</v>
+        <v>122</v>
       </c>
       <c r="C49" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D49" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="E49" s="2">
-        <v>45990.90592821759</v>
+        <v>45564.364519016206</v>
       </c>
       <c r="F49" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G49" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>75</v>
+        <v>124</v>
       </c>
       <c r="C50" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D50" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E50" s="2">
-        <v>45049.124113784725</v>
+        <v>45623.599512245375</v>
       </c>
       <c r="F50" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G50" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>76</v>
+        <v>126</v>
       </c>
       <c r="C51" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D51" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="E51" s="2">
-        <v>45941.83024940972</v>
+        <v>45811.9235183912</v>
       </c>
       <c r="F51" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+      <c r="G51" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>78</v>
+        <v>129</v>
       </c>
       <c r="C52" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D52" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E52" s="2">
-        <v>44983.69295790509</v>
+        <v>45720.68672372685</v>
       </c>
       <c r="F52" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G52" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>79</v>
+        <v>131</v>
       </c>
       <c r="C53" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D53" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E53" s="2">
-        <v>45135.63467547453</v>
+        <v>45616.891705891205</v>
       </c>
       <c r="F53" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G53" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>80</v>
+        <v>133</v>
       </c>
       <c r="C54" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="D54" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="E54" s="2">
-        <v>45563.86546690972</v>
+        <v>45027.24291149306</v>
       </c>
       <c r="F54" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G54" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>81</v>
+        <v>135</v>
       </c>
       <c r="C55" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D55" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="E55" s="2">
-        <v>45020.3392925463</v>
+        <v>45843.89208065972</v>
       </c>
       <c r="F55" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G55" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>82</v>
+        <v>137</v>
       </c>
       <c r="C56" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D56" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="E56" s="2">
-        <v>45116.560534097225</v>
+        <v>45736.07226515046</v>
       </c>
       <c r="F56" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+        <v>138</v>
+      </c>
+      <c r="G56" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>84</v>
+        <v>140</v>
       </c>
       <c r="C57" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D57" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="E57" s="2">
-        <v>45715.693400324075</v>
+        <v>45400.41687768519</v>
       </c>
       <c r="F57" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G57" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>85</v>
+        <v>142</v>
       </c>
       <c r="C58" t="s">
+        <v>27</v>
+      </c>
+      <c r="D58" t="s">
         <v>17</v>
       </c>
-      <c r="D58" t="s">
-        <v>26</v>
-      </c>
       <c r="E58" s="2">
-        <v>45462.207752511575</v>
+        <v>44957.99531815972</v>
       </c>
       <c r="F58" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G58" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>86</v>
+        <v>144</v>
       </c>
       <c r="C59" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D59" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="E59" s="2">
-        <v>45442.94714199074</v>
+        <v>45234.60419372685</v>
       </c>
       <c r="F59" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G59" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>87</v>
+        <v>146</v>
       </c>
       <c r="C60" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="D60" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="E60" s="2">
-        <v>45917.88822875</v>
+        <v>45818.20147559028</v>
       </c>
       <c r="F60" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G60" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>88</v>
+        <v>148</v>
       </c>
       <c r="C61" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D61" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E61" s="2">
-        <v>45660.3972925</v>
+        <v>45935.13023473379</v>
       </c>
       <c r="F61" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+        <v>149</v>
+      </c>
+      <c r="G61" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>90</v>
+        <v>151</v>
       </c>
       <c r="C62" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="D62" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E62" s="2">
-        <v>45244.33806231481</v>
+        <v>45302.556765914356</v>
       </c>
       <c r="F62" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G62" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>91</v>
+        <v>153</v>
       </c>
       <c r="C63" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="D63" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E63" s="2">
-        <v>45293.99625136574</v>
+        <v>45294.62664263889</v>
       </c>
       <c r="F63" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G63" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>92</v>
+        <v>155</v>
       </c>
       <c r="C64" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="D64" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E64" s="2">
-        <v>45739.185270104164</v>
+        <v>45467.796339560184</v>
       </c>
       <c r="F64" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G64" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>93</v>
+        <v>157</v>
       </c>
       <c r="C65" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="D65" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="E65" s="2">
-        <v>45452.03619690972</v>
+        <v>45335.1821847338</v>
       </c>
       <c r="F65" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G65" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>94</v>
+        <v>159</v>
       </c>
       <c r="C66" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="D66" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E66" s="2">
-        <v>45802.069729930554</v>
+        <v>45311.052109675926</v>
       </c>
       <c r="F66" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+        <v>160</v>
+      </c>
+      <c r="G66" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>96</v>
+        <v>162</v>
       </c>
       <c r="C67" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D67" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="E67" s="2">
-        <v>45587.77622542824</v>
+        <v>45535.51867761574</v>
       </c>
       <c r="F67" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G67" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>97</v>
+        <v>164</v>
       </c>
       <c r="C68" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="D68" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E68" s="2">
-        <v>44976.783875196765</v>
+        <v>45953.30696099537</v>
       </c>
       <c r="F68" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G68" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C69" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="D69" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E69" s="2">
-        <v>45102.417371620366</v>
+        <v>46002.94170137732</v>
       </c>
       <c r="F69" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G69" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>99</v>
+        <v>168</v>
       </c>
       <c r="C70" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D70" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E70" s="2">
-        <v>45816.34622247685</v>
+        <v>45516.61608061343</v>
       </c>
       <c r="F70" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G70" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>100</v>
+        <v>170</v>
       </c>
       <c r="C71" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="D71" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E71" s="2">
-        <v>45128.61241459491</v>
+        <v>45958.16971809028</v>
       </c>
       <c r="F71" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+        <v>171</v>
+      </c>
+      <c r="G71" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>102</v>
+        <v>173</v>
       </c>
       <c r="C72" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D72" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="E72" s="2">
-        <v>45362.548487465276</v>
+        <v>45239.540429305554</v>
       </c>
       <c r="F72" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G72" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>103</v>
+        <v>175</v>
       </c>
       <c r="C73" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="D73" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="E73" s="2">
-        <v>45185.82872722222</v>
+        <v>45433.2772591088</v>
       </c>
       <c r="F73" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G73" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>104</v>
+        <v>177</v>
       </c>
       <c r="C74" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="D74" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="E74" s="2">
-        <v>45783.604509502315</v>
+        <v>45028.213824189814</v>
       </c>
       <c r="F74" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G74" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>105</v>
+        <v>179</v>
       </c>
       <c r="C75" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="D75" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E75" s="2">
-        <v>45679.71418309028</v>
+        <v>45527.03661445602</v>
       </c>
       <c r="F75" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G75" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>106</v>
+        <v>181</v>
       </c>
       <c r="C76" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="D76" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E76" s="2">
-        <v>45737.10757591436</v>
+        <v>45105.430805972224</v>
       </c>
       <c r="F76" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+        <v>182</v>
+      </c>
+      <c r="G76" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>108</v>
+        <v>184</v>
       </c>
       <c r="C77" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="D77" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E77" s="2">
-        <v>45531.011194328705</v>
+        <v>45639.95255487268</v>
       </c>
       <c r="F77" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G77" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>109</v>
+        <v>186</v>
       </c>
       <c r="C78" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D78" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="E78" s="2">
-        <v>45865.47856950232</v>
+        <v>44964.21926517361</v>
       </c>
       <c r="F78" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G78" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>110</v>
+        <v>188</v>
       </c>
       <c r="C79" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="D79" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E79" s="2">
-        <v>45991.24701575231</v>
+        <v>45708.60857604167</v>
       </c>
       <c r="F79" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G79" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>111</v>
+        <v>190</v>
       </c>
       <c r="C80" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="D80" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E80" s="2">
-        <v>45494.81253793981</v>
+        <v>44962.5959587963</v>
       </c>
       <c r="F80" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G80" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>112</v>
+        <v>192</v>
       </c>
       <c r="C81" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="D81" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E81" s="2">
-        <v>45018.91857383102</v>
+        <v>45954.233109560184</v>
       </c>
       <c r="F81" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+        <v>193</v>
+      </c>
+      <c r="G81" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>114</v>
+        <v>195</v>
       </c>
       <c r="C82" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D82" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="E82" s="2">
-        <v>45195.333881805556</v>
+        <v>45914.23393903935</v>
       </c>
       <c r="F82" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G82" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>115</v>
+        <v>197</v>
       </c>
       <c r="C83" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D83" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="E83" s="2">
-        <v>45144.2159972338</v>
+        <v>45916.55266976852</v>
       </c>
       <c r="F83" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G83" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>116</v>
+        <v>199</v>
       </c>
       <c r="C84" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="D84" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="E84" s="2">
-        <v>45541.17612150463</v>
+        <v>46003.01454564815</v>
       </c>
       <c r="F84" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G84" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>117</v>
+        <v>201</v>
       </c>
       <c r="C85" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="D85" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E85" s="2">
-        <v>45921.00710207176</v>
+        <v>45184.68932694444</v>
       </c>
       <c r="F85" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G85" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>118</v>
+        <v>203</v>
       </c>
       <c r="C86" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D86" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E86" s="2">
-        <v>45781.68917100695</v>
+        <v>45165.907294652774</v>
       </c>
       <c r="F86" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+        <v>204</v>
+      </c>
+      <c r="G86" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>120</v>
+        <v>206</v>
       </c>
       <c r="C87" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D87" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="E87" s="2">
-        <v>45605.27464834491</v>
+        <v>44978.10087409722</v>
       </c>
       <c r="F87" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G87" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>121</v>
+        <v>208</v>
       </c>
       <c r="C88" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D88" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="E88" s="2">
-        <v>45806.6847171875</v>
+        <v>45258.709709131945</v>
       </c>
       <c r="F88" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G88" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>122</v>
+        <v>210</v>
       </c>
       <c r="C89" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D89" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E89" s="2">
-        <v>45038.293456388885</v>
+        <v>45495.08433222222</v>
       </c>
       <c r="F89" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G89" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>123</v>
+        <v>212</v>
       </c>
       <c r="C90" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="D90" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="E90" s="2">
-        <v>45255.2180877662</v>
+        <v>44960.44466962963</v>
       </c>
       <c r="F90" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G90" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>124</v>
+        <v>214</v>
       </c>
       <c r="C91" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="D91" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E91" s="2">
-        <v>45627.365948692124</v>
+        <v>45263.67264236111</v>
       </c>
       <c r="F91" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+        <v>215</v>
+      </c>
+      <c r="G91" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>126</v>
+        <v>217</v>
       </c>
       <c r="C92" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="D92" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E92" s="2">
-        <v>45855.4849374537</v>
+        <v>45941.580582002316</v>
       </c>
       <c r="F92" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G92" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>127</v>
+        <v>219</v>
       </c>
       <c r="C93" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D93" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E93" s="2">
-        <v>45929.957528252315</v>
+        <v>45051.26440961806</v>
       </c>
       <c r="F93" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G93" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>128</v>
+        <v>221</v>
       </c>
       <c r="C94" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="D94" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="E94" s="2">
-        <v>45031.54272760417</v>
+        <v>45758.96857486111</v>
       </c>
       <c r="F94" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G94" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>129</v>
+        <v>223</v>
       </c>
       <c r="C95" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="D95" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E95" s="2">
-        <v>45043.196392962964</v>
+        <v>45435.274083888886</v>
       </c>
       <c r="F95" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G95" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>130</v>
+        <v>225</v>
       </c>
       <c r="C96" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D96" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E96" s="2">
-        <v>45204.895870555556</v>
+        <v>45847.39112222222</v>
       </c>
       <c r="F96" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+        <v>226</v>
+      </c>
+      <c r="G96" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>132</v>
+        <v>228</v>
       </c>
       <c r="C97" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="D97" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E97" s="2">
-        <v>44929.925646620366</v>
+        <v>45676.47784122685</v>
       </c>
       <c r="F97" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G97" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>133</v>
+        <v>230</v>
       </c>
       <c r="C98" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="D98" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="E98" s="2">
-        <v>45835.8027225</v>
+        <v>45541.36499606482</v>
       </c>
       <c r="F98" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G98" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>134</v>
+        <v>232</v>
       </c>
       <c r="C99" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D99" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E99" s="2">
-        <v>45086.501720451386</v>
+        <v>45052.40101703704</v>
       </c>
       <c r="F99" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G99" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>135</v>
+        <v>234</v>
       </c>
       <c r="C100" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D100" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="E100" s="2">
-        <v>45104.61304674769</v>
+        <v>45302.71360663194</v>
       </c>
       <c r="F100" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G100" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>136</v>
+        <v>236</v>
       </c>
       <c r="C101" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D101" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E101" s="2">
-        <v>45295.220789363426</v>
+        <v>45506.506499236115</v>
       </c>
       <c r="F101" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+        <v>237</v>
+      </c>
+      <c r="G101" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>138</v>
+        <v>239</v>
       </c>
       <c r="C102" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D102" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="E102" s="2">
-        <v>45659.3377363426</v>
+        <v>45056.49916269676</v>
       </c>
       <c r="F102" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G102" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>139</v>
+        <v>241</v>
       </c>
       <c r="C103" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="D103" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E103" s="2">
-        <v>45155.052664386574</v>
+        <v>45355.5749168287</v>
       </c>
       <c r="F103" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G103" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>140</v>
+        <v>243</v>
       </c>
       <c r="C104" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D104" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E104" s="2">
-        <v>45608.08380554398</v>
+        <v>45695.15101966435</v>
       </c>
       <c r="F104" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G104" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>141</v>
+        <v>245</v>
       </c>
       <c r="C105" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D105" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E105" s="2">
-        <v>46003.01426872685</v>
+        <v>44962.36287738426</v>
       </c>
       <c r="F105" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G105" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>142</v>
+        <v>247</v>
       </c>
       <c r="C106" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="D106" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E106" s="2">
-        <v>45739.81275774306</v>
+        <v>45499.22285344907</v>
       </c>
       <c r="F106" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+        <v>248</v>
+      </c>
+      <c r="G106" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>144</v>
+        <v>250</v>
       </c>
       <c r="C107" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D107" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="E107" s="2">
-        <v>45100.53655638889</v>
+        <v>45392.83781189815</v>
       </c>
       <c r="F107" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G107" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>145</v>
+        <v>252</v>
       </c>
       <c r="C108" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D108" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E108" s="2">
-        <v>44933.57071270833</v>
+        <v>45483.082809722226</v>
       </c>
       <c r="F108" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G108" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>146</v>
+        <v>254</v>
       </c>
       <c r="C109" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D109" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E109" s="2">
-        <v>45065.12355366898</v>
+        <v>45868.89017791666</v>
       </c>
       <c r="F109" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G109" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>147</v>
+        <v>256</v>
       </c>
       <c r="C110" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D110" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="E110" s="2">
-        <v>45763.93087628472</v>
+        <v>45651.097384479166</v>
       </c>
       <c r="F110" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G110" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>148</v>
+        <v>258</v>
       </c>
       <c r="C111" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="D111" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="E111" s="2">
-        <v>46015.46855576389</v>
+        <v>45073.02354079861</v>
       </c>
       <c r="F111" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+        <v>259</v>
+      </c>
+      <c r="G111" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>150</v>
+        <v>261</v>
       </c>
       <c r="C112" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="D112" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="E112" s="2">
-        <v>45471.93298210648</v>
+        <v>45798.32618423611</v>
       </c>
       <c r="F112" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G112" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>151</v>
+        <v>263</v>
       </c>
       <c r="C113" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="D113" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="E113" s="2">
-        <v>45111.78447400463</v>
+        <v>45911.58478009259</v>
       </c>
       <c r="F113" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G113" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>152</v>
+        <v>265</v>
       </c>
       <c r="C114" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="D114" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E114" s="2">
-        <v>45558.33870226852</v>
+        <v>45613.62141184028</v>
       </c>
       <c r="F114" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G114" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>153</v>
+        <v>267</v>
       </c>
       <c r="C115" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D115" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="E115" s="2">
-        <v>45242.59115586805</v>
+        <v>45082.269679895835</v>
       </c>
       <c r="F115" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G115" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>154</v>
+        <v>269</v>
       </c>
       <c r="C116" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="D116" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="E116" s="2">
-        <v>45968.935523125</v>
+        <v>46015.79121354167</v>
       </c>
       <c r="F116" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+        <v>270</v>
+      </c>
+      <c r="G116" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>156</v>
+        <v>272</v>
       </c>
       <c r="C117" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D117" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E117" s="2">
-        <v>44975.541631875</v>
+        <v>45677.40574072917</v>
       </c>
       <c r="F117" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G117" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>157</v>
+        <v>274</v>
       </c>
       <c r="C118" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="D118" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E118" s="2">
-        <v>45477.8994446875</v>
+        <v>45838.84162186342</v>
       </c>
       <c r="F118" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G118" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>158</v>
+        <v>276</v>
       </c>
       <c r="C119" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D119" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E119" s="2">
-        <v>45791.11059719908</v>
+        <v>46004.96139363426</v>
       </c>
       <c r="F119" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G119" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>159</v>
+        <v>278</v>
       </c>
       <c r="C120" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D120" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E120" s="2">
-        <v>45197.949214004635</v>
+        <v>45288.91956030093</v>
       </c>
       <c r="F120" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G120" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>160</v>
+        <v>280</v>
       </c>
       <c r="C121" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D121" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E121" s="2">
-        <v>45946.68050296296</v>
+        <v>45813.053018425926</v>
       </c>
       <c r="F121" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+        <v>281</v>
+      </c>
+      <c r="G121" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>162</v>
+        <v>283</v>
       </c>
       <c r="C122" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D122" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E122" s="2">
-        <v>45169.05375190973</v>
+        <v>45992.223867152774</v>
       </c>
       <c r="F122" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G122" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>163</v>
+        <v>285</v>
       </c>
       <c r="C123" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D123" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E123" s="2">
-        <v>45313.756019328706</v>
+        <v>45532.72355439815</v>
       </c>
       <c r="F123" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G123" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>164</v>
+        <v>287</v>
       </c>
       <c r="C124" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D124" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E124" s="2">
-        <v>45202.72132285879</v>
+        <v>45555.4931994213</v>
       </c>
       <c r="F124" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G124" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>165</v>
+        <v>289</v>
       </c>
       <c r="C125" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D125" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="E125" s="2">
-        <v>45460.47408533565</v>
+        <v>45540.089882175926</v>
       </c>
       <c r="F125" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G125" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>166</v>
+        <v>291</v>
       </c>
       <c r="C126" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="D126" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="E126" s="2">
-        <v>45105.3390234375</v>
+        <v>44964.88472938657</v>
       </c>
       <c r="F126" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+        <v>292</v>
+      </c>
+      <c r="G126" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>168</v>
+        <v>294</v>
       </c>
       <c r="C127" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D127" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E127" s="2">
-        <v>45279.23010043982</v>
+        <v>44953.94492369213</v>
       </c>
       <c r="F127" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G127" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>169</v>
+        <v>296</v>
       </c>
       <c r="C128" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D128" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="E128" s="2">
-        <v>45082.08718877315</v>
+        <v>45324.695443923614</v>
       </c>
       <c r="F128" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G128" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>170</v>
+        <v>298</v>
       </c>
       <c r="C129" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D129" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="E129" s="2">
-        <v>45062.358714918984</v>
+        <v>45101.035642731484</v>
       </c>
       <c r="F129" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G129" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>171</v>
+        <v>300</v>
       </c>
       <c r="C130" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D130" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="E130" s="2">
-        <v>45905.68349335648</v>
+        <v>45129.42967627315</v>
       </c>
       <c r="F130" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G130" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>172</v>
+        <v>302</v>
       </c>
       <c r="C131" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D131" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="E131" s="2">
-        <v>45205.43582445601</v>
+        <v>45566.74313787037</v>
       </c>
       <c r="F131" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+        <v>303</v>
+      </c>
+      <c r="G131" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>174</v>
+        <v>305</v>
       </c>
       <c r="C132" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D132" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E132" s="2">
-        <v>45490.407541203705</v>
+        <v>45264.48665486111</v>
       </c>
       <c r="F132" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G132" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>175</v>
+        <v>307</v>
       </c>
       <c r="C133" t="s">
+        <v>38</v>
+      </c>
+      <c r="D133" t="s">
         <v>21</v>
       </c>
-      <c r="D133" t="s">
-        <v>15</v>
-      </c>
       <c r="E133" s="2">
-        <v>45915.94741604167</v>
+        <v>46009.39292804398</v>
       </c>
       <c r="F133" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G133" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>176</v>
+        <v>309</v>
       </c>
       <c r="C134" t="s">
+        <v>13</v>
+      </c>
+      <c r="D134" t="s">
         <v>21</v>
       </c>
-      <c r="D134" t="s">
-        <v>12</v>
-      </c>
       <c r="E134" s="2">
-        <v>45147.367361655095</v>
+        <v>45750.978238842596</v>
       </c>
       <c r="F134" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G134" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>177</v>
+        <v>311</v>
       </c>
       <c r="C135" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="D135" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="E135" s="2">
-        <v>45371.36429104167</v>
+        <v>45440.029211284724</v>
       </c>
       <c r="F135" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G135" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>178</v>
+        <v>313</v>
       </c>
       <c r="C136" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="D136" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E136" s="2">
-        <v>45702.90671173611</v>
+        <v>45853.02421038195</v>
       </c>
       <c r="F136" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+        <v>314</v>
+      </c>
+      <c r="G136" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>180</v>
+        <v>316</v>
       </c>
       <c r="C137" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="D137" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="E137" s="2">
-        <v>44951.40575826389</v>
+        <v>45950.411978749995</v>
       </c>
       <c r="F137" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G137" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>137</v>
       </c>
       <c r="B138" t="s">
-        <v>181</v>
+        <v>318</v>
       </c>
       <c r="C138" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="D138" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E138" s="2">
-        <v>45708.804541875</v>
+        <v>45778.29636489583</v>
       </c>
       <c r="F138" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G138" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>182</v>
+        <v>320</v>
       </c>
       <c r="C139" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D139" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="E139" s="2">
-        <v>45718.64279629629</v>
+        <v>45140.5583369213</v>
       </c>
       <c r="F139" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G139" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>183</v>
+        <v>322</v>
       </c>
       <c r="C140" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="D140" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="E140" s="2">
-        <v>45117.51364377315</v>
+        <v>45707.56647947917</v>
       </c>
       <c r="F140" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G140" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>184</v>
+        <v>324</v>
       </c>
       <c r="C141" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D141" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="E141" s="2">
-        <v>45866.755907280094</v>
+        <v>45187.61086648148</v>
       </c>
       <c r="F141" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+        <v>325</v>
+      </c>
+      <c r="G141" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>186</v>
+        <v>327</v>
       </c>
       <c r="C142" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D142" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="E142" s="2">
-        <v>45303.916257268516</v>
+        <v>45027.952963171294</v>
       </c>
       <c r="F142" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G142" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>187</v>
+        <v>329</v>
       </c>
       <c r="C143" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="D143" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E143" s="2">
-        <v>45383.74967056713</v>
+        <v>44988.76783952546</v>
       </c>
       <c r="F143" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G143" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>143</v>
       </c>
       <c r="B144" t="s">
-        <v>188</v>
+        <v>331</v>
       </c>
       <c r="C144" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="D144" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="E144" s="2">
-        <v>45396.83874436343</v>
+        <v>45748.65552069445</v>
       </c>
       <c r="F144" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G144" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>144</v>
       </c>
       <c r="B145" t="s">
-        <v>189</v>
+        <v>333</v>
       </c>
       <c r="C145" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D145" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E145" s="2">
-        <v>45323.514683587964</v>
+        <v>45037.62701403935</v>
       </c>
       <c r="F145" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G145" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>145</v>
       </c>
       <c r="B146" t="s">
-        <v>190</v>
+        <v>335</v>
       </c>
       <c r="C146" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D146" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="E146" s="2">
-        <v>45869.27488871528</v>
+        <v>45487.90942037037</v>
       </c>
       <c r="F146" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+        <v>336</v>
+      </c>
+      <c r="G146" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>146</v>
       </c>
       <c r="B147" t="s">
-        <v>192</v>
+        <v>338</v>
       </c>
       <c r="C147" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="D147" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="E147" s="2">
-        <v>45442.23598269676</v>
+        <v>45573.61754835648</v>
       </c>
       <c r="F147" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G147" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>147</v>
       </c>
       <c r="B148" t="s">
-        <v>193</v>
+        <v>340</v>
       </c>
       <c r="C148" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D148" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E148" s="2">
-        <v>45220.314411099534</v>
+        <v>45648.464409039356</v>
       </c>
       <c r="F148" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G148" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>148</v>
       </c>
       <c r="B149" t="s">
-        <v>194</v>
+        <v>342</v>
       </c>
       <c r="C149" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="D149" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="E149" s="2">
-        <v>45600.72355949074</v>
+        <v>45855.216170775464</v>
       </c>
       <c r="F149" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G149" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>149</v>
       </c>
       <c r="B150" t="s">
-        <v>195</v>
+        <v>344</v>
       </c>
       <c r="C150" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="D150" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E150" s="2">
-        <v>45128.62223987268</v>
+        <v>45098.60729505787</v>
       </c>
       <c r="F150" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G150" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>150</v>
       </c>
       <c r="B151" t="s">
-        <v>196</v>
+        <v>346</v>
       </c>
       <c r="C151" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="D151" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="E151" s="2">
-        <v>45042.47163914352</v>
+        <v>45507.37991927083</v>
       </c>
       <c r="F151" t="s">
-        <v>197</v>
+        <v>347</v>
+      </c>
+      <c r="G151" t="s">
+        <v>348</v>
       </c>
     </row>
   </sheetData>
